--- a/01_AI_Governance_Risk_Compliance/1.2_AI_Risk_Assessment_Framework/GT_AI_Risk_Assessment_Toolkit_Worked_Example.xlsx
+++ b/01_AI_Governance_Risk_Compliance/1.2_AI_Risk_Assessment_Framework/GT_AI_Risk_Assessment_Toolkit_Worked_Example.xlsx
@@ -2,7 +2,6 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
@@ -18,8 +17,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="9" state="hidden" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4. Risk Register'!$A$4:$T$62</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Taxonomy'!$A$4:$G$52</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Guide'!$A$1:$C$13</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'1. Use Case Profile'!$A$1:$D$19</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'2. Prohibited Screen'!$A$1:$D$14</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'3. Risk Tiering'!$A$1:$G$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4. Risk Register'!$A$4:$T$66</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'4. Risk Register'!$A$1:$V$66</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'5. Heat Map &amp; Summary'!$A$1:$N$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Taxonomy'!$A$4:$G$56</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Taxonomy'!$A$1:$G$56</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'Scales'!$A$1:$I$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -981,7 +988,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Companion to the GT AI Risk Assessment Framework (v1.0, 2026). Grant Thornton Bahrain - AI Governance, Risk &amp; Compliance.</t>
+          <t>Companion to the GT AI Risk Assessment Framework (v1.1, 2026). Grant Thornton Bahrain - AI Governance, Risk &amp; Compliance.</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1036,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Work through the 48 taxonomy risks: mark applicability, tailor scenarios, rate likelihood &amp; impact, evaluate existing control effectiveness (mapped to RCM v2.0 controls) and plan treatment. Add bespoke risks in rows BSP-01..10.</t>
+          <t>Work through the 52 taxonomy risks: mark applicability, tailor scenarios, rate likelihood &amp; impact, evaluate existing control effectiveness (mapped to RCM v2.1 controls) and plan treatment. Add bespoke risks in rows BSP-01..10.</t>
         </is>
       </c>
     </row>
@@ -1098,8 +1105,9 @@
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <printOptions gridLines="0"/>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.25" footer="0.25"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1341,8 +1349,9 @@
       <formula1>=Lists!$H$1:$H$4</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <printOptions gridLines="0"/>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.25" footer="0.25"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1589,8 +1598,9 @@
       <formula1>=Lists!$A$1:$A$2</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <printOptions gridLines="0"/>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.25" footer="0.25"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2145,8 +2155,9 @@
       <formula1>=Lists!$U$1:$U$5</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <printOptions gridLines="0"/>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.25" footer="0.25"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2157,7 +2168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V62"/>
+  <dimension ref="A1:V66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2245,7 +2256,7 @@
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
-          <t>Existing / required controls (RCM v2.0)</t>
+          <t>Existing / required controls (RCM v2.1)</t>
         </is>
       </c>
       <c r="K4" s="8" t="inlineStr">
@@ -4223,39 +4234,31 @@
     <row r="30" ht="44" customHeight="1">
       <c r="A30" s="17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>TRA-01</t>
+          <t>PER-05</t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>Transparency, Explainability &amp; Contestability</t>
+          <t>Model Performance, Reliability &amp; Robustness</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Undisclosed AI interaction or content</t>
+          <t>Uncontrolled prompt / configuration changes</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>Users are unaware they interact with AI or that content is AI-generated.</t>
-        </is>
-      </c>
-      <c r="F30" s="17" t="inlineStr">
-        <is>
-          <t>Unlikely</t>
-        </is>
-      </c>
-      <c r="G30" s="17" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
+          <t>Changes to prompts, guardrails, tool permissions or retrieval sources degrade safety or behaviour without regression testing.</t>
+        </is>
+      </c>
+      <c r="F30" s="17" t="n"/>
+      <c r="G30" s="17" t="n"/>
       <c r="H30" s="9">
         <f>IF(OR($A30&lt;&gt;"Yes",F30="",G30=""),"",MATCH(F30,Lists!$B$1:$B$5,0)*MATCH(G30,Lists!$C$1:$C$5,0))</f>
         <v/>
@@ -4266,14 +4269,10 @@
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>CO-1, LC-7</t>
-        </is>
-      </c>
-      <c r="K30" s="17" t="inlineStr">
-        <is>
-          <t>Satisfactory</t>
-        </is>
-      </c>
+          <t>LC-12</t>
+        </is>
+      </c>
+      <c r="K30" s="17" t="n"/>
       <c r="L30" s="9">
         <f>IF(OR(H30="",K30=""),"",ROUND(H30*VLOOKUP(K30,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
@@ -4286,30 +4285,14 @@
         <f>IF(M30="","",IF(OR(M30="Low",M30="Medium"),"Yes","No"))</f>
         <v/>
       </c>
-      <c r="O30" s="17" t="inlineStr">
-        <is>
-          <t>Mitigate</t>
-        </is>
-      </c>
-      <c r="P30" s="7" t="inlineStr">
-        <is>
-          <t>Display 'AI assistant' disclosure and handover-to-human option at session start.</t>
-        </is>
-      </c>
-      <c r="Q30" s="17" t="inlineStr">
-        <is>
-          <t>Product Owner</t>
-        </is>
-      </c>
+      <c r="O30" s="17" t="n"/>
+      <c r="P30" s="7" t="n"/>
+      <c r="Q30" s="17" t="n"/>
       <c r="R30" s="17" t="n"/>
-      <c r="S30" s="17" t="inlineStr">
-        <is>
-          <t>Treatment planned</t>
-        </is>
-      </c>
+      <c r="S30" s="17" t="n"/>
       <c r="T30" s="7" t="inlineStr">
         <is>
-          <t>AI touchpoints lacking disclosure</t>
+          <t>Releases without passing LLM regression suite</t>
         </is>
       </c>
       <c r="V30">
@@ -4320,12 +4303,12 @@
     <row r="31" ht="44" customHeight="1">
       <c r="A31" s="17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>TRA-02</t>
+          <t>TRA-01</t>
         </is>
       </c>
       <c r="C31" s="14" t="inlineStr">
@@ -4335,16 +4318,24 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Unexplainable decisions</t>
+          <t>Undisclosed AI interaction or content</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>Organisation cannot explain AI-supported decisions to affected persons, regulators or auditors.</t>
-        </is>
-      </c>
-      <c r="F31" s="17" t="n"/>
-      <c r="G31" s="17" t="n"/>
+          <t>Users are unaware they interact with AI or that content is AI-generated.</t>
+        </is>
+      </c>
+      <c r="F31" s="17" t="inlineStr">
+        <is>
+          <t>Unlikely</t>
+        </is>
+      </c>
+      <c r="G31" s="17" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
       <c r="H31" s="9">
         <f>IF(OR($A31&lt;&gt;"Yes",F31="",G31=""),"",MATCH(F31,Lists!$B$1:$B$5,0)*MATCH(G31,Lists!$C$1:$C$5,0))</f>
         <v/>
@@ -4355,10 +4346,14 @@
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>RS-4, LC-4</t>
-        </is>
-      </c>
-      <c r="K31" s="17" t="n"/>
+          <t>CO-1, LC-7</t>
+        </is>
+      </c>
+      <c r="K31" s="17" t="inlineStr">
+        <is>
+          <t>Satisfactory</t>
+        </is>
+      </c>
       <c r="L31" s="9">
         <f>IF(OR(H31="",K31=""),"",ROUND(H31*VLOOKUP(K31,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
@@ -4371,14 +4366,30 @@
         <f>IF(M31="","",IF(OR(M31="Low",M31="Medium"),"Yes","No"))</f>
         <v/>
       </c>
-      <c r="O31" s="17" t="n"/>
-      <c r="P31" s="7" t="n"/>
-      <c r="Q31" s="17" t="n"/>
+      <c r="O31" s="17" t="inlineStr">
+        <is>
+          <t>Mitigate</t>
+        </is>
+      </c>
+      <c r="P31" s="7" t="inlineStr">
+        <is>
+          <t>Display 'AI assistant' disclosure and handover-to-human option at session start.</t>
+        </is>
+      </c>
+      <c r="Q31" s="17" t="inlineStr">
+        <is>
+          <t>Product Owner</t>
+        </is>
+      </c>
       <c r="R31" s="17" t="n"/>
-      <c r="S31" s="17" t="n"/>
+      <c r="S31" s="17" t="inlineStr">
+        <is>
+          <t>Treatment planned</t>
+        </is>
+      </c>
       <c r="T31" s="7" t="inlineStr">
         <is>
-          <t>Explanation requests not satisfied</t>
+          <t>AI touchpoints lacking disclosure</t>
         </is>
       </c>
       <c r="V31">
@@ -4394,7 +4405,7 @@
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>TRA-03</t>
+          <t>TRA-02</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
@@ -4404,12 +4415,12 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>No effective contest or redress route</t>
+          <t>Unexplainable decisions</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>Affected persons cannot challenge or obtain human review of AI-supported decisions.</t>
+          <t>Organisation cannot explain AI-supported decisions to affected persons, regulators or auditors.</t>
         </is>
       </c>
       <c r="F32" s="17" t="n"/>
@@ -4424,7 +4435,7 @@
       </c>
       <c r="J32" s="7" t="inlineStr">
         <is>
-          <t>CO-3, PR-5</t>
+          <t>RS-4, LC-4</t>
         </is>
       </c>
       <c r="K32" s="17" t="n"/>
@@ -4447,7 +4458,7 @@
       <c r="S32" s="17" t="n"/>
       <c r="T32" s="7" t="inlineStr">
         <is>
-          <t>Appeals exceeding SLA</t>
+          <t>Explanation requests not satisfied</t>
         </is>
       </c>
       <c r="V32">
@@ -4463,7 +4474,7 @@
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>TRA-04</t>
+          <t>TRA-03</t>
         </is>
       </c>
       <c r="C33" s="14" t="inlineStr">
@@ -4473,12 +4484,12 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Inadequate documentation and records</t>
+          <t>No effective contest or redress route</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>Technical documentation, logs or decisions are insufficient for audit or regulatory inspection.</t>
+          <t>Affected persons cannot challenge or obtain human review of AI-supported decisions.</t>
         </is>
       </c>
       <c r="F33" s="17" t="n"/>
@@ -4493,7 +4504,7 @@
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
-          <t>LC-4, OM-2, RO-3</t>
+          <t>CO-3, PR-5</t>
         </is>
       </c>
       <c r="K33" s="17" t="n"/>
@@ -4516,7 +4527,7 @@
       <c r="S33" s="17" t="n"/>
       <c r="T33" s="7" t="inlineStr">
         <is>
-          <t>Systems with incomplete documentation pack</t>
+          <t>Appeals exceeding SLA</t>
         </is>
       </c>
       <c r="V33">
@@ -4527,39 +4538,31 @@
     <row r="34" ht="44" customHeight="1">
       <c r="A34" s="17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>SEC-01</t>
+          <t>TRA-04</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>Security of AI Systems</t>
+          <t>Transparency, Explainability &amp; Contestability</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Prompt injection and jailbreak</t>
+          <t>Inadequate documentation and records</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>Attacker manipulates model behaviour via direct or indirect (embedded content) instructions.</t>
-        </is>
-      </c>
-      <c r="F34" s="17" t="inlineStr">
-        <is>
-          <t>Likely</t>
-        </is>
-      </c>
-      <c r="G34" s="17" t="inlineStr">
-        <is>
-          <t>Major</t>
-        </is>
-      </c>
+          <t>Technical documentation, logs or decisions are insufficient for audit or regulatory inspection.</t>
+        </is>
+      </c>
+      <c r="F34" s="17" t="n"/>
+      <c r="G34" s="17" t="n"/>
       <c r="H34" s="9">
         <f>IF(OR($A34&lt;&gt;"Yes",F34="",G34=""),"",MATCH(F34,Lists!$B$1:$B$5,0)*MATCH(G34,Lists!$C$1:$C$5,0))</f>
         <v/>
@@ -4570,14 +4573,10 @@
       </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
-          <t>SE-6</t>
-        </is>
-      </c>
-      <c r="K34" s="17" t="inlineStr">
-        <is>
-          <t>Needs improvement</t>
-        </is>
-      </c>
+          <t>LC-4, OM-2, RO-3</t>
+        </is>
+      </c>
+      <c r="K34" s="17" t="n"/>
       <c r="L34" s="9">
         <f>IF(OR(H34="",K34=""),"",ROUND(H34*VLOOKUP(K34,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
@@ -4590,30 +4589,14 @@
         <f>IF(M34="","",IF(OR(M34="Low",M34="Medium"),"Yes","No"))</f>
         <v/>
       </c>
-      <c r="O34" s="17" t="inlineStr">
-        <is>
-          <t>Mitigate</t>
-        </is>
-      </c>
-      <c r="P34" s="7" t="inlineStr">
-        <is>
-          <t>Prompt-injection filters; separate system/user/retrieved content; OWASP LLM red-team before launch.</t>
-        </is>
-      </c>
-      <c r="Q34" s="17" t="inlineStr">
-        <is>
-          <t>CISO</t>
-        </is>
-      </c>
+      <c r="O34" s="17" t="n"/>
+      <c r="P34" s="7" t="n"/>
+      <c r="Q34" s="17" t="n"/>
       <c r="R34" s="17" t="n"/>
-      <c r="S34" s="17" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
+      <c r="S34" s="17" t="n"/>
       <c r="T34" s="7" t="inlineStr">
         <is>
-          <t>Blocked injection attempts / bypasses in testing</t>
+          <t>Systems with incomplete documentation pack</t>
         </is>
       </c>
       <c r="V34">
@@ -4624,12 +4607,12 @@
     <row r="35" ht="44" customHeight="1">
       <c r="A35" s="17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>SEC-02</t>
+          <t>SEC-01</t>
         </is>
       </c>
       <c r="C35" s="14" t="inlineStr">
@@ -4639,16 +4622,24 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Data or model poisoning</t>
+          <t>Prompt injection and jailbreak</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>Training, fine-tuning or retrieval data is manipulated to corrupt outputs or insert backdoors.</t>
-        </is>
-      </c>
-      <c r="F35" s="17" t="n"/>
-      <c r="G35" s="17" t="n"/>
+          <t>Attacker manipulates model behaviour via direct or indirect (embedded content) instructions.</t>
+        </is>
+      </c>
+      <c r="F35" s="17" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="G35" s="17" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
       <c r="H35" s="9">
         <f>IF(OR($A35&lt;&gt;"Yes",F35="",G35=""),"",MATCH(F35,Lists!$B$1:$B$5,0)*MATCH(G35,Lists!$C$1:$C$5,0))</f>
         <v/>
@@ -4659,10 +4650,14 @@
       </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
-          <t>SE-6, LC-1, SE-7</t>
-        </is>
-      </c>
-      <c r="K35" s="17" t="n"/>
+          <t>SE-6</t>
+        </is>
+      </c>
+      <c r="K35" s="17" t="inlineStr">
+        <is>
+          <t>Needs improvement</t>
+        </is>
+      </c>
       <c r="L35" s="9">
         <f>IF(OR(H35="",K35=""),"",ROUND(H35*VLOOKUP(K35,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
@@ -4675,14 +4670,30 @@
         <f>IF(M35="","",IF(OR(M35="Low",M35="Medium"),"Yes","No"))</f>
         <v/>
       </c>
-      <c r="O35" s="17" t="n"/>
-      <c r="P35" s="7" t="n"/>
-      <c r="Q35" s="17" t="n"/>
+      <c r="O35" s="17" t="inlineStr">
+        <is>
+          <t>Mitigate</t>
+        </is>
+      </c>
+      <c r="P35" s="7" t="inlineStr">
+        <is>
+          <t>Prompt-injection filters; separate system/user/retrieved content; OWASP LLM red-team before launch.</t>
+        </is>
+      </c>
+      <c r="Q35" s="17" t="inlineStr">
+        <is>
+          <t>CISO</t>
+        </is>
+      </c>
       <c r="R35" s="17" t="n"/>
-      <c r="S35" s="17" t="n"/>
+      <c r="S35" s="17" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
       <c r="T35" s="7" t="inlineStr">
         <is>
-          <t>Integrity check failures</t>
+          <t>Blocked injection attempts / bypasses in testing</t>
         </is>
       </c>
       <c r="V35">
@@ -4698,7 +4709,7 @@
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>SEC-03</t>
+          <t>SEC-02</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
@@ -4708,12 +4719,12 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Model theft, extraction or inversion</t>
+          <t>Data or model poisoning</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>Model weights, system prompts or training data are extracted.</t>
+          <t>Training, fine-tuning or retrieval data is manipulated to corrupt outputs or insert backdoors.</t>
         </is>
       </c>
       <c r="F36" s="17" t="n"/>
@@ -4728,7 +4739,7 @@
       </c>
       <c r="J36" s="7" t="inlineStr">
         <is>
-          <t>SE-4, SE-6</t>
+          <t>SE-6, LC-1, SE-7</t>
         </is>
       </c>
       <c r="K36" s="17" t="n"/>
@@ -4751,7 +4762,7 @@
       <c r="S36" s="17" t="n"/>
       <c r="T36" s="7" t="inlineStr">
         <is>
-          <t>Anomalous query volumes</t>
+          <t>Integrity check failures</t>
         </is>
       </c>
       <c r="V36">
@@ -4762,12 +4773,12 @@
     <row r="37" ht="44" customHeight="1">
       <c r="A37" s="17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>SEC-04</t>
+          <t>SEC-03</t>
         </is>
       </c>
       <c r="C37" s="14" t="inlineStr">
@@ -4777,24 +4788,16 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Insecure integration and excessive privilege</t>
+          <t>Model theft, extraction or inversion</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>AI components have excessive permissions or insecure APIs/plugins, enabling unauthorised actions.</t>
-        </is>
-      </c>
-      <c r="F37" s="17" t="inlineStr">
-        <is>
-          <t>Possible</t>
-        </is>
-      </c>
-      <c r="G37" s="17" t="inlineStr">
-        <is>
-          <t>Severe</t>
-        </is>
-      </c>
+          <t>Model weights, system prompts or training data are extracted.</t>
+        </is>
+      </c>
+      <c r="F37" s="17" t="n"/>
+      <c r="G37" s="17" t="n"/>
       <c r="H37" s="9">
         <f>IF(OR($A37&lt;&gt;"Yes",F37="",G37=""),"",MATCH(F37,Lists!$B$1:$B$5,0)*MATCH(G37,Lists!$C$1:$C$5,0))</f>
         <v/>
@@ -4805,14 +4808,10 @@
       </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
-          <t>SE-2, LC-8</t>
-        </is>
-      </c>
-      <c r="K37" s="17" t="inlineStr">
-        <is>
-          <t>Needs improvement</t>
-        </is>
-      </c>
+          <t>SE-4, SE-6</t>
+        </is>
+      </c>
+      <c r="K37" s="17" t="n"/>
       <c r="L37" s="9">
         <f>IF(OR(H37="",K37=""),"",ROUND(H37*VLOOKUP(K37,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
@@ -4825,30 +4824,14 @@
         <f>IF(M37="","",IF(OR(M37="Low",M37="Medium"),"Yes","No"))</f>
         <v/>
       </c>
-      <c r="O37" s="17" t="inlineStr">
-        <is>
-          <t>Mitigate</t>
-        </is>
-      </c>
-      <c r="P37" s="7" t="inlineStr">
-        <is>
-          <t>Scoped OAuth tokens per action; transaction limits (BHD 500); step-up authentication for changes.</t>
-        </is>
-      </c>
-      <c r="Q37" s="17" t="inlineStr">
-        <is>
-          <t>CISO</t>
-        </is>
-      </c>
+      <c r="O37" s="17" t="n"/>
+      <c r="P37" s="7" t="n"/>
+      <c r="Q37" s="17" t="n"/>
       <c r="R37" s="17" t="n"/>
-      <c r="S37" s="17" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
+      <c r="S37" s="17" t="n"/>
       <c r="T37" s="7" t="inlineStr">
         <is>
-          <t>Agents / integrations with privileged standing access</t>
+          <t>Anomalous query volumes</t>
         </is>
       </c>
       <c r="V37">
@@ -4859,12 +4842,12 @@
     <row r="38" ht="44" customHeight="1">
       <c r="A38" s="17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>SEC-05</t>
+          <t>SEC-04</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
@@ -4874,16 +4857,24 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Compromised AI supply chain</t>
+          <t>Insecure integration and excessive privilege</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>Malicious or vulnerable third-party models, libraries, plugins or MCP servers.</t>
-        </is>
-      </c>
-      <c r="F38" s="17" t="n"/>
-      <c r="G38" s="17" t="n"/>
+          <t>AI components have excessive permissions or insecure APIs/plugins, enabling unauthorised actions.</t>
+        </is>
+      </c>
+      <c r="F38" s="17" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="G38" s="17" t="inlineStr">
+        <is>
+          <t>Severe</t>
+        </is>
+      </c>
       <c r="H38" s="9">
         <f>IF(OR($A38&lt;&gt;"Yes",F38="",G38=""),"",MATCH(F38,Lists!$B$1:$B$5,0)*MATCH(G38,Lists!$C$1:$C$5,0))</f>
         <v/>
@@ -4894,10 +4885,14 @@
       </c>
       <c r="J38" s="7" t="inlineStr">
         <is>
-          <t>SE-7</t>
-        </is>
-      </c>
-      <c r="K38" s="17" t="n"/>
+          <t>SE-2, LC-8</t>
+        </is>
+      </c>
+      <c r="K38" s="17" t="inlineStr">
+        <is>
+          <t>Needs improvement</t>
+        </is>
+      </c>
       <c r="L38" s="9">
         <f>IF(OR(H38="",K38=""),"",ROUND(H38*VLOOKUP(K38,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
@@ -4910,14 +4905,30 @@
         <f>IF(M38="","",IF(OR(M38="Low",M38="Medium"),"Yes","No"))</f>
         <v/>
       </c>
-      <c r="O38" s="17" t="n"/>
-      <c r="P38" s="7" t="n"/>
-      <c r="Q38" s="17" t="n"/>
+      <c r="O38" s="17" t="inlineStr">
+        <is>
+          <t>Mitigate</t>
+        </is>
+      </c>
+      <c r="P38" s="7" t="inlineStr">
+        <is>
+          <t>Scoped OAuth tokens per action; transaction limits (BHD 500); step-up authentication for changes.</t>
+        </is>
+      </c>
+      <c r="Q38" s="17" t="inlineStr">
+        <is>
+          <t>CISO</t>
+        </is>
+      </c>
       <c r="R38" s="17" t="n"/>
-      <c r="S38" s="17" t="n"/>
+      <c r="S38" s="17" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
       <c r="T38" s="7" t="inlineStr">
         <is>
-          <t>Unscanned model artefacts</t>
+          <t>Agents / integrations with privileged standing access</t>
         </is>
       </c>
       <c r="V38">
@@ -4933,22 +4944,22 @@
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>HUM-01</t>
+          <t>SEC-06</t>
         </is>
       </c>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>Human Oversight &amp; Autonomy</t>
+          <t>Security of AI Systems</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Automation bias and over-reliance</t>
+          <t>Agent memory poisoning &amp; cross-session leakage</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>Users accept AI outputs without adequate scrutiny, eroding professional judgement.</t>
+          <t>Poisoned or unauthorised content persists in agent memory / vector stores, or context leaks across users, sessions or tenants.</t>
         </is>
       </c>
       <c r="F39" s="17" t="inlineStr">
@@ -4958,7 +4969,7 @@
       </c>
       <c r="G39" s="17" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="H39" s="9">
@@ -4971,12 +4982,12 @@
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>RS-1, GL-4, LC-7</t>
+          <t>SE-8</t>
         </is>
       </c>
       <c r="K39" s="17" t="inlineStr">
         <is>
-          <t>Satisfactory</t>
+          <t>Needs improvement</t>
         </is>
       </c>
       <c r="L39" s="9">
@@ -4998,23 +5009,23 @@
       </c>
       <c r="P39" s="7" t="inlineStr">
         <is>
-          <t>Agent-assist mode for complex queries; train contact-centre staff on verification.</t>
+          <t>Isolate conversation memory per customer; TTL 30 days; authorisation check before retrieval.</t>
         </is>
       </c>
       <c r="Q39" s="17" t="inlineStr">
         <is>
-          <t>Head of Contact Centre</t>
+          <t>Head of Digital Engineering</t>
         </is>
       </c>
       <c r="R39" s="17" t="n"/>
       <c r="S39" s="17" t="inlineStr">
         <is>
-          <t>Treatment planned</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="T39" s="7" t="inlineStr">
         <is>
-          <t>Override / challenge rate</t>
+          <t>Cross-tenant retrieval test failures</t>
         </is>
       </c>
       <c r="V39">
@@ -5030,22 +5041,22 @@
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>HUM-02</t>
+          <t>SEC-07</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>Human Oversight &amp; Autonomy</t>
+          <t>Security of AI Systems</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Ineffective human oversight</t>
+          <t>Unsafe code execution, SSRF &amp; sandbox escape</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>Oversight persons lack competence, authority, time or information to intervene.</t>
+          <t>Agent-generated code or tool calls reach internal networks, cloud metadata services or production secrets.</t>
         </is>
       </c>
       <c r="F40" s="17" t="n"/>
@@ -5060,7 +5071,7 @@
       </c>
       <c r="J40" s="7" t="inlineStr">
         <is>
-          <t>RS-1, GL-4</t>
+          <t>SE-9, SE-10</t>
         </is>
       </c>
       <c r="K40" s="17" t="n"/>
@@ -5083,7 +5094,7 @@
       <c r="S40" s="17" t="n"/>
       <c r="T40" s="7" t="inlineStr">
         <is>
-          <t>Oversight roles without training</t>
+          <t>Blocked egress / SSRF attempts</t>
         </is>
       </c>
       <c r="V40">
@@ -5094,39 +5105,31 @@
     <row r="41" ht="44" customHeight="1">
       <c r="A41" s="17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>HUM-03</t>
+          <t>SEC-05</t>
         </is>
       </c>
       <c r="C41" s="14" t="inlineStr">
         <is>
-          <t>Human Oversight &amp; Autonomy</t>
+          <t>Security of AI Systems</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Unbounded autonomous agent actions</t>
+          <t>Compromised AI supply chain</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>AI agents take high-impact actions (payments, communications, code execution) without adequate limits or approval.</t>
-        </is>
-      </c>
-      <c r="F41" s="17" t="inlineStr">
-        <is>
-          <t>Possible</t>
-        </is>
-      </c>
-      <c r="G41" s="17" t="inlineStr">
-        <is>
-          <t>Severe</t>
-        </is>
-      </c>
+          <t>Malicious or vulnerable third-party models, libraries, plugins or MCP servers.</t>
+        </is>
+      </c>
+      <c r="F41" s="17" t="n"/>
+      <c r="G41" s="17" t="n"/>
       <c r="H41" s="9">
         <f>IF(OR($A41&lt;&gt;"Yes",F41="",G41=""),"",MATCH(F41,Lists!$B$1:$B$5,0)*MATCH(G41,Lists!$C$1:$C$5,0))</f>
         <v/>
@@ -5137,14 +5140,10 @@
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
-          <t>LC-8</t>
-        </is>
-      </c>
-      <c r="K41" s="17" t="inlineStr">
-        <is>
-          <t>Needs improvement</t>
-        </is>
-      </c>
+          <t>SE-7</t>
+        </is>
+      </c>
+      <c r="K41" s="17" t="n"/>
       <c r="L41" s="9">
         <f>IF(OR(H41="",K41=""),"",ROUND(H41*VLOOKUP(K41,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
@@ -5157,30 +5156,14 @@
         <f>IF(M41="","",IF(OR(M41="Low",M41="Medium"),"Yes","No"))</f>
         <v/>
       </c>
-      <c r="O41" s="17" t="inlineStr">
-        <is>
-          <t>Mitigate</t>
-        </is>
-      </c>
-      <c r="P41" s="7" t="inlineStr">
-        <is>
-          <t>Human approval for standing-order changes; kill-switch; full action logging.</t>
-        </is>
-      </c>
-      <c r="Q41" s="17" t="inlineStr">
-        <is>
-          <t>Head of Digital Engineering</t>
-        </is>
-      </c>
+      <c r="O41" s="17" t="n"/>
+      <c r="P41" s="7" t="n"/>
+      <c r="Q41" s="17" t="n"/>
       <c r="R41" s="17" t="n"/>
-      <c r="S41" s="17" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
+      <c r="S41" s="17" t="n"/>
       <c r="T41" s="7" t="inlineStr">
         <is>
-          <t>High-impact agent actions without approval</t>
+          <t>Unscanned model artefacts</t>
         </is>
       </c>
       <c r="V41">
@@ -5191,12 +5174,12 @@
     <row r="42" ht="44" customHeight="1">
       <c r="A42" s="17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>HUM-04</t>
+          <t>HUM-01</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
@@ -5206,16 +5189,24 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Adverse workforce impact</t>
+          <t>Automation bias and over-reliance</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>AI adoption causes skills erosion, job anxiety or unconsulted changes to working conditions.</t>
-        </is>
-      </c>
-      <c r="F42" s="17" t="n"/>
-      <c r="G42" s="17" t="n"/>
+          <t>Users accept AI outputs without adequate scrutiny, eroding professional judgement.</t>
+        </is>
+      </c>
+      <c r="F42" s="17" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="G42" s="17" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
       <c r="H42" s="9">
         <f>IF(OR($A42&lt;&gt;"Yes",F42="",G42=""),"",MATCH(F42,Lists!$B$1:$B$5,0)*MATCH(G42,Lists!$C$1:$C$5,0))</f>
         <v/>
@@ -5226,10 +5217,14 @@
       </c>
       <c r="J42" s="7" t="inlineStr">
         <is>
-          <t>RS-9, GL-4</t>
-        </is>
-      </c>
-      <c r="K42" s="17" t="n"/>
+          <t>RS-1, GL-4, LC-7</t>
+        </is>
+      </c>
+      <c r="K42" s="17" t="inlineStr">
+        <is>
+          <t>Satisfactory</t>
+        </is>
+      </c>
       <c r="L42" s="9">
         <f>IF(OR(H42="",K42=""),"",ROUND(H42*VLOOKUP(K42,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
@@ -5242,14 +5237,30 @@
         <f>IF(M42="","",IF(OR(M42="Low",M42="Medium"),"Yes","No"))</f>
         <v/>
       </c>
-      <c r="O42" s="17" t="n"/>
-      <c r="P42" s="7" t="n"/>
-      <c r="Q42" s="17" t="n"/>
+      <c r="O42" s="17" t="inlineStr">
+        <is>
+          <t>Mitigate</t>
+        </is>
+      </c>
+      <c r="P42" s="7" t="inlineStr">
+        <is>
+          <t>Agent-assist mode for complex queries; train contact-centre staff on verification.</t>
+        </is>
+      </c>
+      <c r="Q42" s="17" t="inlineStr">
+        <is>
+          <t>Head of Contact Centre</t>
+        </is>
+      </c>
       <c r="R42" s="17" t="n"/>
-      <c r="S42" s="17" t="n"/>
+      <c r="S42" s="17" t="inlineStr">
+        <is>
+          <t>Treatment planned</t>
+        </is>
+      </c>
       <c r="T42" s="7" t="inlineStr">
         <is>
-          <t>Staff sentiment / attrition in affected roles</t>
+          <t>Override / challenge rate</t>
         </is>
       </c>
       <c r="V42">
@@ -5265,22 +5276,22 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>TPR-01</t>
+          <t>HUM-02</t>
         </is>
       </c>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>Third-Party &amp; Supply Chain</t>
+          <t>Human Oversight &amp; Autonomy</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Vendor lock-in and concentration</t>
+          <t>Ineffective human oversight</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>Critical dependence on a single AI provider or cloud creates resilience and bargaining risk.</t>
+          <t>Oversight persons lack competence, authority, time or information to intervene.</t>
         </is>
       </c>
       <c r="F43" s="17" t="n"/>
@@ -5295,7 +5306,7 @@
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>TP-2, TP-3</t>
+          <t>RS-1, GL-4</t>
         </is>
       </c>
       <c r="K43" s="17" t="n"/>
@@ -5318,7 +5329,7 @@
       <c r="S43" s="17" t="n"/>
       <c r="T43" s="7" t="inlineStr">
         <is>
-          <t>% critical AI workloads on single provider</t>
+          <t>Oversight roles without training</t>
         </is>
       </c>
       <c r="V43">
@@ -5334,22 +5345,22 @@
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>TPR-02</t>
+          <t>HUM-03</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>Third-Party &amp; Supply Chain</t>
+          <t>Human Oversight &amp; Autonomy</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Inadequate vendor transparency and assurance</t>
+          <t>Unbounded autonomous agent actions</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>Vendor cannot provide documentation, testing evidence or incident information needed for compliance.</t>
+          <t>AI agents take high-impact actions (payments, communications, code execution) without adequate limits or approval.</t>
         </is>
       </c>
       <c r="F44" s="17" t="inlineStr">
@@ -5359,7 +5370,7 @@
       </c>
       <c r="G44" s="17" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Severe</t>
         </is>
       </c>
       <c r="H44" s="9">
@@ -5372,12 +5383,12 @@
       </c>
       <c r="J44" s="7" t="inlineStr">
         <is>
-          <t>TP-1, TP-3, LC-6</t>
+          <t>LC-8</t>
         </is>
       </c>
       <c r="K44" s="17" t="inlineStr">
         <is>
-          <t>Satisfactory</t>
+          <t>Needs improvement</t>
         </is>
       </c>
       <c r="L44" s="9">
@@ -5399,23 +5410,23 @@
       </c>
       <c r="P44" s="7" t="inlineStr">
         <is>
-          <t>Obtain model card, SOC 2 and ISO/IEC 42001 evidence; contractual incident notification (24h).</t>
+          <t>Human approval for standing-order changes; kill-switch; full action logging.</t>
         </is>
       </c>
       <c r="Q44" s="17" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Head of Digital Engineering</t>
         </is>
       </c>
       <c r="R44" s="17" t="n"/>
       <c r="S44" s="17" t="inlineStr">
         <is>
-          <t>Treatment planned</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="T44" s="7" t="inlineStr">
         <is>
-          <t>Vendors without current assurance evidence</t>
+          <t>High-impact agent actions without approval</t>
         </is>
       </c>
       <c r="V44">
@@ -5431,22 +5442,22 @@
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>TPR-03</t>
+          <t>HUM-04</t>
         </is>
       </c>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>Third-Party &amp; Supply Chain</t>
+          <t>Human Oversight &amp; Autonomy</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Vendor use of organisation data</t>
+          <t>Adverse workforce impact</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>Provider uses prompts, outputs or client data to train models or retains data beyond agreed terms.</t>
+          <t>AI adoption causes skills erosion, job anxiety or unconsulted changes to working conditions.</t>
         </is>
       </c>
       <c r="F45" s="17" t="n"/>
@@ -5461,7 +5472,7 @@
       </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
-          <t>TP-3, PR-6</t>
+          <t>RS-9, GL-4</t>
         </is>
       </c>
       <c r="K45" s="17" t="n"/>
@@ -5484,7 +5495,7 @@
       <c r="S45" s="17" t="n"/>
       <c r="T45" s="7" t="inlineStr">
         <is>
-          <t>Contracts lacking no-training clause</t>
+          <t>Staff sentiment / attrition in affected roles</t>
         </is>
       </c>
       <c r="V45">
@@ -5495,39 +5506,31 @@
     <row r="46" ht="44" customHeight="1">
       <c r="A46" s="17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>OPS-01</t>
+          <t>TPR-01</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>Operational, Financial &amp; Sustainability</t>
+          <t>Third-Party &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>AI service outage or degradation</t>
+          <t>Vendor lock-in and concentration</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>Business processes dependent on AI are disrupted by service unavailability or latency.</t>
-        </is>
-      </c>
-      <c r="F46" s="17" t="inlineStr">
-        <is>
-          <t>Unlikely</t>
-        </is>
-      </c>
-      <c r="G46" s="17" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
+          <t>Critical dependence on a single AI provider or cloud creates resilience and bargaining risk.</t>
+        </is>
+      </c>
+      <c r="F46" s="17" t="n"/>
+      <c r="G46" s="17" t="n"/>
       <c r="H46" s="9">
         <f>IF(OR($A46&lt;&gt;"Yes",F46="",G46=""),"",MATCH(F46,Lists!$B$1:$B$5,0)*MATCH(G46,Lists!$C$1:$C$5,0))</f>
         <v/>
@@ -5538,14 +5541,10 @@
       </c>
       <c r="J46" s="7" t="inlineStr">
         <is>
-          <t>OM-1, SE-1</t>
-        </is>
-      </c>
-      <c r="K46" s="17" t="inlineStr">
-        <is>
-          <t>Satisfactory</t>
-        </is>
-      </c>
+          <t>TP-2, TP-3</t>
+        </is>
+      </c>
+      <c r="K46" s="17" t="n"/>
       <c r="L46" s="9">
         <f>IF(OR(H46="",K46=""),"",ROUND(H46*VLOOKUP(K46,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
@@ -5558,30 +5557,14 @@
         <f>IF(M46="","",IF(OR(M46="Low",M46="Medium"),"Yes","No"))</f>
         <v/>
       </c>
-      <c r="O46" s="17" t="inlineStr">
-        <is>
-          <t>Mitigate</t>
-        </is>
-      </c>
-      <c r="P46" s="7" t="inlineStr">
-        <is>
-          <t>Fallback to human agents / static FAQ; SLA monitoring.</t>
-        </is>
-      </c>
-      <c r="Q46" s="17" t="inlineStr">
-        <is>
-          <t>IT Operations</t>
-        </is>
-      </c>
+      <c r="O46" s="17" t="n"/>
+      <c r="P46" s="7" t="n"/>
+      <c r="Q46" s="17" t="n"/>
       <c r="R46" s="17" t="n"/>
-      <c r="S46" s="17" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
+      <c r="S46" s="17" t="n"/>
       <c r="T46" s="7" t="inlineStr">
         <is>
-          <t>AI service availability vs SLA</t>
+          <t>% critical AI workloads on single provider</t>
         </is>
       </c>
       <c r="V46">
@@ -5592,31 +5575,39 @@
     <row r="47" ht="44" customHeight="1">
       <c r="A47" s="17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>OPS-02</t>
+          <t>TPR-02</t>
         </is>
       </c>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>Operational, Financial &amp; Sustainability</t>
+          <t>Third-Party &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Uncontrolled AI cost and consumption</t>
+          <t>Inadequate vendor transparency and assurance</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>Compute and API spend escalate without governance (incl. denial-of-wallet attacks).</t>
-        </is>
-      </c>
-      <c r="F47" s="17" t="n"/>
-      <c r="G47" s="17" t="n"/>
+          <t>Vendor cannot provide documentation, testing evidence or incident information needed for compliance.</t>
+        </is>
+      </c>
+      <c r="F47" s="17" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="G47" s="17" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
       <c r="H47" s="9">
         <f>IF(OR($A47&lt;&gt;"Yes",F47="",G47=""),"",MATCH(F47,Lists!$B$1:$B$5,0)*MATCH(G47,Lists!$C$1:$C$5,0))</f>
         <v/>
@@ -5627,10 +5618,14 @@
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
-          <t>GL-6, SE-6</t>
-        </is>
-      </c>
-      <c r="K47" s="17" t="n"/>
+          <t>TP-1, TP-3, LC-6</t>
+        </is>
+      </c>
+      <c r="K47" s="17" t="inlineStr">
+        <is>
+          <t>Satisfactory</t>
+        </is>
+      </c>
       <c r="L47" s="9">
         <f>IF(OR(H47="",K47=""),"",ROUND(H47*VLOOKUP(K47,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
@@ -5643,14 +5638,30 @@
         <f>IF(M47="","",IF(OR(M47="Low",M47="Medium"),"Yes","No"))</f>
         <v/>
       </c>
-      <c r="O47" s="17" t="n"/>
-      <c r="P47" s="7" t="n"/>
-      <c r="Q47" s="17" t="n"/>
+      <c r="O47" s="17" t="inlineStr">
+        <is>
+          <t>Mitigate</t>
+        </is>
+      </c>
+      <c r="P47" s="7" t="inlineStr">
+        <is>
+          <t>Obtain model card, SOC 2 and ISO/IEC 42001 evidence; contractual incident notification (24h).</t>
+        </is>
+      </c>
+      <c r="Q47" s="17" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
       <c r="R47" s="17" t="n"/>
-      <c r="S47" s="17" t="n"/>
+      <c r="S47" s="17" t="inlineStr">
+        <is>
+          <t>Treatment planned</t>
+        </is>
+      </c>
       <c r="T47" s="7" t="inlineStr">
         <is>
-          <t>AI spend vs budget</t>
+          <t>Vendors without current assurance evidence</t>
         </is>
       </c>
       <c r="V47">
@@ -5666,22 +5677,22 @@
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>OPS-03</t>
+          <t>TPR-03</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>Operational, Financial &amp; Sustainability</t>
+          <t>Third-Party &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Environmental impact of AI</t>
+          <t>Vendor use of organisation data</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>Energy, water and carbon footprint of AI workloads conflicts with sustainability commitments.</t>
+          <t>Provider uses prompts, outputs or client data to train models or retains data beyond agreed terms.</t>
         </is>
       </c>
       <c r="F48" s="17" t="n"/>
@@ -5696,7 +5707,7 @@
       </c>
       <c r="J48" s="7" t="inlineStr">
         <is>
-          <t>RS-8</t>
+          <t>TP-3, PR-6</t>
         </is>
       </c>
       <c r="K48" s="17" t="n"/>
@@ -5719,7 +5730,7 @@
       <c r="S48" s="17" t="n"/>
       <c r="T48" s="7" t="inlineStr">
         <is>
-          <t>kgCO2e per 1,000 inferences</t>
+          <t>Contracts lacking no-training clause</t>
         </is>
       </c>
       <c r="V48">
@@ -5730,31 +5741,39 @@
     <row r="49" ht="44" customHeight="1">
       <c r="A49" s="17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>SOC-01</t>
+          <t>OPS-01</t>
         </is>
       </c>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>Societal, Reputational &amp; AI-Enabled Threats</t>
+          <t>Operational, Financial &amp; Sustainability</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Harmful, toxic or unsafe content</t>
+          <t>AI service outage or degradation</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>AI generates offensive, dangerous or culturally inappropriate content.</t>
-        </is>
-      </c>
-      <c r="F49" s="17" t="n"/>
-      <c r="G49" s="17" t="n"/>
+          <t>Business processes dependent on AI are disrupted by service unavailability or latency.</t>
+        </is>
+      </c>
+      <c r="F49" s="17" t="inlineStr">
+        <is>
+          <t>Unlikely</t>
+        </is>
+      </c>
+      <c r="G49" s="17" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
       <c r="H49" s="9">
         <f>IF(OR($A49&lt;&gt;"Yes",F49="",G49=""),"",MATCH(F49,Lists!$B$1:$B$5,0)*MATCH(G49,Lists!$C$1:$C$5,0))</f>
         <v/>
@@ -5765,10 +5784,14 @@
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>RS-2, SE-6</t>
-        </is>
-      </c>
-      <c r="K49" s="17" t="n"/>
+          <t>OM-1, SE-1</t>
+        </is>
+      </c>
+      <c r="K49" s="17" t="inlineStr">
+        <is>
+          <t>Satisfactory</t>
+        </is>
+      </c>
       <c r="L49" s="9">
         <f>IF(OR(H49="",K49=""),"",ROUND(H49*VLOOKUP(K49,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
@@ -5781,14 +5804,30 @@
         <f>IF(M49="","",IF(OR(M49="Low",M49="Medium"),"Yes","No"))</f>
         <v/>
       </c>
-      <c r="O49" s="17" t="n"/>
-      <c r="P49" s="7" t="n"/>
-      <c r="Q49" s="17" t="n"/>
+      <c r="O49" s="17" t="inlineStr">
+        <is>
+          <t>Mitigate</t>
+        </is>
+      </c>
+      <c r="P49" s="7" t="inlineStr">
+        <is>
+          <t>Fallback to human agents / static FAQ; SLA monitoring.</t>
+        </is>
+      </c>
+      <c r="Q49" s="17" t="inlineStr">
+        <is>
+          <t>IT Operations</t>
+        </is>
+      </c>
       <c r="R49" s="17" t="n"/>
-      <c r="S49" s="17" t="n"/>
+      <c r="S49" s="17" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="T49" s="7" t="inlineStr">
         <is>
-          <t>Content-policy violations per 1,000 outputs</t>
+          <t>AI service availability vs SLA</t>
         </is>
       </c>
       <c r="V49">
@@ -5799,39 +5838,31 @@
     <row r="50" ht="44" customHeight="1">
       <c r="A50" s="17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>SOC-02</t>
+          <t>OPS-02</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>Societal, Reputational &amp; AI-Enabled Threats</t>
+          <t>Operational, Financial &amp; Sustainability</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Misinformation and loss of stakeholder trust</t>
+          <t>Uncontrolled AI cost and consumption</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>AI-generated errors or undisclosed AI use damage client, regulator or public trust.</t>
-        </is>
-      </c>
-      <c r="F50" s="17" t="inlineStr">
-        <is>
-          <t>Possible</t>
-        </is>
-      </c>
-      <c r="G50" s="17" t="inlineStr">
-        <is>
-          <t>Major</t>
-        </is>
-      </c>
+          <t>Compute and API spend escalate without governance (incl. denial-of-wallet attacks).</t>
+        </is>
+      </c>
+      <c r="F50" s="17" t="n"/>
+      <c r="G50" s="17" t="n"/>
       <c r="H50" s="9">
         <f>IF(OR($A50&lt;&gt;"Yes",F50="",G50=""),"",MATCH(F50,Lists!$B$1:$B$5,0)*MATCH(G50,Lists!$C$1:$C$5,0))</f>
         <v/>
@@ -5842,14 +5873,10 @@
       </c>
       <c r="J50" s="7" t="inlineStr">
         <is>
-          <t>LC-7, CO-1, CO-2</t>
-        </is>
-      </c>
-      <c r="K50" s="17" t="inlineStr">
-        <is>
-          <t>Satisfactory</t>
-        </is>
-      </c>
+          <t>GL-6, SE-6</t>
+        </is>
+      </c>
+      <c r="K50" s="17" t="n"/>
       <c r="L50" s="9">
         <f>IF(OR(H50="",K50=""),"",ROUND(H50*VLOOKUP(K50,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
@@ -5862,30 +5889,14 @@
         <f>IF(M50="","",IF(OR(M50="Low",M50="Medium"),"Yes","No"))</f>
         <v/>
       </c>
-      <c r="O50" s="17" t="inlineStr">
-        <is>
-          <t>Mitigate</t>
-        </is>
-      </c>
-      <c r="P50" s="7" t="inlineStr">
-        <is>
-          <t>Complaint tagging for AI interactions; monthly review by Conduct Risk.</t>
-        </is>
-      </c>
-      <c r="Q50" s="17" t="inlineStr">
-        <is>
-          <t>Conduct Risk</t>
-        </is>
-      </c>
+      <c r="O50" s="17" t="n"/>
+      <c r="P50" s="7" t="n"/>
+      <c r="Q50" s="17" t="n"/>
       <c r="R50" s="17" t="n"/>
-      <c r="S50" s="17" t="inlineStr">
-        <is>
-          <t>Treatment planned</t>
-        </is>
-      </c>
+      <c r="S50" s="17" t="n"/>
       <c r="T50" s="7" t="inlineStr">
         <is>
-          <t>Client complaints linked to AI</t>
+          <t>AI spend vs budget</t>
         </is>
       </c>
       <c r="V50">
@@ -5901,27 +5912,27 @@
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>SOC-03</t>
+          <t>OPS-04</t>
         </is>
       </c>
       <c r="C51" s="14" t="inlineStr">
         <is>
-          <t>Societal, Reputational &amp; AI-Enabled Threats</t>
+          <t>Operational, Financial &amp; Sustainability</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Deepfake and AI-enabled fraud against the organisation</t>
+          <t>No safe degradation or kill switch</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>Voice/video impersonation or AI-crafted phishing leads to fraudulent payments or data release.</t>
+          <t>A failing or compromised AI system cannot be stopped quickly or the business process cannot revert to manual operation.</t>
         </is>
       </c>
       <c r="F51" s="17" t="inlineStr">
         <is>
-          <t>Possible</t>
+          <t>Unlikely</t>
         </is>
       </c>
       <c r="G51" s="17" t="inlineStr">
@@ -5939,7 +5950,7 @@
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>AT-3, GL-4</t>
+          <t>OM-4</t>
         </is>
       </c>
       <c r="K51" s="17" t="inlineStr">
@@ -5966,23 +5977,23 @@
       </c>
       <c r="P51" s="7" t="inlineStr">
         <is>
-          <t>Out-of-band verification for high-risk requests; voice-channel deepfake awareness.</t>
+          <t>Global and per-action kill switch; fallback to human agents; semi-annual test.</t>
         </is>
       </c>
       <c r="Q51" s="17" t="inlineStr">
         <is>
-          <t>Fraud Risk</t>
+          <t>IT Operations</t>
         </is>
       </c>
       <c r="R51" s="17" t="n"/>
       <c r="S51" s="17" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Treatment planned</t>
         </is>
       </c>
       <c r="T51" s="7" t="inlineStr">
         <is>
-          <t>Deepfake / BEC attempts detected</t>
+          <t>Kill-switch test age (days)</t>
         </is>
       </c>
       <c r="V51">
@@ -5998,22 +6009,22 @@
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>SOC-04</t>
+          <t>OPS-03</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>Societal, Reputational &amp; AI-Enabled Threats</t>
+          <t>Operational, Financial &amp; Sustainability</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>AI-accelerated cyber attacks</t>
+          <t>Environmental impact of AI</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>Adversaries use AI for automated discovery, exploit chaining and scaled social engineering, outpacing defences.</t>
+          <t>Energy, water and carbon footprint of AI workloads conflicts with sustainability commitments.</t>
         </is>
       </c>
       <c r="F52" s="17" t="n"/>
@@ -6028,7 +6039,7 @@
       </c>
       <c r="J52" s="7" t="inlineStr">
         <is>
-          <t>AT-1, AT-2, AT-4</t>
+          <t>RS-8</t>
         </is>
       </c>
       <c r="K52" s="17" t="n"/>
@@ -6051,7 +6062,7 @@
       <c r="S52" s="17" t="n"/>
       <c r="T52" s="7" t="inlineStr">
         <is>
-          <t>Mean time to remediate critical vulnerabilities</t>
+          <t>kgCO2e per 1,000 inferences</t>
         </is>
       </c>
       <c r="V52">
@@ -6060,15 +6071,31 @@
       </c>
     </row>
     <row r="53" ht="44" customHeight="1">
-      <c r="A53" s="17" t="n"/>
+      <c r="A53" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>BSP-01</t>
-        </is>
-      </c>
-      <c r="C53" s="14" t="n"/>
-      <c r="D53" s="4" t="n"/>
-      <c r="E53" s="7" t="n"/>
+          <t>SOC-01</t>
+        </is>
+      </c>
+      <c r="C53" s="14" t="inlineStr">
+        <is>
+          <t>Societal, Reputational &amp; AI-Enabled Threats</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>Harmful, toxic or unsafe content</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>AI generates offensive, dangerous or culturally inappropriate content.</t>
+        </is>
+      </c>
       <c r="F53" s="17" t="n"/>
       <c r="G53" s="17" t="n"/>
       <c r="H53" s="9">
@@ -6079,7 +6106,11 @@
         <f>IF(H53="","",IF(H53&gt;=17,"Critical",IF(H53&gt;=10,"High",IF(H53&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="J53" s="7" t="n"/>
+      <c r="J53" s="7" t="inlineStr">
+        <is>
+          <t>RS-2, SE-6</t>
+        </is>
+      </c>
       <c r="K53" s="17" t="n"/>
       <c r="L53" s="9">
         <f>IF(OR(H53="",K53=""),"",ROUND(H53*VLOOKUP(K53,Scales!$A$22:$B$25,2,FALSE),1))</f>
@@ -6098,24 +6129,52 @@
       <c r="Q53" s="17" t="n"/>
       <c r="R53" s="17" t="n"/>
       <c r="S53" s="17" t="n"/>
-      <c r="T53" s="7" t="n"/>
+      <c r="T53" s="7" t="inlineStr">
+        <is>
+          <t>Content-policy violations per 1,000 outputs</t>
+        </is>
+      </c>
       <c r="V53">
         <f>IF(L53="","",L53+ROW()/100000)</f>
         <v/>
       </c>
     </row>
     <row r="54" ht="44" customHeight="1">
-      <c r="A54" s="17" t="n"/>
+      <c r="A54" s="17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>BSP-02</t>
-        </is>
-      </c>
-      <c r="C54" s="14" t="n"/>
-      <c r="D54" s="4" t="n"/>
-      <c r="E54" s="7" t="n"/>
-      <c r="F54" s="17" t="n"/>
-      <c r="G54" s="17" t="n"/>
+          <t>SOC-02</t>
+        </is>
+      </c>
+      <c r="C54" s="14" t="inlineStr">
+        <is>
+          <t>Societal, Reputational &amp; AI-Enabled Threats</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>Misinformation and loss of stakeholder trust</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>AI-generated errors or undisclosed AI use damage client, regulator or public trust.</t>
+        </is>
+      </c>
+      <c r="F54" s="17" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="G54" s="17" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
       <c r="H54" s="9">
         <f>IF(OR($A54&lt;&gt;"Yes",F54="",G54=""),"",MATCH(F54,Lists!$B$1:$B$5,0)*MATCH(G54,Lists!$C$1:$C$5,0))</f>
         <v/>
@@ -6124,8 +6183,16 @@
         <f>IF(H54="","",IF(H54&gt;=17,"Critical",IF(H54&gt;=10,"High",IF(H54&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="J54" s="7" t="n"/>
-      <c r="K54" s="17" t="n"/>
+      <c r="J54" s="7" t="inlineStr">
+        <is>
+          <t>LC-7, CO-1, CO-2</t>
+        </is>
+      </c>
+      <c r="K54" s="17" t="inlineStr">
+        <is>
+          <t>Satisfactory</t>
+        </is>
+      </c>
       <c r="L54" s="9">
         <f>IF(OR(H54="",K54=""),"",ROUND(H54*VLOOKUP(K54,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
@@ -6138,29 +6205,73 @@
         <f>IF(M54="","",IF(OR(M54="Low",M54="Medium"),"Yes","No"))</f>
         <v/>
       </c>
-      <c r="O54" s="17" t="n"/>
-      <c r="P54" s="7" t="n"/>
-      <c r="Q54" s="17" t="n"/>
+      <c r="O54" s="17" t="inlineStr">
+        <is>
+          <t>Mitigate</t>
+        </is>
+      </c>
+      <c r="P54" s="7" t="inlineStr">
+        <is>
+          <t>Complaint tagging for AI interactions; monthly review by Conduct Risk.</t>
+        </is>
+      </c>
+      <c r="Q54" s="17" t="inlineStr">
+        <is>
+          <t>Conduct Risk</t>
+        </is>
+      </c>
       <c r="R54" s="17" t="n"/>
-      <c r="S54" s="17" t="n"/>
-      <c r="T54" s="7" t="n"/>
+      <c r="S54" s="17" t="inlineStr">
+        <is>
+          <t>Treatment planned</t>
+        </is>
+      </c>
+      <c r="T54" s="7" t="inlineStr">
+        <is>
+          <t>Client complaints linked to AI</t>
+        </is>
+      </c>
       <c r="V54">
         <f>IF(L54="","",L54+ROW()/100000)</f>
         <v/>
       </c>
     </row>
     <row r="55" ht="44" customHeight="1">
-      <c r="A55" s="17" t="n"/>
+      <c r="A55" s="17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>BSP-03</t>
-        </is>
-      </c>
-      <c r="C55" s="14" t="n"/>
-      <c r="D55" s="4" t="n"/>
-      <c r="E55" s="7" t="n"/>
-      <c r="F55" s="17" t="n"/>
-      <c r="G55" s="17" t="n"/>
+          <t>SOC-03</t>
+        </is>
+      </c>
+      <c r="C55" s="14" t="inlineStr">
+        <is>
+          <t>Societal, Reputational &amp; AI-Enabled Threats</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>Deepfake and AI-enabled fraud against the organisation</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>Voice/video impersonation or AI-crafted phishing leads to fraudulent payments or data release.</t>
+        </is>
+      </c>
+      <c r="F55" s="17" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="G55" s="17" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
       <c r="H55" s="9">
         <f>IF(OR($A55&lt;&gt;"Yes",F55="",G55=""),"",MATCH(F55,Lists!$B$1:$B$5,0)*MATCH(G55,Lists!$C$1:$C$5,0))</f>
         <v/>
@@ -6169,8 +6280,16 @@
         <f>IF(H55="","",IF(H55&gt;=17,"Critical",IF(H55&gt;=10,"High",IF(H55&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="J55" s="7" t="n"/>
-      <c r="K55" s="17" t="n"/>
+      <c r="J55" s="7" t="inlineStr">
+        <is>
+          <t>AT-3, GL-4</t>
+        </is>
+      </c>
+      <c r="K55" s="17" t="inlineStr">
+        <is>
+          <t>Satisfactory</t>
+        </is>
+      </c>
       <c r="L55" s="9">
         <f>IF(OR(H55="",K55=""),"",ROUND(H55*VLOOKUP(K55,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
@@ -6183,27 +6302,63 @@
         <f>IF(M55="","",IF(OR(M55="Low",M55="Medium"),"Yes","No"))</f>
         <v/>
       </c>
-      <c r="O55" s="17" t="n"/>
-      <c r="P55" s="7" t="n"/>
-      <c r="Q55" s="17" t="n"/>
+      <c r="O55" s="17" t="inlineStr">
+        <is>
+          <t>Mitigate</t>
+        </is>
+      </c>
+      <c r="P55" s="7" t="inlineStr">
+        <is>
+          <t>Out-of-band verification for high-risk requests; voice-channel deepfake awareness.</t>
+        </is>
+      </c>
+      <c r="Q55" s="17" t="inlineStr">
+        <is>
+          <t>Fraud Risk</t>
+        </is>
+      </c>
       <c r="R55" s="17" t="n"/>
-      <c r="S55" s="17" t="n"/>
-      <c r="T55" s="7" t="n"/>
+      <c r="S55" s="17" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="T55" s="7" t="inlineStr">
+        <is>
+          <t>Deepfake / BEC attempts detected</t>
+        </is>
+      </c>
       <c r="V55">
         <f>IF(L55="","",L55+ROW()/100000)</f>
         <v/>
       </c>
     </row>
     <row r="56" ht="44" customHeight="1">
-      <c r="A56" s="17" t="n"/>
+      <c r="A56" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>BSP-04</t>
-        </is>
-      </c>
-      <c r="C56" s="14" t="n"/>
-      <c r="D56" s="4" t="n"/>
-      <c r="E56" s="7" t="n"/>
+          <t>SOC-04</t>
+        </is>
+      </c>
+      <c r="C56" s="14" t="inlineStr">
+        <is>
+          <t>Societal, Reputational &amp; AI-Enabled Threats</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>AI-accelerated cyber attacks</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>Adversaries use AI for automated discovery, exploit chaining and scaled social engineering, outpacing defences.</t>
+        </is>
+      </c>
       <c r="F56" s="17" t="n"/>
       <c r="G56" s="17" t="n"/>
       <c r="H56" s="9">
@@ -6214,7 +6369,11 @@
         <f>IF(H56="","",IF(H56&gt;=17,"Critical",IF(H56&gt;=10,"High",IF(H56&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="J56" s="7" t="n"/>
+      <c r="J56" s="7" t="inlineStr">
+        <is>
+          <t>AT-1, AT-2, AT-4</t>
+        </is>
+      </c>
       <c r="K56" s="17" t="n"/>
       <c r="L56" s="9">
         <f>IF(OR(H56="",K56=""),"",ROUND(H56*VLOOKUP(K56,Scales!$A$22:$B$25,2,FALSE),1))</f>
@@ -6233,7 +6392,11 @@
       <c r="Q56" s="17" t="n"/>
       <c r="R56" s="17" t="n"/>
       <c r="S56" s="17" t="n"/>
-      <c r="T56" s="7" t="n"/>
+      <c r="T56" s="7" t="inlineStr">
+        <is>
+          <t>Mean time to remediate critical vulnerabilities</t>
+        </is>
+      </c>
       <c r="V56">
         <f>IF(L56="","",L56+ROW()/100000)</f>
         <v/>
@@ -6243,7 +6406,7 @@
       <c r="A57" s="17" t="n"/>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>BSP-05</t>
+          <t>BSP-01</t>
         </is>
       </c>
       <c r="C57" s="14" t="n"/>
@@ -6288,7 +6451,7 @@
       <c r="A58" s="17" t="n"/>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>BSP-06</t>
+          <t>BSP-02</t>
         </is>
       </c>
       <c r="C58" s="14" t="n"/>
@@ -6333,7 +6496,7 @@
       <c r="A59" s="17" t="n"/>
       <c r="B59" s="14" t="inlineStr">
         <is>
-          <t>BSP-07</t>
+          <t>BSP-03</t>
         </is>
       </c>
       <c r="C59" s="14" t="n"/>
@@ -6378,7 +6541,7 @@
       <c r="A60" s="17" t="n"/>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>BSP-08</t>
+          <t>BSP-04</t>
         </is>
       </c>
       <c r="C60" s="14" t="n"/>
@@ -6423,7 +6586,7 @@
       <c r="A61" s="17" t="n"/>
       <c r="B61" s="14" t="inlineStr">
         <is>
-          <t>BSP-09</t>
+          <t>BSP-05</t>
         </is>
       </c>
       <c r="C61" s="14" t="n"/>
@@ -6468,7 +6631,7 @@
       <c r="A62" s="17" t="n"/>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>BSP-10</t>
+          <t>BSP-06</t>
         </is>
       </c>
       <c r="C62" s="14" t="n"/>
@@ -6509,13 +6672,193 @@
         <v/>
       </c>
     </row>
+    <row r="63" ht="44" customHeight="1">
+      <c r="A63" s="17" t="n"/>
+      <c r="B63" s="14" t="inlineStr">
+        <is>
+          <t>BSP-07</t>
+        </is>
+      </c>
+      <c r="C63" s="14" t="n"/>
+      <c r="D63" s="4" t="n"/>
+      <c r="E63" s="7" t="n"/>
+      <c r="F63" s="17" t="n"/>
+      <c r="G63" s="17" t="n"/>
+      <c r="H63" s="9">
+        <f>IF(OR($A63&lt;&gt;"Yes",F63="",G63=""),"",MATCH(F63,Lists!$B$1:$B$5,0)*MATCH(G63,Lists!$C$1:$C$5,0))</f>
+        <v/>
+      </c>
+      <c r="I63" s="9">
+        <f>IF(H63="","",IF(H63&gt;=17,"Critical",IF(H63&gt;=10,"High",IF(H63&gt;=5,"Medium","Low"))))</f>
+        <v/>
+      </c>
+      <c r="J63" s="7" t="n"/>
+      <c r="K63" s="17" t="n"/>
+      <c r="L63" s="9">
+        <f>IF(OR(H63="",K63=""),"",ROUND(H63*VLOOKUP(K63,Scales!$A$22:$B$25,2,FALSE),1))</f>
+        <v/>
+      </c>
+      <c r="M63" s="9">
+        <f>IF(L63="","",IF(L63&gt;=17,"Critical",IF(L63&gt;=10,"High",IF(L63&gt;=5,"Medium","Low"))))</f>
+        <v/>
+      </c>
+      <c r="N63" s="9">
+        <f>IF(M63="","",IF(OR(M63="Low",M63="Medium"),"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="O63" s="17" t="n"/>
+      <c r="P63" s="7" t="n"/>
+      <c r="Q63" s="17" t="n"/>
+      <c r="R63" s="17" t="n"/>
+      <c r="S63" s="17" t="n"/>
+      <c r="T63" s="7" t="n"/>
+      <c r="V63">
+        <f>IF(L63="","",L63+ROW()/100000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64" ht="44" customHeight="1">
+      <c r="A64" s="17" t="n"/>
+      <c r="B64" s="14" t="inlineStr">
+        <is>
+          <t>BSP-08</t>
+        </is>
+      </c>
+      <c r="C64" s="14" t="n"/>
+      <c r="D64" s="4" t="n"/>
+      <c r="E64" s="7" t="n"/>
+      <c r="F64" s="17" t="n"/>
+      <c r="G64" s="17" t="n"/>
+      <c r="H64" s="9">
+        <f>IF(OR($A64&lt;&gt;"Yes",F64="",G64=""),"",MATCH(F64,Lists!$B$1:$B$5,0)*MATCH(G64,Lists!$C$1:$C$5,0))</f>
+        <v/>
+      </c>
+      <c r="I64" s="9">
+        <f>IF(H64="","",IF(H64&gt;=17,"Critical",IF(H64&gt;=10,"High",IF(H64&gt;=5,"Medium","Low"))))</f>
+        <v/>
+      </c>
+      <c r="J64" s="7" t="n"/>
+      <c r="K64" s="17" t="n"/>
+      <c r="L64" s="9">
+        <f>IF(OR(H64="",K64=""),"",ROUND(H64*VLOOKUP(K64,Scales!$A$22:$B$25,2,FALSE),1))</f>
+        <v/>
+      </c>
+      <c r="M64" s="9">
+        <f>IF(L64="","",IF(L64&gt;=17,"Critical",IF(L64&gt;=10,"High",IF(L64&gt;=5,"Medium","Low"))))</f>
+        <v/>
+      </c>
+      <c r="N64" s="9">
+        <f>IF(M64="","",IF(OR(M64="Low",M64="Medium"),"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="O64" s="17" t="n"/>
+      <c r="P64" s="7" t="n"/>
+      <c r="Q64" s="17" t="n"/>
+      <c r="R64" s="17" t="n"/>
+      <c r="S64" s="17" t="n"/>
+      <c r="T64" s="7" t="n"/>
+      <c r="V64">
+        <f>IF(L64="","",L64+ROW()/100000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65" ht="44" customHeight="1">
+      <c r="A65" s="17" t="n"/>
+      <c r="B65" s="14" t="inlineStr">
+        <is>
+          <t>BSP-09</t>
+        </is>
+      </c>
+      <c r="C65" s="14" t="n"/>
+      <c r="D65" s="4" t="n"/>
+      <c r="E65" s="7" t="n"/>
+      <c r="F65" s="17" t="n"/>
+      <c r="G65" s="17" t="n"/>
+      <c r="H65" s="9">
+        <f>IF(OR($A65&lt;&gt;"Yes",F65="",G65=""),"",MATCH(F65,Lists!$B$1:$B$5,0)*MATCH(G65,Lists!$C$1:$C$5,0))</f>
+        <v/>
+      </c>
+      <c r="I65" s="9">
+        <f>IF(H65="","",IF(H65&gt;=17,"Critical",IF(H65&gt;=10,"High",IF(H65&gt;=5,"Medium","Low"))))</f>
+        <v/>
+      </c>
+      <c r="J65" s="7" t="n"/>
+      <c r="K65" s="17" t="n"/>
+      <c r="L65" s="9">
+        <f>IF(OR(H65="",K65=""),"",ROUND(H65*VLOOKUP(K65,Scales!$A$22:$B$25,2,FALSE),1))</f>
+        <v/>
+      </c>
+      <c r="M65" s="9">
+        <f>IF(L65="","",IF(L65&gt;=17,"Critical",IF(L65&gt;=10,"High",IF(L65&gt;=5,"Medium","Low"))))</f>
+        <v/>
+      </c>
+      <c r="N65" s="9">
+        <f>IF(M65="","",IF(OR(M65="Low",M65="Medium"),"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="O65" s="17" t="n"/>
+      <c r="P65" s="7" t="n"/>
+      <c r="Q65" s="17" t="n"/>
+      <c r="R65" s="17" t="n"/>
+      <c r="S65" s="17" t="n"/>
+      <c r="T65" s="7" t="n"/>
+      <c r="V65">
+        <f>IF(L65="","",L65+ROW()/100000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" ht="44" customHeight="1">
+      <c r="A66" s="17" t="n"/>
+      <c r="B66" s="14" t="inlineStr">
+        <is>
+          <t>BSP-10</t>
+        </is>
+      </c>
+      <c r="C66" s="14" t="n"/>
+      <c r="D66" s="4" t="n"/>
+      <c r="E66" s="7" t="n"/>
+      <c r="F66" s="17" t="n"/>
+      <c r="G66" s="17" t="n"/>
+      <c r="H66" s="9">
+        <f>IF(OR($A66&lt;&gt;"Yes",F66="",G66=""),"",MATCH(F66,Lists!$B$1:$B$5,0)*MATCH(G66,Lists!$C$1:$C$5,0))</f>
+        <v/>
+      </c>
+      <c r="I66" s="9">
+        <f>IF(H66="","",IF(H66&gt;=17,"Critical",IF(H66&gt;=10,"High",IF(H66&gt;=5,"Medium","Low"))))</f>
+        <v/>
+      </c>
+      <c r="J66" s="7" t="n"/>
+      <c r="K66" s="17" t="n"/>
+      <c r="L66" s="9">
+        <f>IF(OR(H66="",K66=""),"",ROUND(H66*VLOOKUP(K66,Scales!$A$22:$B$25,2,FALSE),1))</f>
+        <v/>
+      </c>
+      <c r="M66" s="9">
+        <f>IF(L66="","",IF(L66&gt;=17,"Critical",IF(L66&gt;=10,"High",IF(L66&gt;=5,"Medium","Low"))))</f>
+        <v/>
+      </c>
+      <c r="N66" s="9">
+        <f>IF(M66="","",IF(OR(M66="Low",M66="Medium"),"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="O66" s="17" t="n"/>
+      <c r="P66" s="7" t="n"/>
+      <c r="Q66" s="17" t="n"/>
+      <c r="R66" s="17" t="n"/>
+      <c r="S66" s="17" t="n"/>
+      <c r="T66" s="7" t="n"/>
+      <c r="V66">
+        <f>IF(L66="","",L66+ROW()/100000)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:T62"/>
+  <autoFilter ref="A4:T66"/>
   <mergeCells count="2">
     <mergeCell ref="A1:T1"/>
     <mergeCell ref="A2:T2"/>
   </mergeCells>
-  <conditionalFormatting sqref="I5:I62">
+  <conditionalFormatting sqref="I5:I66">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="2">
       <formula>"Low"</formula>
     </cfRule>
@@ -6532,7 +6875,7 @@
       <formula>"Prohibited"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M5:M62">
+  <conditionalFormatting sqref="M5:M66">
     <cfRule type="cellIs" priority="6" operator="equal" dxfId="2">
       <formula>"Low"</formula>
     </cfRule>
@@ -6549,38 +6892,39 @@
       <formula>"Prohibited"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N5:N62">
+  <conditionalFormatting sqref="N5:N66">
     <cfRule type="cellIs" priority="11" operator="equal" dxfId="6">
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:T62">
+  <conditionalFormatting sqref="A5:T66">
     <cfRule type="expression" priority="12" dxfId="7">
       <formula>$A5="No"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
-    <dataValidation sqref="A5:A62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5:A66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Lists!$A$1:$A$2</formula1>
     </dataValidation>
-    <dataValidation sqref="F5:F62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:F66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Lists!$B$1:$B$5</formula1>
     </dataValidation>
-    <dataValidation sqref="G5:G62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Lists!$C$1:$C$5</formula1>
     </dataValidation>
-    <dataValidation sqref="K5:K62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K5:K66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Lists!$D$1:$D$4</formula1>
     </dataValidation>
-    <dataValidation sqref="O5:O62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O5:O66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Lists!$E$1:$E$4</formula1>
     </dataValidation>
-    <dataValidation sqref="S5:S62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="S5:S66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Lists!$F$1:$F$5</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <printOptions gridLines="0"/>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.25" footer="0.25"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -6684,23 +7028,23 @@
         </is>
       </c>
       <c r="B6" s="20">
-        <f>COUNTIFS('4. Risk Register'!$A$5:$A$62,"Yes",'4. Risk Register'!$F$5:$F$62,"Almost certain",'4. Risk Register'!$G$5:$G$62,"Insignificant")</f>
+        <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Almost certain",'4. Risk Register'!$G$5:$G$66,"Insignificant")</f>
         <v/>
       </c>
       <c r="C6" s="21">
-        <f>COUNTIFS('4. Risk Register'!$A$5:$A$62,"Yes",'4. Risk Register'!$F$5:$F$62,"Almost certain",'4. Risk Register'!$G$5:$G$62,"Minor")</f>
+        <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Almost certain",'4. Risk Register'!$G$5:$G$66,"Minor")</f>
         <v/>
       </c>
       <c r="D6" s="21">
-        <f>COUNTIFS('4. Risk Register'!$A$5:$A$62,"Yes",'4. Risk Register'!$F$5:$F$62,"Almost certain",'4. Risk Register'!$G$5:$G$62,"Moderate")</f>
+        <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Almost certain",'4. Risk Register'!$G$5:$G$66,"Moderate")</f>
         <v/>
       </c>
       <c r="E6" s="22">
-        <f>COUNTIFS('4. Risk Register'!$A$5:$A$62,"Yes",'4. Risk Register'!$F$5:$F$62,"Almost certain",'4. Risk Register'!$G$5:$G$62,"Major")</f>
+        <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Almost certain",'4. Risk Register'!$G$5:$G$66,"Major")</f>
         <v/>
       </c>
       <c r="F6" s="22">
-        <f>COUNTIFS('4. Risk Register'!$A$5:$A$62,"Yes",'4. Risk Register'!$F$5:$F$62,"Almost certain",'4. Risk Register'!$G$5:$G$62,"Severe")</f>
+        <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Almost certain",'4. Risk Register'!$G$5:$G$66,"Severe")</f>
         <v/>
       </c>
       <c r="H6" s="23" t="inlineStr">
@@ -6709,11 +7053,11 @@
         </is>
       </c>
       <c r="I6" s="9">
-        <f>COUNTIF('4. Risk Register'!$I$5:$I$62,"Critical")</f>
+        <f>COUNTIF('4. Risk Register'!$I$5:$I$66,"Critical")</f>
         <v/>
       </c>
       <c r="J6" s="9">
-        <f>COUNTIF('4. Risk Register'!$M$5:$M$62,"Critical")</f>
+        <f>COUNTIF('4. Risk Register'!$M$5:$M$66,"Critical")</f>
         <v/>
       </c>
     </row>
@@ -6724,23 +7068,23 @@
         </is>
       </c>
       <c r="B7" s="24">
-        <f>COUNTIFS('4. Risk Register'!$A$5:$A$62,"Yes",'4. Risk Register'!$F$5:$F$62,"Likely",'4. Risk Register'!$G$5:$G$62,"Insignificant")</f>
+        <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Likely",'4. Risk Register'!$G$5:$G$66,"Insignificant")</f>
         <v/>
       </c>
       <c r="C7" s="20">
-        <f>COUNTIFS('4. Risk Register'!$A$5:$A$62,"Yes",'4. Risk Register'!$F$5:$F$62,"Likely",'4. Risk Register'!$G$5:$G$62,"Minor")</f>
+        <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Likely",'4. Risk Register'!$G$5:$G$66,"Minor")</f>
         <v/>
       </c>
       <c r="D7" s="21">
-        <f>COUNTIFS('4. Risk Register'!$A$5:$A$62,"Yes",'4. Risk Register'!$F$5:$F$62,"Likely",'4. Risk Register'!$G$5:$G$62,"Moderate")</f>
+        <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Likely",'4. Risk Register'!$G$5:$G$66,"Moderate")</f>
         <v/>
       </c>
       <c r="E7" s="21">
-        <f>COUNTIFS('4. Risk Register'!$A$5:$A$62,"Yes",'4. Risk Register'!$F$5:$F$62,"Likely",'4. Risk Register'!$G$5:$G$62,"Major")</f>
+        <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Likely",'4. Risk Register'!$G$5:$G$66,"Major")</f>
         <v/>
       </c>
       <c r="F7" s="22">
-        <f>COUNTIFS('4. Risk Register'!$A$5:$A$62,"Yes",'4. Risk Register'!$F$5:$F$62,"Likely",'4. Risk Register'!$G$5:$G$62,"Severe")</f>
+        <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Likely",'4. Risk Register'!$G$5:$G$66,"Severe")</f>
         <v/>
       </c>
       <c r="H7" s="25" t="inlineStr">
@@ -6749,11 +7093,11 @@
         </is>
       </c>
       <c r="I7" s="9">
-        <f>COUNTIF('4. Risk Register'!$I$5:$I$62,"High")</f>
+        <f>COUNTIF('4. Risk Register'!$I$5:$I$66,"High")</f>
         <v/>
       </c>
       <c r="J7" s="9">
-        <f>COUNTIF('4. Risk Register'!$M$5:$M$62,"High")</f>
+        <f>COUNTIF('4. Risk Register'!$M$5:$M$66,"High")</f>
         <v/>
       </c>
     </row>
@@ -6764,23 +7108,23 @@
         </is>
       </c>
       <c r="B8" s="24">
-        <f>COUNTIFS('4. Risk Register'!$A$5:$A$62,"Yes",'4. Risk Register'!$F$5:$F$62,"Possible",'4. Risk Register'!$G$5:$G$62,"Insignificant")</f>
+        <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Possible",'4. Risk Register'!$G$5:$G$66,"Insignificant")</f>
         <v/>
       </c>
       <c r="C8" s="20">
-        <f>COUNTIFS('4. Risk Register'!$A$5:$A$62,"Yes",'4. Risk Register'!$F$5:$F$62,"Possible",'4. Risk Register'!$G$5:$G$62,"Minor")</f>
+        <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Possible",'4. Risk Register'!$G$5:$G$66,"Minor")</f>
         <v/>
       </c>
       <c r="D8" s="20">
-        <f>COUNTIFS('4. Risk Register'!$A$5:$A$62,"Yes",'4. Risk Register'!$F$5:$F$62,"Possible",'4. Risk Register'!$G$5:$G$62,"Moderate")</f>
+        <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Possible",'4. Risk Register'!$G$5:$G$66,"Moderate")</f>
         <v/>
       </c>
       <c r="E8" s="21">
-        <f>COUNTIFS('4. Risk Register'!$A$5:$A$62,"Yes",'4. Risk Register'!$F$5:$F$62,"Possible",'4. Risk Register'!$G$5:$G$62,"Major")</f>
+        <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Possible",'4. Risk Register'!$G$5:$G$66,"Major")</f>
         <v/>
       </c>
       <c r="F8" s="21">
-        <f>COUNTIFS('4. Risk Register'!$A$5:$A$62,"Yes",'4. Risk Register'!$F$5:$F$62,"Possible",'4. Risk Register'!$G$5:$G$62,"Severe")</f>
+        <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Possible",'4. Risk Register'!$G$5:$G$66,"Severe")</f>
         <v/>
       </c>
       <c r="H8" s="26" t="inlineStr">
@@ -6789,11 +7133,11 @@
         </is>
       </c>
       <c r="I8" s="9">
-        <f>COUNTIF('4. Risk Register'!$I$5:$I$62,"Medium")</f>
+        <f>COUNTIF('4. Risk Register'!$I$5:$I$66,"Medium")</f>
         <v/>
       </c>
       <c r="J8" s="9">
-        <f>COUNTIF('4. Risk Register'!$M$5:$M$62,"Medium")</f>
+        <f>COUNTIF('4. Risk Register'!$M$5:$M$66,"Medium")</f>
         <v/>
       </c>
     </row>
@@ -6804,23 +7148,23 @@
         </is>
       </c>
       <c r="B9" s="24">
-        <f>COUNTIFS('4. Risk Register'!$A$5:$A$62,"Yes",'4. Risk Register'!$F$5:$F$62,"Unlikely",'4. Risk Register'!$G$5:$G$62,"Insignificant")</f>
+        <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Unlikely",'4. Risk Register'!$G$5:$G$66,"Insignificant")</f>
         <v/>
       </c>
       <c r="C9" s="24">
-        <f>COUNTIFS('4. Risk Register'!$A$5:$A$62,"Yes",'4. Risk Register'!$F$5:$F$62,"Unlikely",'4. Risk Register'!$G$5:$G$62,"Minor")</f>
+        <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Unlikely",'4. Risk Register'!$G$5:$G$66,"Minor")</f>
         <v/>
       </c>
       <c r="D9" s="20">
-        <f>COUNTIFS('4. Risk Register'!$A$5:$A$62,"Yes",'4. Risk Register'!$F$5:$F$62,"Unlikely",'4. Risk Register'!$G$5:$G$62,"Moderate")</f>
+        <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Unlikely",'4. Risk Register'!$G$5:$G$66,"Moderate")</f>
         <v/>
       </c>
       <c r="E9" s="20">
-        <f>COUNTIFS('4. Risk Register'!$A$5:$A$62,"Yes",'4. Risk Register'!$F$5:$F$62,"Unlikely",'4. Risk Register'!$G$5:$G$62,"Major")</f>
+        <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Unlikely",'4. Risk Register'!$G$5:$G$66,"Major")</f>
         <v/>
       </c>
       <c r="F9" s="21">
-        <f>COUNTIFS('4. Risk Register'!$A$5:$A$62,"Yes",'4. Risk Register'!$F$5:$F$62,"Unlikely",'4. Risk Register'!$G$5:$G$62,"Severe")</f>
+        <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Unlikely",'4. Risk Register'!$G$5:$G$66,"Severe")</f>
         <v/>
       </c>
       <c r="H9" s="27" t="inlineStr">
@@ -6829,11 +7173,11 @@
         </is>
       </c>
       <c r="I9" s="9">
-        <f>COUNTIF('4. Risk Register'!$I$5:$I$62,"Low")</f>
+        <f>COUNTIF('4. Risk Register'!$I$5:$I$66,"Low")</f>
         <v/>
       </c>
       <c r="J9" s="9">
-        <f>COUNTIF('4. Risk Register'!$M$5:$M$62,"Low")</f>
+        <f>COUNTIF('4. Risk Register'!$M$5:$M$66,"Low")</f>
         <v/>
       </c>
     </row>
@@ -6844,23 +7188,23 @@
         </is>
       </c>
       <c r="B10" s="24">
-        <f>COUNTIFS('4. Risk Register'!$A$5:$A$62,"Yes",'4. Risk Register'!$F$5:$F$62,"Rare",'4. Risk Register'!$G$5:$G$62,"Insignificant")</f>
+        <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Rare",'4. Risk Register'!$G$5:$G$66,"Insignificant")</f>
         <v/>
       </c>
       <c r="C10" s="24">
-        <f>COUNTIFS('4. Risk Register'!$A$5:$A$62,"Yes",'4. Risk Register'!$F$5:$F$62,"Rare",'4. Risk Register'!$G$5:$G$62,"Minor")</f>
+        <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Rare",'4. Risk Register'!$G$5:$G$66,"Minor")</f>
         <v/>
       </c>
       <c r="D10" s="24">
-        <f>COUNTIFS('4. Risk Register'!$A$5:$A$62,"Yes",'4. Risk Register'!$F$5:$F$62,"Rare",'4. Risk Register'!$G$5:$G$62,"Moderate")</f>
+        <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Rare",'4. Risk Register'!$G$5:$G$66,"Moderate")</f>
         <v/>
       </c>
       <c r="E10" s="24">
-        <f>COUNTIFS('4. Risk Register'!$A$5:$A$62,"Yes",'4. Risk Register'!$F$5:$F$62,"Rare",'4. Risk Register'!$G$5:$G$62,"Major")</f>
+        <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Rare",'4. Risk Register'!$G$5:$G$66,"Major")</f>
         <v/>
       </c>
       <c r="F10" s="20">
-        <f>COUNTIFS('4. Risk Register'!$A$5:$A$62,"Yes",'4. Risk Register'!$F$5:$F$62,"Rare",'4. Risk Register'!$G$5:$G$62,"Severe")</f>
+        <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Rare",'4. Risk Register'!$G$5:$G$66,"Severe")</f>
         <v/>
       </c>
       <c r="H10" s="13" t="inlineStr">
@@ -6947,27 +7291,27 @@
         </is>
       </c>
       <c r="D16" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Governance &amp; Accountability",'4. Risk Register'!$A$5:$A$62,"Yes")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Governance &amp; Accountability",'4. Risk Register'!$A$5:$A$66,"Yes")</f>
         <v/>
       </c>
       <c r="E16" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Governance &amp; Accountability",'4. Risk Register'!$M$5:$M$62,"Critical")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Governance &amp; Accountability",'4. Risk Register'!$M$5:$M$66,"Critical")</f>
         <v/>
       </c>
       <c r="F16" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Governance &amp; Accountability",'4. Risk Register'!$M$5:$M$62,"High")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Governance &amp; Accountability",'4. Risk Register'!$M$5:$M$66,"High")</f>
         <v/>
       </c>
       <c r="G16" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Governance &amp; Accountability",'4. Risk Register'!$M$5:$M$62,"Medium")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Governance &amp; Accountability",'4. Risk Register'!$M$5:$M$66,"Medium")</f>
         <v/>
       </c>
       <c r="H16" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Governance &amp; Accountability",'4. Risk Register'!$M$5:$M$62,"Low")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Governance &amp; Accountability",'4. Risk Register'!$M$5:$M$66,"Low")</f>
         <v/>
       </c>
       <c r="I16" s="9">
-        <f>IFERROR(ROUND(AVERAGEIFS('4. Risk Register'!$L$5:$L$62,'4. Risk Register'!$C$5:$C$62,"Governance &amp; Accountability",'4. Risk Register'!$A$5:$A$62,"Yes"),1),"-")</f>
+        <f>IFERROR(ROUND(AVERAGEIFS('4. Risk Register'!$L$5:$L$66,'4. Risk Register'!$C$5:$C$66,"Governance &amp; Accountability",'4. Risk Register'!$A$5:$A$66,"Yes"),1),"-")</f>
         <v/>
       </c>
     </row>
@@ -6978,27 +7322,27 @@
         </is>
       </c>
       <c r="D17" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Legal, Regulatory &amp; Compliance",'4. Risk Register'!$A$5:$A$62,"Yes")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Legal, Regulatory &amp; Compliance",'4. Risk Register'!$A$5:$A$66,"Yes")</f>
         <v/>
       </c>
       <c r="E17" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Legal, Regulatory &amp; Compliance",'4. Risk Register'!$M$5:$M$62,"Critical")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Legal, Regulatory &amp; Compliance",'4. Risk Register'!$M$5:$M$66,"Critical")</f>
         <v/>
       </c>
       <c r="F17" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Legal, Regulatory &amp; Compliance",'4. Risk Register'!$M$5:$M$62,"High")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Legal, Regulatory &amp; Compliance",'4. Risk Register'!$M$5:$M$66,"High")</f>
         <v/>
       </c>
       <c r="G17" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Legal, Regulatory &amp; Compliance",'4. Risk Register'!$M$5:$M$62,"Medium")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Legal, Regulatory &amp; Compliance",'4. Risk Register'!$M$5:$M$66,"Medium")</f>
         <v/>
       </c>
       <c r="H17" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Legal, Regulatory &amp; Compliance",'4. Risk Register'!$M$5:$M$62,"Low")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Legal, Regulatory &amp; Compliance",'4. Risk Register'!$M$5:$M$66,"Low")</f>
         <v/>
       </c>
       <c r="I17" s="9">
-        <f>IFERROR(ROUND(AVERAGEIFS('4. Risk Register'!$L$5:$L$62,'4. Risk Register'!$C$5:$C$62,"Legal, Regulatory &amp; Compliance",'4. Risk Register'!$A$5:$A$62,"Yes"),1),"-")</f>
+        <f>IFERROR(ROUND(AVERAGEIFS('4. Risk Register'!$L$5:$L$66,'4. Risk Register'!$C$5:$C$66,"Legal, Regulatory &amp; Compliance",'4. Risk Register'!$A$5:$A$66,"Yes"),1),"-")</f>
         <v/>
       </c>
     </row>
@@ -7009,27 +7353,27 @@
         </is>
       </c>
       <c r="D18" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Fairness, Bias &amp; Human Rights",'4. Risk Register'!$A$5:$A$62,"Yes")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Fairness, Bias &amp; Human Rights",'4. Risk Register'!$A$5:$A$66,"Yes")</f>
         <v/>
       </c>
       <c r="E18" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Fairness, Bias &amp; Human Rights",'4. Risk Register'!$M$5:$M$62,"Critical")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Fairness, Bias &amp; Human Rights",'4. Risk Register'!$M$5:$M$66,"Critical")</f>
         <v/>
       </c>
       <c r="F18" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Fairness, Bias &amp; Human Rights",'4. Risk Register'!$M$5:$M$62,"High")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Fairness, Bias &amp; Human Rights",'4. Risk Register'!$M$5:$M$66,"High")</f>
         <v/>
       </c>
       <c r="G18" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Fairness, Bias &amp; Human Rights",'4. Risk Register'!$M$5:$M$62,"Medium")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Fairness, Bias &amp; Human Rights",'4. Risk Register'!$M$5:$M$66,"Medium")</f>
         <v/>
       </c>
       <c r="H18" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Fairness, Bias &amp; Human Rights",'4. Risk Register'!$M$5:$M$62,"Low")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Fairness, Bias &amp; Human Rights",'4. Risk Register'!$M$5:$M$66,"Low")</f>
         <v/>
       </c>
       <c r="I18" s="9">
-        <f>IFERROR(ROUND(AVERAGEIFS('4. Risk Register'!$L$5:$L$62,'4. Risk Register'!$C$5:$C$62,"Fairness, Bias &amp; Human Rights",'4. Risk Register'!$A$5:$A$62,"Yes"),1),"-")</f>
+        <f>IFERROR(ROUND(AVERAGEIFS('4. Risk Register'!$L$5:$L$66,'4. Risk Register'!$C$5:$C$66,"Fairness, Bias &amp; Human Rights",'4. Risk Register'!$A$5:$A$66,"Yes"),1),"-")</f>
         <v/>
       </c>
     </row>
@@ -7040,27 +7384,27 @@
         </is>
       </c>
       <c r="D19" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Privacy &amp; Data Protection",'4. Risk Register'!$A$5:$A$62,"Yes")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Privacy &amp; Data Protection",'4. Risk Register'!$A$5:$A$66,"Yes")</f>
         <v/>
       </c>
       <c r="E19" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Privacy &amp; Data Protection",'4. Risk Register'!$M$5:$M$62,"Critical")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Privacy &amp; Data Protection",'4. Risk Register'!$M$5:$M$66,"Critical")</f>
         <v/>
       </c>
       <c r="F19" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Privacy &amp; Data Protection",'4. Risk Register'!$M$5:$M$62,"High")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Privacy &amp; Data Protection",'4. Risk Register'!$M$5:$M$66,"High")</f>
         <v/>
       </c>
       <c r="G19" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Privacy &amp; Data Protection",'4. Risk Register'!$M$5:$M$62,"Medium")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Privacy &amp; Data Protection",'4. Risk Register'!$M$5:$M$66,"Medium")</f>
         <v/>
       </c>
       <c r="H19" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Privacy &amp; Data Protection",'4. Risk Register'!$M$5:$M$62,"Low")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Privacy &amp; Data Protection",'4. Risk Register'!$M$5:$M$66,"Low")</f>
         <v/>
       </c>
       <c r="I19" s="9">
-        <f>IFERROR(ROUND(AVERAGEIFS('4. Risk Register'!$L$5:$L$62,'4. Risk Register'!$C$5:$C$62,"Privacy &amp; Data Protection",'4. Risk Register'!$A$5:$A$62,"Yes"),1),"-")</f>
+        <f>IFERROR(ROUND(AVERAGEIFS('4. Risk Register'!$L$5:$L$66,'4. Risk Register'!$C$5:$C$66,"Privacy &amp; Data Protection",'4. Risk Register'!$A$5:$A$66,"Yes"),1),"-")</f>
         <v/>
       </c>
     </row>
@@ -7071,27 +7415,27 @@
         </is>
       </c>
       <c r="D20" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Data Quality &amp; Integrity",'4. Risk Register'!$A$5:$A$62,"Yes")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Data Quality &amp; Integrity",'4. Risk Register'!$A$5:$A$66,"Yes")</f>
         <v/>
       </c>
       <c r="E20" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Data Quality &amp; Integrity",'4. Risk Register'!$M$5:$M$62,"Critical")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Data Quality &amp; Integrity",'4. Risk Register'!$M$5:$M$66,"Critical")</f>
         <v/>
       </c>
       <c r="F20" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Data Quality &amp; Integrity",'4. Risk Register'!$M$5:$M$62,"High")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Data Quality &amp; Integrity",'4. Risk Register'!$M$5:$M$66,"High")</f>
         <v/>
       </c>
       <c r="G20" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Data Quality &amp; Integrity",'4. Risk Register'!$M$5:$M$62,"Medium")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Data Quality &amp; Integrity",'4. Risk Register'!$M$5:$M$66,"Medium")</f>
         <v/>
       </c>
       <c r="H20" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Data Quality &amp; Integrity",'4. Risk Register'!$M$5:$M$62,"Low")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Data Quality &amp; Integrity",'4. Risk Register'!$M$5:$M$66,"Low")</f>
         <v/>
       </c>
       <c r="I20" s="9">
-        <f>IFERROR(ROUND(AVERAGEIFS('4. Risk Register'!$L$5:$L$62,'4. Risk Register'!$C$5:$C$62,"Data Quality &amp; Integrity",'4. Risk Register'!$A$5:$A$62,"Yes"),1),"-")</f>
+        <f>IFERROR(ROUND(AVERAGEIFS('4. Risk Register'!$L$5:$L$66,'4. Risk Register'!$C$5:$C$66,"Data Quality &amp; Integrity",'4. Risk Register'!$A$5:$A$66,"Yes"),1),"-")</f>
         <v/>
       </c>
     </row>
@@ -7102,27 +7446,27 @@
         </is>
       </c>
       <c r="D21" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Model Performance, Reliability &amp; Robustness",'4. Risk Register'!$A$5:$A$62,"Yes")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Model Performance, Reliability &amp; Robustness",'4. Risk Register'!$A$5:$A$66,"Yes")</f>
         <v/>
       </c>
       <c r="E21" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Model Performance, Reliability &amp; Robustness",'4. Risk Register'!$M$5:$M$62,"Critical")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Model Performance, Reliability &amp; Robustness",'4. Risk Register'!$M$5:$M$66,"Critical")</f>
         <v/>
       </c>
       <c r="F21" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Model Performance, Reliability &amp; Robustness",'4. Risk Register'!$M$5:$M$62,"High")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Model Performance, Reliability &amp; Robustness",'4. Risk Register'!$M$5:$M$66,"High")</f>
         <v/>
       </c>
       <c r="G21" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Model Performance, Reliability &amp; Robustness",'4. Risk Register'!$M$5:$M$62,"Medium")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Model Performance, Reliability &amp; Robustness",'4. Risk Register'!$M$5:$M$66,"Medium")</f>
         <v/>
       </c>
       <c r="H21" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Model Performance, Reliability &amp; Robustness",'4. Risk Register'!$M$5:$M$62,"Low")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Model Performance, Reliability &amp; Robustness",'4. Risk Register'!$M$5:$M$66,"Low")</f>
         <v/>
       </c>
       <c r="I21" s="9">
-        <f>IFERROR(ROUND(AVERAGEIFS('4. Risk Register'!$L$5:$L$62,'4. Risk Register'!$C$5:$C$62,"Model Performance, Reliability &amp; Robustness",'4. Risk Register'!$A$5:$A$62,"Yes"),1),"-")</f>
+        <f>IFERROR(ROUND(AVERAGEIFS('4. Risk Register'!$L$5:$L$66,'4. Risk Register'!$C$5:$C$66,"Model Performance, Reliability &amp; Robustness",'4. Risk Register'!$A$5:$A$66,"Yes"),1),"-")</f>
         <v/>
       </c>
     </row>
@@ -7133,27 +7477,27 @@
         </is>
       </c>
       <c r="D22" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Transparency, Explainability &amp; Contestability",'4. Risk Register'!$A$5:$A$62,"Yes")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Transparency, Explainability &amp; Contestability",'4. Risk Register'!$A$5:$A$66,"Yes")</f>
         <v/>
       </c>
       <c r="E22" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Transparency, Explainability &amp; Contestability",'4. Risk Register'!$M$5:$M$62,"Critical")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Transparency, Explainability &amp; Contestability",'4. Risk Register'!$M$5:$M$66,"Critical")</f>
         <v/>
       </c>
       <c r="F22" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Transparency, Explainability &amp; Contestability",'4. Risk Register'!$M$5:$M$62,"High")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Transparency, Explainability &amp; Contestability",'4. Risk Register'!$M$5:$M$66,"High")</f>
         <v/>
       </c>
       <c r="G22" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Transparency, Explainability &amp; Contestability",'4. Risk Register'!$M$5:$M$62,"Medium")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Transparency, Explainability &amp; Contestability",'4. Risk Register'!$M$5:$M$66,"Medium")</f>
         <v/>
       </c>
       <c r="H22" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Transparency, Explainability &amp; Contestability",'4. Risk Register'!$M$5:$M$62,"Low")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Transparency, Explainability &amp; Contestability",'4. Risk Register'!$M$5:$M$66,"Low")</f>
         <v/>
       </c>
       <c r="I22" s="9">
-        <f>IFERROR(ROUND(AVERAGEIFS('4. Risk Register'!$L$5:$L$62,'4. Risk Register'!$C$5:$C$62,"Transparency, Explainability &amp; Contestability",'4. Risk Register'!$A$5:$A$62,"Yes"),1),"-")</f>
+        <f>IFERROR(ROUND(AVERAGEIFS('4. Risk Register'!$L$5:$L$66,'4. Risk Register'!$C$5:$C$66,"Transparency, Explainability &amp; Contestability",'4. Risk Register'!$A$5:$A$66,"Yes"),1),"-")</f>
         <v/>
       </c>
     </row>
@@ -7164,27 +7508,27 @@
         </is>
       </c>
       <c r="D23" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Security of AI Systems",'4. Risk Register'!$A$5:$A$62,"Yes")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Security of AI Systems",'4. Risk Register'!$A$5:$A$66,"Yes")</f>
         <v/>
       </c>
       <c r="E23" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Security of AI Systems",'4. Risk Register'!$M$5:$M$62,"Critical")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Security of AI Systems",'4. Risk Register'!$M$5:$M$66,"Critical")</f>
         <v/>
       </c>
       <c r="F23" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Security of AI Systems",'4. Risk Register'!$M$5:$M$62,"High")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Security of AI Systems",'4. Risk Register'!$M$5:$M$66,"High")</f>
         <v/>
       </c>
       <c r="G23" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Security of AI Systems",'4. Risk Register'!$M$5:$M$62,"Medium")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Security of AI Systems",'4. Risk Register'!$M$5:$M$66,"Medium")</f>
         <v/>
       </c>
       <c r="H23" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Security of AI Systems",'4. Risk Register'!$M$5:$M$62,"Low")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Security of AI Systems",'4. Risk Register'!$M$5:$M$66,"Low")</f>
         <v/>
       </c>
       <c r="I23" s="9">
-        <f>IFERROR(ROUND(AVERAGEIFS('4. Risk Register'!$L$5:$L$62,'4. Risk Register'!$C$5:$C$62,"Security of AI Systems",'4. Risk Register'!$A$5:$A$62,"Yes"),1),"-")</f>
+        <f>IFERROR(ROUND(AVERAGEIFS('4. Risk Register'!$L$5:$L$66,'4. Risk Register'!$C$5:$C$66,"Security of AI Systems",'4. Risk Register'!$A$5:$A$66,"Yes"),1),"-")</f>
         <v/>
       </c>
     </row>
@@ -7195,27 +7539,27 @@
         </is>
       </c>
       <c r="D24" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Human Oversight &amp; Autonomy",'4. Risk Register'!$A$5:$A$62,"Yes")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Human Oversight &amp; Autonomy",'4. Risk Register'!$A$5:$A$66,"Yes")</f>
         <v/>
       </c>
       <c r="E24" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Human Oversight &amp; Autonomy",'4. Risk Register'!$M$5:$M$62,"Critical")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Human Oversight &amp; Autonomy",'4. Risk Register'!$M$5:$M$66,"Critical")</f>
         <v/>
       </c>
       <c r="F24" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Human Oversight &amp; Autonomy",'4. Risk Register'!$M$5:$M$62,"High")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Human Oversight &amp; Autonomy",'4. Risk Register'!$M$5:$M$66,"High")</f>
         <v/>
       </c>
       <c r="G24" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Human Oversight &amp; Autonomy",'4. Risk Register'!$M$5:$M$62,"Medium")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Human Oversight &amp; Autonomy",'4. Risk Register'!$M$5:$M$66,"Medium")</f>
         <v/>
       </c>
       <c r="H24" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Human Oversight &amp; Autonomy",'4. Risk Register'!$M$5:$M$62,"Low")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Human Oversight &amp; Autonomy",'4. Risk Register'!$M$5:$M$66,"Low")</f>
         <v/>
       </c>
       <c r="I24" s="9">
-        <f>IFERROR(ROUND(AVERAGEIFS('4. Risk Register'!$L$5:$L$62,'4. Risk Register'!$C$5:$C$62,"Human Oversight &amp; Autonomy",'4. Risk Register'!$A$5:$A$62,"Yes"),1),"-")</f>
+        <f>IFERROR(ROUND(AVERAGEIFS('4. Risk Register'!$L$5:$L$66,'4. Risk Register'!$C$5:$C$66,"Human Oversight &amp; Autonomy",'4. Risk Register'!$A$5:$A$66,"Yes"),1),"-")</f>
         <v/>
       </c>
     </row>
@@ -7226,27 +7570,27 @@
         </is>
       </c>
       <c r="D25" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Third-Party &amp; Supply Chain",'4. Risk Register'!$A$5:$A$62,"Yes")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Third-Party &amp; Supply Chain",'4. Risk Register'!$A$5:$A$66,"Yes")</f>
         <v/>
       </c>
       <c r="E25" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Third-Party &amp; Supply Chain",'4. Risk Register'!$M$5:$M$62,"Critical")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Third-Party &amp; Supply Chain",'4. Risk Register'!$M$5:$M$66,"Critical")</f>
         <v/>
       </c>
       <c r="F25" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Third-Party &amp; Supply Chain",'4. Risk Register'!$M$5:$M$62,"High")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Third-Party &amp; Supply Chain",'4. Risk Register'!$M$5:$M$66,"High")</f>
         <v/>
       </c>
       <c r="G25" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Third-Party &amp; Supply Chain",'4. Risk Register'!$M$5:$M$62,"Medium")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Third-Party &amp; Supply Chain",'4. Risk Register'!$M$5:$M$66,"Medium")</f>
         <v/>
       </c>
       <c r="H25" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Third-Party &amp; Supply Chain",'4. Risk Register'!$M$5:$M$62,"Low")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Third-Party &amp; Supply Chain",'4. Risk Register'!$M$5:$M$66,"Low")</f>
         <v/>
       </c>
       <c r="I25" s="9">
-        <f>IFERROR(ROUND(AVERAGEIFS('4. Risk Register'!$L$5:$L$62,'4. Risk Register'!$C$5:$C$62,"Third-Party &amp; Supply Chain",'4. Risk Register'!$A$5:$A$62,"Yes"),1),"-")</f>
+        <f>IFERROR(ROUND(AVERAGEIFS('4. Risk Register'!$L$5:$L$66,'4. Risk Register'!$C$5:$C$66,"Third-Party &amp; Supply Chain",'4. Risk Register'!$A$5:$A$66,"Yes"),1),"-")</f>
         <v/>
       </c>
     </row>
@@ -7257,27 +7601,27 @@
         </is>
       </c>
       <c r="D26" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Operational, Financial &amp; Sustainability",'4. Risk Register'!$A$5:$A$62,"Yes")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Operational, Financial &amp; Sustainability",'4. Risk Register'!$A$5:$A$66,"Yes")</f>
         <v/>
       </c>
       <c r="E26" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Operational, Financial &amp; Sustainability",'4. Risk Register'!$M$5:$M$62,"Critical")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Operational, Financial &amp; Sustainability",'4. Risk Register'!$M$5:$M$66,"Critical")</f>
         <v/>
       </c>
       <c r="F26" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Operational, Financial &amp; Sustainability",'4. Risk Register'!$M$5:$M$62,"High")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Operational, Financial &amp; Sustainability",'4. Risk Register'!$M$5:$M$66,"High")</f>
         <v/>
       </c>
       <c r="G26" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Operational, Financial &amp; Sustainability",'4. Risk Register'!$M$5:$M$62,"Medium")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Operational, Financial &amp; Sustainability",'4. Risk Register'!$M$5:$M$66,"Medium")</f>
         <v/>
       </c>
       <c r="H26" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Operational, Financial &amp; Sustainability",'4. Risk Register'!$M$5:$M$62,"Low")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Operational, Financial &amp; Sustainability",'4. Risk Register'!$M$5:$M$66,"Low")</f>
         <v/>
       </c>
       <c r="I26" s="9">
-        <f>IFERROR(ROUND(AVERAGEIFS('4. Risk Register'!$L$5:$L$62,'4. Risk Register'!$C$5:$C$62,"Operational, Financial &amp; Sustainability",'4. Risk Register'!$A$5:$A$62,"Yes"),1),"-")</f>
+        <f>IFERROR(ROUND(AVERAGEIFS('4. Risk Register'!$L$5:$L$66,'4. Risk Register'!$C$5:$C$66,"Operational, Financial &amp; Sustainability",'4. Risk Register'!$A$5:$A$66,"Yes"),1),"-")</f>
         <v/>
       </c>
     </row>
@@ -7288,27 +7632,27 @@
         </is>
       </c>
       <c r="D27" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Societal, Reputational &amp; AI-Enabled Threats",'4. Risk Register'!$A$5:$A$62,"Yes")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Societal, Reputational &amp; AI-Enabled Threats",'4. Risk Register'!$A$5:$A$66,"Yes")</f>
         <v/>
       </c>
       <c r="E27" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Societal, Reputational &amp; AI-Enabled Threats",'4. Risk Register'!$M$5:$M$62,"Critical")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Societal, Reputational &amp; AI-Enabled Threats",'4. Risk Register'!$M$5:$M$66,"Critical")</f>
         <v/>
       </c>
       <c r="F27" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Societal, Reputational &amp; AI-Enabled Threats",'4. Risk Register'!$M$5:$M$62,"High")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Societal, Reputational &amp; AI-Enabled Threats",'4. Risk Register'!$M$5:$M$66,"High")</f>
         <v/>
       </c>
       <c r="G27" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Societal, Reputational &amp; AI-Enabled Threats",'4. Risk Register'!$M$5:$M$62,"Medium")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Societal, Reputational &amp; AI-Enabled Threats",'4. Risk Register'!$M$5:$M$66,"Medium")</f>
         <v/>
       </c>
       <c r="H27" s="9">
-        <f>COUNTIFS('4. Risk Register'!$C$5:$C$62,"Societal, Reputational &amp; AI-Enabled Threats",'4. Risk Register'!$M$5:$M$62,"Low")</f>
+        <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Societal, Reputational &amp; AI-Enabled Threats",'4. Risk Register'!$M$5:$M$66,"Low")</f>
         <v/>
       </c>
       <c r="I27" s="9">
-        <f>IFERROR(ROUND(AVERAGEIFS('4. Risk Register'!$L$5:$L$62,'4. Risk Register'!$C$5:$C$62,"Societal, Reputational &amp; AI-Enabled Threats",'4. Risk Register'!$A$5:$A$62,"Yes"),1),"-")</f>
+        <f>IFERROR(ROUND(AVERAGEIFS('4. Risk Register'!$L$5:$L$66,'4. Risk Register'!$C$5:$C$66,"Societal, Reputational &amp; AI-Enabled Threats",'4. Risk Register'!$A$5:$A$66,"Yes"),1),"-")</f>
         <v/>
       </c>
     </row>
@@ -7369,34 +7713,34 @@
         <v>1</v>
       </c>
       <c r="B32" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$B$5:$B$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,1),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$B$5:$B$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,1),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="C32" s="14">
-        <f>IFERROR(INDEX('4. Risk Register'!$D$5:$D$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,1),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$D$5:$D$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,1),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="D32" s="14" t="n"/>
       <c r="E32" s="14" t="n"/>
       <c r="F32" s="14" t="n"/>
       <c r="G32" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$L$5:$L$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,1),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$L$5:$L$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,1),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="H32" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$M$5:$M$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,1),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$M$5:$M$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,1),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="I32" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$O$5:$O$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,1),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$O$5:$O$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,1),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="J32" s="14">
-        <f>IFERROR(INDEX('4. Risk Register'!$Q$5:$Q$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,1),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$Q$5:$Q$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,1),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="K32" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$S$5:$S$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,1),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$S$5:$S$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,1),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
     </row>
@@ -7405,34 +7749,34 @@
         <v>2</v>
       </c>
       <c r="B33" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$B$5:$B$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,2),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$B$5:$B$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,2),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="C33" s="14">
-        <f>IFERROR(INDEX('4. Risk Register'!$D$5:$D$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,2),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$D$5:$D$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,2),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="D33" s="14" t="n"/>
       <c r="E33" s="14" t="n"/>
       <c r="F33" s="14" t="n"/>
       <c r="G33" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$L$5:$L$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,2),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$L$5:$L$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,2),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="H33" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$M$5:$M$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,2),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$M$5:$M$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,2),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="I33" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$O$5:$O$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,2),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$O$5:$O$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,2),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="J33" s="14">
-        <f>IFERROR(INDEX('4. Risk Register'!$Q$5:$Q$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,2),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$Q$5:$Q$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,2),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="K33" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$S$5:$S$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,2),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$S$5:$S$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,2),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
     </row>
@@ -7441,34 +7785,34 @@
         <v>3</v>
       </c>
       <c r="B34" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$B$5:$B$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,3),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$B$5:$B$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,3),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="C34" s="14">
-        <f>IFERROR(INDEX('4. Risk Register'!$D$5:$D$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,3),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$D$5:$D$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,3),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="D34" s="14" t="n"/>
       <c r="E34" s="14" t="n"/>
       <c r="F34" s="14" t="n"/>
       <c r="G34" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$L$5:$L$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,3),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$L$5:$L$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,3),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="H34" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$M$5:$M$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,3),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$M$5:$M$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,3),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="I34" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$O$5:$O$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,3),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$O$5:$O$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,3),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="J34" s="14">
-        <f>IFERROR(INDEX('4. Risk Register'!$Q$5:$Q$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,3),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$Q$5:$Q$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,3),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="K34" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$S$5:$S$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,3),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$S$5:$S$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,3),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
     </row>
@@ -7477,34 +7821,34 @@
         <v>4</v>
       </c>
       <c r="B35" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$B$5:$B$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,4),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$B$5:$B$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,4),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="C35" s="14">
-        <f>IFERROR(INDEX('4. Risk Register'!$D$5:$D$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,4),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$D$5:$D$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,4),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="D35" s="14" t="n"/>
       <c r="E35" s="14" t="n"/>
       <c r="F35" s="14" t="n"/>
       <c r="G35" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$L$5:$L$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,4),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$L$5:$L$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,4),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="H35" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$M$5:$M$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,4),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$M$5:$M$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,4),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="I35" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$O$5:$O$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,4),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$O$5:$O$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,4),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="J35" s="14">
-        <f>IFERROR(INDEX('4. Risk Register'!$Q$5:$Q$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,4),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$Q$5:$Q$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,4),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="K35" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$S$5:$S$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,4),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$S$5:$S$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,4),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
     </row>
@@ -7513,34 +7857,34 @@
         <v>5</v>
       </c>
       <c r="B36" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$B$5:$B$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,5),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$B$5:$B$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,5),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="C36" s="14">
-        <f>IFERROR(INDEX('4. Risk Register'!$D$5:$D$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,5),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$D$5:$D$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,5),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="D36" s="14" t="n"/>
       <c r="E36" s="14" t="n"/>
       <c r="F36" s="14" t="n"/>
       <c r="G36" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$L$5:$L$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,5),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$L$5:$L$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,5),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="H36" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$M$5:$M$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,5),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$M$5:$M$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,5),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="I36" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$O$5:$O$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,5),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$O$5:$O$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,5),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="J36" s="14">
-        <f>IFERROR(INDEX('4. Risk Register'!$Q$5:$Q$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,5),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$Q$5:$Q$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,5),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="K36" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$S$5:$S$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,5),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$S$5:$S$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,5),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
     </row>
@@ -7549,34 +7893,34 @@
         <v>6</v>
       </c>
       <c r="B37" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$B$5:$B$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,6),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$B$5:$B$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,6),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="C37" s="14">
-        <f>IFERROR(INDEX('4. Risk Register'!$D$5:$D$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,6),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$D$5:$D$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,6),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="D37" s="14" t="n"/>
       <c r="E37" s="14" t="n"/>
       <c r="F37" s="14" t="n"/>
       <c r="G37" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$L$5:$L$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,6),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$L$5:$L$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,6),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="H37" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$M$5:$M$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,6),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$M$5:$M$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,6),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="I37" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$O$5:$O$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,6),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$O$5:$O$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,6),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="J37" s="14">
-        <f>IFERROR(INDEX('4. Risk Register'!$Q$5:$Q$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,6),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$Q$5:$Q$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,6),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="K37" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$S$5:$S$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,6),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$S$5:$S$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,6),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
     </row>
@@ -7585,34 +7929,34 @@
         <v>7</v>
       </c>
       <c r="B38" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$B$5:$B$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,7),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$B$5:$B$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,7),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="C38" s="14">
-        <f>IFERROR(INDEX('4. Risk Register'!$D$5:$D$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,7),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$D$5:$D$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,7),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="D38" s="14" t="n"/>
       <c r="E38" s="14" t="n"/>
       <c r="F38" s="14" t="n"/>
       <c r="G38" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$L$5:$L$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,7),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$L$5:$L$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,7),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="H38" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$M$5:$M$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,7),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$M$5:$M$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,7),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="I38" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$O$5:$O$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,7),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$O$5:$O$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,7),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="J38" s="14">
-        <f>IFERROR(INDEX('4. Risk Register'!$Q$5:$Q$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,7),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$Q$5:$Q$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,7),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="K38" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$S$5:$S$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,7),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$S$5:$S$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,7),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
     </row>
@@ -7621,34 +7965,34 @@
         <v>8</v>
       </c>
       <c r="B39" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$B$5:$B$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,8),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$B$5:$B$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,8),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="C39" s="14">
-        <f>IFERROR(INDEX('4. Risk Register'!$D$5:$D$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,8),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$D$5:$D$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,8),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="D39" s="14" t="n"/>
       <c r="E39" s="14" t="n"/>
       <c r="F39" s="14" t="n"/>
       <c r="G39" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$L$5:$L$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,8),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$L$5:$L$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,8),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="H39" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$M$5:$M$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,8),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$M$5:$M$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,8),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="I39" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$O$5:$O$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,8),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$O$5:$O$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,8),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="J39" s="14">
-        <f>IFERROR(INDEX('4. Risk Register'!$Q$5:$Q$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,8),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$Q$5:$Q$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,8),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="K39" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$S$5:$S$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,8),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$S$5:$S$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,8),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
     </row>
@@ -7657,34 +8001,34 @@
         <v>9</v>
       </c>
       <c r="B40" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$B$5:$B$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,9),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$B$5:$B$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,9),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="C40" s="14">
-        <f>IFERROR(INDEX('4. Risk Register'!$D$5:$D$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,9),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$D$5:$D$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,9),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="D40" s="14" t="n"/>
       <c r="E40" s="14" t="n"/>
       <c r="F40" s="14" t="n"/>
       <c r="G40" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$L$5:$L$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,9),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$L$5:$L$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,9),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="H40" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$M$5:$M$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,9),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$M$5:$M$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,9),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="I40" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$O$5:$O$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,9),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$O$5:$O$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,9),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="J40" s="14">
-        <f>IFERROR(INDEX('4. Risk Register'!$Q$5:$Q$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,9),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$Q$5:$Q$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,9),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="K40" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$S$5:$S$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,9),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$S$5:$S$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,9),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
     </row>
@@ -7693,34 +8037,34 @@
         <v>10</v>
       </c>
       <c r="B41" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$B$5:$B$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,10),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$B$5:$B$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,10),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="C41" s="14">
-        <f>IFERROR(INDEX('4. Risk Register'!$D$5:$D$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,10),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$D$5:$D$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,10),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="D41" s="14" t="n"/>
       <c r="E41" s="14" t="n"/>
       <c r="F41" s="14" t="n"/>
       <c r="G41" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$L$5:$L$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,10),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$L$5:$L$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,10),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="H41" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$M$5:$M$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,10),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$M$5:$M$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,10),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="I41" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$O$5:$O$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,10),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$O$5:$O$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,10),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="J41" s="14">
-        <f>IFERROR(INDEX('4. Risk Register'!$Q$5:$Q$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,10),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$Q$5:$Q$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,10),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
       <c r="K41" s="9">
-        <f>IFERROR(INDEX('4. Risk Register'!$S$5:$S$62,MATCH(LARGE('4. Risk Register'!$V$5:$V$62,10),'4. Risk Register'!$V$5:$V$62,0)),"")</f>
+        <f>IFERROR(INDEX('4. Risk Register'!$S$5:$S$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,10),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
         <v/>
       </c>
     </row>
@@ -7912,8 +8256,9 @@
       <formula>"Prohibited"</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <printOptions gridLines="0"/>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.25" footer="0.25"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -7925,7 +8270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -7947,7 +8292,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>48 risks in 12 categories. Sources: NIST AI RMF &amp; AI 600-1, ISO/IEC 23894, EU AI Act, OWASP LLM / Agentic Top 10, MITRE ATLAS, MIT AI Risk Repository, GT AI Ready7. RCM IDs refer to GT AI RCM v2.0.</t>
+          <t>52 risks in 12 categories. Sources: NIST AI RMF &amp; AI 600-1, ISO/IEC 23894, EU AI Act, OWASP LLM / Agentic Top 10, MITRE ATLAS, MIT AI Risk Repository, GT AI Ready7. RCM IDs refer to GT AI RCM v2.1; agent risks draw on ISACA Securing AI Agents (2026).</t>
         </is>
       </c>
     </row>
@@ -7979,7 +8324,7 @@
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>RCM v2.0 controls</t>
+          <t>RCM v2.1 controls</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -8916,44 +9261,44 @@
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>TRA-01</t>
+          <t>PER-05</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Transparency, Explainability &amp; Contestability</t>
+          <t>Model Performance, Reliability &amp; Robustness</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>Undisclosed AI interaction or content</t>
+          <t>Uncontrolled prompt / configuration changes</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Users are unaware they interact with AI or that content is AI-generated.</t>
+          <t>Changes to prompts, guardrails, tool permissions or retrieval sources degrade safety or behaviour without regression testing.</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>EU AI Act Art. 50</t>
+          <t>ISACA Securing AI Agents (2026)</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>CO-1, LC-7</t>
+          <t>LC-12</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>AI touchpoints lacking disclosure</t>
+          <t>Releases without passing LLM regression suite</t>
         </is>
       </c>
     </row>
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>TRA-02</t>
+          <t>TRA-01</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -8963,34 +9308,34 @@
       </c>
       <c r="C31" s="13" t="inlineStr">
         <is>
-          <t>Unexplainable decisions</t>
+          <t>Undisclosed AI interaction or content</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Organisation cannot explain AI-supported decisions to affected persons, regulators or auditors.</t>
+          <t>Users are unaware they interact with AI or that content is AI-generated.</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>EU AI Act Art. 13, 86; NIST IR 8312</t>
+          <t>EU AI Act Art. 50</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>RS-4, LC-4</t>
+          <t>CO-1, LC-7</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>Explanation requests not satisfied</t>
+          <t>AI touchpoints lacking disclosure</t>
         </is>
       </c>
     </row>
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>TRA-03</t>
+          <t>TRA-02</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -9000,34 +9345,34 @@
       </c>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>No effective contest or redress route</t>
+          <t>Unexplainable decisions</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Affected persons cannot challenge or obtain human review of AI-supported decisions.</t>
+          <t>Organisation cannot explain AI-supported decisions to affected persons, regulators or auditors.</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>EU AI Act Art. 86; NSW AIAF</t>
+          <t>EU AI Act Art. 13, 86; NIST IR 8312</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>CO-3, PR-5</t>
+          <t>RS-4, LC-4</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>Appeals exceeding SLA</t>
+          <t>Explanation requests not satisfied</t>
         </is>
       </c>
     </row>
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>TRA-04</t>
+          <t>TRA-03</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -9037,71 +9382,71 @@
       </c>
       <c r="C33" s="13" t="inlineStr">
         <is>
-          <t>Inadequate documentation and records</t>
+          <t>No effective contest or redress route</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Technical documentation, logs or decisions are insufficient for audit or regulatory inspection.</t>
+          <t>Affected persons cannot challenge or obtain human review of AI-supported decisions.</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>EU AI Act Art. 11-12, 18-19</t>
+          <t>EU AI Act Art. 86; NSW AIAF</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>LC-4, OM-2, RO-3</t>
+          <t>CO-3, PR-5</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>Systems with incomplete documentation pack</t>
+          <t>Appeals exceeding SLA</t>
         </is>
       </c>
     </row>
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>SEC-01</t>
+          <t>TRA-04</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Security of AI Systems</t>
+          <t>Transparency, Explainability &amp; Contestability</t>
         </is>
       </c>
       <c r="C34" s="13" t="inlineStr">
         <is>
-          <t>Prompt injection and jailbreak</t>
+          <t>Inadequate documentation and records</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Attacker manipulates model behaviour via direct or indirect (embedded content) instructions.</t>
+          <t>Technical documentation, logs or decisions are insufficient for audit or regulatory inspection.</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>OWASP LLM01:2025; MITRE ATLAS</t>
+          <t>EU AI Act Art. 11-12, 18-19</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>SE-6</t>
+          <t>LC-4, OM-2, RO-3</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>Blocked injection attempts / bypasses in testing</t>
+          <t>Systems with incomplete documentation pack</t>
         </is>
       </c>
     </row>
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>SEC-02</t>
+          <t>SEC-01</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -9111,34 +9456,34 @@
       </c>
       <c r="C35" s="13" t="inlineStr">
         <is>
-          <t>Data or model poisoning</t>
+          <t>Prompt injection and jailbreak</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Training, fine-tuning or retrieval data is manipulated to corrupt outputs or insert backdoors.</t>
+          <t>Attacker manipulates model behaviour via direct or indirect (embedded content) instructions.</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>OWASP LLM04:2025; NIST AI 100-2</t>
+          <t>OWASP LLM01:2025; MITRE ATLAS</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>SE-6, LC-1, SE-7</t>
+          <t>SE-6</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>Integrity check failures</t>
+          <t>Blocked injection attempts / bypasses in testing</t>
         </is>
       </c>
     </row>
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>SEC-03</t>
+          <t>SEC-02</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
@@ -9148,34 +9493,34 @@
       </c>
       <c r="C36" s="13" t="inlineStr">
         <is>
-          <t>Model theft, extraction or inversion</t>
+          <t>Data or model poisoning</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Model weights, system prompts or training data are extracted.</t>
+          <t>Training, fine-tuning or retrieval data is manipulated to corrupt outputs or insert backdoors.</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>OWASP LLM07/LLM10:2025; MITRE ATLAS</t>
+          <t>OWASP LLM04:2025; NIST AI 100-2</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>SE-4, SE-6</t>
+          <t>SE-6, LC-1, SE-7</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>Anomalous query volumes</t>
+          <t>Integrity check failures</t>
         </is>
       </c>
     </row>
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>SEC-04</t>
+          <t>SEC-03</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
@@ -9185,34 +9530,34 @@
       </c>
       <c r="C37" s="13" t="inlineStr">
         <is>
-          <t>Insecure integration and excessive privilege</t>
+          <t>Model theft, extraction or inversion</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>AI components have excessive permissions or insecure APIs/plugins, enabling unauthorised actions.</t>
+          <t>Model weights, system prompts or training data are extracted.</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>OWASP LLM05/LLM06:2025; AI Ready7 4.2-4.3</t>
+          <t>OWASP LLM07/LLM10:2025; MITRE ATLAS</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>SE-2, LC-8</t>
+          <t>SE-4, SE-6</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>Agents / integrations with privileged standing access</t>
+          <t>Anomalous query volumes</t>
         </is>
       </c>
     </row>
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>SEC-05</t>
+          <t>SEC-04</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
@@ -9222,145 +9567,145 @@
       </c>
       <c r="C38" s="13" t="inlineStr">
         <is>
-          <t>Compromised AI supply chain</t>
+          <t>Insecure integration and excessive privilege</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Malicious or vulnerable third-party models, libraries, plugins or MCP servers.</t>
+          <t>AI components have excessive permissions or insecure APIs/plugins, enabling unauthorised actions.</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>OWASP LLM03:2025; CISA AI Data Security</t>
+          <t>OWASP LLM05/LLM06:2025; AI Ready7 4.2-4.3</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>SE-7</t>
+          <t>SE-2, LC-8</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>Unscanned model artefacts</t>
+          <t>Agents / integrations with privileged standing access</t>
         </is>
       </c>
     </row>
     <row r="39" ht="36" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>HUM-01</t>
+          <t>SEC-06</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Human Oversight &amp; Autonomy</t>
+          <t>Security of AI Systems</t>
         </is>
       </c>
       <c r="C39" s="13" t="inlineStr">
         <is>
-          <t>Automation bias and over-reliance</t>
+          <t>Agent memory poisoning &amp; cross-session leakage</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Users accept AI outputs without adequate scrutiny, eroding professional judgement.</t>
+          <t>Poisoned or unauthorised content persists in agent memory / vector stores, or context leaks across users, sessions or tenants.</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>EU AI Act Art. 14(4)(b); NIST AI 600-1 (Human-AI configuration)</t>
+          <t>ISACA Securing AI Agents (2026); OWASP LLM08:2025</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>RS-1, GL-4, LC-7</t>
+          <t>SE-8</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>Override / challenge rate</t>
+          <t>Cross-tenant retrieval test failures</t>
         </is>
       </c>
     </row>
     <row r="40" ht="36" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>HUM-02</t>
+          <t>SEC-07</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Human Oversight &amp; Autonomy</t>
+          <t>Security of AI Systems</t>
         </is>
       </c>
       <c r="C40" s="13" t="inlineStr">
         <is>
-          <t>Ineffective human oversight</t>
+          <t>Unsafe code execution, SSRF &amp; sandbox escape</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Oversight persons lack competence, authority, time or information to intervene.</t>
+          <t>Agent-generated code or tool calls reach internal networks, cloud metadata services or production secrets.</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>EU AI Act Art. 14, 26(2)</t>
+          <t>ISACA Securing AI Agents (2026); CWS ISO 42001 checklist 33</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>RS-1, GL-4</t>
+          <t>SE-9, SE-10</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>Oversight roles without training</t>
+          <t>Blocked egress / SSRF attempts</t>
         </is>
       </c>
     </row>
     <row r="41" ht="36" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>HUM-03</t>
+          <t>SEC-05</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Human Oversight &amp; Autonomy</t>
+          <t>Security of AI Systems</t>
         </is>
       </c>
       <c r="C41" s="13" t="inlineStr">
         <is>
-          <t>Unbounded autonomous agent actions</t>
+          <t>Compromised AI supply chain</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>AI agents take high-impact actions (payments, communications, code execution) without adequate limits or approval.</t>
+          <t>Malicious or vulnerable third-party models, libraries, plugins or MCP servers.</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>OWASP Agentic Top 10; Singapore Agentic AI framework</t>
+          <t>OWASP LLM03:2025; CISA AI Data Security</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>LC-8</t>
+          <t>SE-7</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>High-impact agent actions without approval</t>
+          <t>Unscanned model artefacts</t>
         </is>
       </c>
     </row>
     <row r="42" ht="36" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>HUM-04</t>
+          <t>HUM-01</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
@@ -9370,408 +9715,557 @@
       </c>
       <c r="C42" s="13" t="inlineStr">
         <is>
-          <t>Adverse workforce impact</t>
+          <t>Automation bias and over-reliance</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>AI adoption causes skills erosion, job anxiety or unconsulted changes to working conditions.</t>
+          <t>Users accept AI outputs without adequate scrutiny, eroding professional judgement.</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>EU AI Act Art. 26(7); AI Ready7 3.4</t>
+          <t>EU AI Act Art. 14(4)(b); NIST AI 600-1 (Human-AI configuration)</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>RS-9, GL-4</t>
+          <t>RS-1, GL-4, LC-7</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>Staff sentiment / attrition in affected roles</t>
+          <t>Override / challenge rate</t>
         </is>
       </c>
     </row>
     <row r="43" ht="36" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>TPR-01</t>
+          <t>HUM-02</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Third-Party &amp; Supply Chain</t>
+          <t>Human Oversight &amp; Autonomy</t>
         </is>
       </c>
       <c r="C43" s="13" t="inlineStr">
         <is>
-          <t>Vendor lock-in and concentration</t>
+          <t>Ineffective human oversight</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Critical dependence on a single AI provider or cloud creates resilience and bargaining risk.</t>
+          <t>Oversight persons lack competence, authority, time or information to intervene.</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>ISO/IEC 42001 A.10; CBB outsourcing</t>
+          <t>EU AI Act Art. 14, 26(2)</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>TP-2, TP-3</t>
+          <t>RS-1, GL-4</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>% critical AI workloads on single provider</t>
+          <t>Oversight roles without training</t>
         </is>
       </c>
     </row>
     <row r="44" ht="36" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>TPR-02</t>
+          <t>HUM-03</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Third-Party &amp; Supply Chain</t>
+          <t>Human Oversight &amp; Autonomy</t>
         </is>
       </c>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>Inadequate vendor transparency and assurance</t>
+          <t>Unbounded autonomous agent actions</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Vendor cannot provide documentation, testing evidence or incident information needed for compliance.</t>
+          <t>AI agents take high-impact actions (payments, communications, code execution) without adequate limits or approval.</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>EU AI Act Art. 25(4); ISO/IEC 42001 A.10.3</t>
+          <t>OWASP Agentic Top 10; Singapore Agentic AI framework</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>TP-1, TP-3, LC-6</t>
+          <t>LC-8</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>Vendors without current assurance evidence</t>
+          <t>High-impact agent actions without approval</t>
         </is>
       </c>
     </row>
     <row r="45" ht="36" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>TPR-03</t>
+          <t>HUM-04</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Third-Party &amp; Supply Chain</t>
+          <t>Human Oversight &amp; Autonomy</t>
         </is>
       </c>
       <c r="C45" s="13" t="inlineStr">
         <is>
-          <t>Vendor use of organisation data</t>
+          <t>Adverse workforce impact</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Provider uses prompts, outputs or client data to train models or retains data beyond agreed terms.</t>
+          <t>AI adoption causes skills erosion, job anxiety or unconsulted changes to working conditions.</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Contract / DPA; Bahrain PDPL</t>
+          <t>EU AI Act Art. 26(7); AI Ready7 3.4</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>TP-3, PR-6</t>
+          <t>RS-9, GL-4</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>Contracts lacking no-training clause</t>
+          <t>Staff sentiment / attrition in affected roles</t>
         </is>
       </c>
     </row>
     <row r="46" ht="36" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>OPS-01</t>
+          <t>TPR-01</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Operational, Financial &amp; Sustainability</t>
+          <t>Third-Party &amp; Supply Chain</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
         <is>
-          <t>AI service outage or degradation</t>
+          <t>Vendor lock-in and concentration</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Business processes dependent on AI are disrupted by service unavailability or latency.</t>
+          <t>Critical dependence on a single AI provider or cloud creates resilience and bargaining risk.</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>ISO/IEC 27001 A.5.30; CBB OM</t>
+          <t>ISO/IEC 42001 A.10; CBB outsourcing</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>OM-1, SE-1</t>
+          <t>TP-2, TP-3</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>AI service availability vs SLA</t>
+          <t>% critical AI workloads on single provider</t>
         </is>
       </c>
     </row>
     <row r="47" ht="36" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>OPS-02</t>
+          <t>TPR-02</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Operational, Financial &amp; Sustainability</t>
+          <t>Third-Party &amp; Supply Chain</t>
         </is>
       </c>
       <c r="C47" s="13" t="inlineStr">
         <is>
-          <t>Uncontrolled AI cost and consumption</t>
+          <t>Inadequate vendor transparency and assurance</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Compute and API spend escalate without governance (incl. denial-of-wallet attacks).</t>
+          <t>Vendor cannot provide documentation, testing evidence or incident information needed for compliance.</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>AI Ready7 4.5; OWASP LLM10:2025</t>
+          <t>EU AI Act Art. 25(4); ISO/IEC 42001 A.10.3</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>GL-6, SE-6</t>
+          <t>TP-1, TP-3, LC-6</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>AI spend vs budget</t>
+          <t>Vendors without current assurance evidence</t>
         </is>
       </c>
     </row>
     <row r="48" ht="36" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>OPS-03</t>
+          <t>TPR-03</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Operational, Financial &amp; Sustainability</t>
+          <t>Third-Party &amp; Supply Chain</t>
         </is>
       </c>
       <c r="C48" s="13" t="inlineStr">
         <is>
-          <t>Environmental impact of AI</t>
+          <t>Vendor use of organisation data</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Energy, water and carbon footprint of AI workloads conflicts with sustainability commitments.</t>
+          <t>Provider uses prompts, outputs or client data to train models or retains data beyond agreed terms.</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>ISO/IEC TR 20226; ISO/IEC 42001</t>
+          <t>Contract / DPA; Bahrain PDPL</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>RS-8</t>
+          <t>TP-3, PR-6</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>kgCO2e per 1,000 inferences</t>
+          <t>Contracts lacking no-training clause</t>
         </is>
       </c>
     </row>
     <row r="49" ht="36" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>SOC-01</t>
+          <t>OPS-01</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Societal, Reputational &amp; AI-Enabled Threats</t>
+          <t>Operational, Financial &amp; Sustainability</t>
         </is>
       </c>
       <c r="C49" s="13" t="inlineStr">
         <is>
-          <t>Harmful, toxic or unsafe content</t>
+          <t>AI service outage or degradation</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>AI generates offensive, dangerous or culturally inappropriate content.</t>
+          <t>Business processes dependent on AI are disrupted by service unavailability or latency.</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>NIST AI 600-1; GCC AI Ethics Manual</t>
+          <t>ISO/IEC 27001 A.5.30; CBB OM</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>RS-2, SE-6</t>
+          <t>OM-1, SE-1</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>Content-policy violations per 1,000 outputs</t>
+          <t>AI service availability vs SLA</t>
         </is>
       </c>
     </row>
     <row r="50" ht="36" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>SOC-02</t>
+          <t>OPS-02</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Societal, Reputational &amp; AI-Enabled Threats</t>
+          <t>Operational, Financial &amp; Sustainability</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr">
         <is>
-          <t>Misinformation and loss of stakeholder trust</t>
+          <t>Uncontrolled AI cost and consumption</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>AI-generated errors or undisclosed AI use damage client, regulator or public trust.</t>
+          <t>Compute and API spend escalate without governance (incl. denial-of-wallet attacks).</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>NIST AI 600-1 (Information integrity); AI Ready7 1.4</t>
+          <t>AI Ready7 4.5; OWASP LLM10:2025</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>LC-7, CO-1, CO-2</t>
+          <t>GL-6, SE-6</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>Client complaints linked to AI</t>
+          <t>AI spend vs budget</t>
         </is>
       </c>
     </row>
     <row r="51" ht="36" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>SOC-03</t>
+          <t>OPS-04</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Societal, Reputational &amp; AI-Enabled Threats</t>
+          <t>Operational, Financial &amp; Sustainability</t>
         </is>
       </c>
       <c r="C51" s="13" t="inlineStr">
         <is>
-          <t>Deepfake and AI-enabled fraud against the organisation</t>
+          <t>No safe degradation or kill switch</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Voice/video impersonation or AI-crafted phishing leads to fraudulent payments or data release.</t>
+          <t>A failing or compromised AI system cannot be stopped quickly or the business process cannot revert to manual operation.</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>FinCEN FIN-2024-Alert004; AI Ready7 7.3</t>
+          <t>ISACA Securing AI Agents (2026); ISO 22301</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>AT-3, GL-4</t>
+          <t>OM-4</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>Deepfake / BEC attempts detected</t>
+          <t>Kill-switch test age (days)</t>
         </is>
       </c>
     </row>
     <row r="52" ht="36" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
+          <t>OPS-03</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>Operational, Financial &amp; Sustainability</t>
+        </is>
+      </c>
+      <c r="C52" s="13" t="inlineStr">
+        <is>
+          <t>Environmental impact of AI</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>Energy, water and carbon footprint of AI workloads conflicts with sustainability commitments.</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>ISO/IEC TR 20226; ISO/IEC 42001</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>RS-8</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>kgCO2e per 1,000 inferences</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="36" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>SOC-01</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>Societal, Reputational &amp; AI-Enabled Threats</t>
+        </is>
+      </c>
+      <c r="C53" s="13" t="inlineStr">
+        <is>
+          <t>Harmful, toxic or unsafe content</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>AI generates offensive, dangerous or culturally inappropriate content.</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>NIST AI 600-1; GCC AI Ethics Manual</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>RS-2, SE-6</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>Content-policy violations per 1,000 outputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="36" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>SOC-02</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>Societal, Reputational &amp; AI-Enabled Threats</t>
+        </is>
+      </c>
+      <c r="C54" s="13" t="inlineStr">
+        <is>
+          <t>Misinformation and loss of stakeholder trust</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>AI-generated errors or undisclosed AI use damage client, regulator or public trust.</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>NIST AI 600-1 (Information integrity); AI Ready7 1.4</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>LC-7, CO-1, CO-2</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>Client complaints linked to AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="36" customHeight="1">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>SOC-03</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Societal, Reputational &amp; AI-Enabled Threats</t>
+        </is>
+      </c>
+      <c r="C55" s="13" t="inlineStr">
+        <is>
+          <t>Deepfake and AI-enabled fraud against the organisation</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>Voice/video impersonation or AI-crafted phishing leads to fraudulent payments or data release.</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>FinCEN FIN-2024-Alert004; AI Ready7 7.3</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>AT-3, GL-4</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>Deepfake / BEC attempts detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="36" customHeight="1">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
           <t>SOC-04</t>
         </is>
       </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>Societal, Reputational &amp; AI-Enabled Threats</t>
         </is>
       </c>
-      <c r="C52" s="13" t="inlineStr">
+      <c r="C56" s="13" t="inlineStr">
         <is>
           <t>AI-accelerated cyber attacks</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="D56" s="4" t="inlineStr">
         <is>
           <t>Adversaries use AI for automated discovery, exploit chaining and scaled social engineering, outpacing defences.</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
+      <c r="E56" s="4" t="inlineStr">
         <is>
           <t>AI Ready7 7.1-7.5; MITRE ATLAS</t>
         </is>
       </c>
-      <c r="F52" s="4" t="inlineStr">
+      <c r="F56" s="4" t="inlineStr">
         <is>
           <t>AT-1, AT-2, AT-4</t>
         </is>
       </c>
-      <c r="G52" s="4" t="inlineStr">
+      <c r="G56" s="4" t="inlineStr">
         <is>
           <t>Mean time to remediate critical vulnerabilities</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G52"/>
+  <autoFilter ref="A4:G56"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <printOptions gridLines="0"/>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.25" footer="0.25"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -10624,8 +11118,9 @@
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="C35:E35"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <printOptions gridLines="0"/>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.25" footer="0.25"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 

--- a/01_AI_Governance_Risk_Compliance/1.2_AI_Risk_Assessment_Framework/GT_AI_Risk_Assessment_Toolkit_Worked_Example.xlsx
+++ b/01_AI_Governance_Risk_Compliance/1.2_AI_Risk_Assessment_Framework/GT_AI_Risk_Assessment_Toolkit_Worked_Example.xlsx
@@ -1573,9 +1573,9 @@
           <t>Screening result</t>
         </is>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="11" t="str">
         <f>IF(COUNTA(C5:C12)&lt;8,"Incomplete",IF(COUNTIF(C5:C12,"Yes")&gt;0,"PROHIBITED","Pass"))</f>
-        <v/>
+        <v>Pass</v>
       </c>
       <c r="D14" s="12" t="n"/>
     </row>
@@ -1687,14 +1687,14 @@
       </c>
       <c r="D5" s="9">
         <f>IF(C5="","",MATCH(C5,Lists!$L$1:$L$5,0)-1)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="E5" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F5" s="9">
         <f>IF(D5="","",D5*E5)</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
@@ -1715,14 +1715,14 @@
       </c>
       <c r="D6" s="9">
         <f>IF(C6="","",MATCH(C6,Lists!$M$1:$M$5,0)-1)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="E6" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F6" s="9">
         <f>IF(D6="","",D6*E6)</f>
-        <v/>
+        <v>9</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
@@ -1743,14 +1743,14 @@
       </c>
       <c r="D7" s="9">
         <f>IF(C7="","",MATCH(C7,Lists!$N$1:$N$5,0)-1)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="E7" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="9">
         <f>IF(D7="","",D7*E7)</f>
-        <v/>
+        <v>8</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
@@ -1771,14 +1771,14 @@
       </c>
       <c r="D8" s="9">
         <f>IF(C8="","",MATCH(C8,Lists!$O$1:$O$5,0)-1)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="E8" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="9">
         <f>IF(D8="","",D8*E8)</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
@@ -1799,14 +1799,14 @@
       </c>
       <c r="D9" s="9">
         <f>IF(C9="","",MATCH(C9,Lists!$P$1:$P$5,0)-1)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="E9" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="9">
         <f>IF(D9="","",D9*E9)</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
@@ -1827,14 +1827,14 @@
       </c>
       <c r="D10" s="9">
         <f>IF(C10="","",MATCH(C10,Lists!$Q$1:$Q$5,0)-1)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="E10" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F10" s="9">
         <f>IF(D10="","",D10*E10)</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
@@ -1855,14 +1855,14 @@
       </c>
       <c r="D11" s="9">
         <f>IF(C11="","",MATCH(C11,Lists!$R$1:$R$5,0)-1)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="E11" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F11" s="9">
         <f>IF(D11="","",D11*E11)</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1">
@@ -1883,14 +1883,14 @@
       </c>
       <c r="D12" s="9">
         <f>IF(C12="","",MATCH(C12,Lists!$S$1:$S$5,0)-1)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="E12" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="9">
         <f>IF(D12="","",D12*E12)</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1">
@@ -1911,14 +1911,14 @@
       </c>
       <c r="D13" s="9">
         <f>IF(C13="","",MATCH(C13,Lists!$T$1:$T$5,0)-1)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="E13" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="9">
         <f>IF(D13="","",D13*E13)</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1">
@@ -1939,14 +1939,14 @@
       </c>
       <c r="D14" s="9">
         <f>IF(C14="","",MATCH(C14,Lists!$U$1:$U$5,0)-1)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="E14" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="9">
         <f>IF(D14="","",D14*E14)</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -1955,9 +1955,9 @@
           <t>Factors answered</t>
         </is>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="14" t="str">
         <f>COUNT(D5:D14)&amp;" of 10"</f>
-        <v/>
+        <v>10 of 10</v>
       </c>
       <c r="D16" s="15" t="n"/>
       <c r="E16" s="15" t="n"/>
@@ -1971,7 +1971,7 @@
       </c>
       <c r="C17" s="14">
         <f>IF(COUNT(D5:D14)&lt;10,"",ROUND(SUM(F5:F14)/(4*SUM(E5:E14))*100,0))</f>
-        <v/>
+        <v>74</v>
       </c>
       <c r="D17" s="15" t="n"/>
       <c r="E17" s="15" t="n"/>
@@ -1983,9 +1983,9 @@
           <t>Score-based tier</t>
         </is>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="14" t="str">
         <f>IF(C17="","",IF(C17&gt;=75,"Critical",IF(C17&gt;=50,"High",IF(C17&gt;=25,"Medium","Low"))))</f>
-        <v/>
+        <v>High</v>
       </c>
       <c r="D18" s="15" t="n"/>
       <c r="E18" s="15" t="n"/>
@@ -1997,9 +1997,9 @@
           <t>Override triggered</t>
         </is>
       </c>
-      <c r="C19" s="14">
+      <c r="C19" s="14" t="str">
         <f>IF(C17="","",IF(AND(D5=4,D6=4),"Critical - significant decisions made autonomously",IF(OR(D5=4,D11=4),"Min. High - significant-effect decisions or high-risk classification",IF(AND(D5&gt;=3,D6&gt;=3),"Min. High - material decisions with limited oversight",IF(D7=4,"Min. Medium - sensitive data","None")))))</f>
-        <v/>
+        <v>Min. Medium - sensitive data</v>
       </c>
       <c r="D19" s="15" t="n"/>
       <c r="E19" s="15" t="n"/>
@@ -2011,9 +2011,9 @@
           <t>Prohibited-practice screen</t>
         </is>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="14" t="str">
         <f>'2. Prohibited Screen'!C14</f>
-        <v/>
+        <v>Pass</v>
       </c>
       <c r="D20" s="15" t="n"/>
       <c r="E20" s="15" t="n"/>
@@ -2025,9 +2025,9 @@
           <t>FINAL INHERENT RISK TIER</t>
         </is>
       </c>
-      <c r="C21" s="16">
+      <c r="C21" s="16" t="str">
         <f>IF(C20="PROHIBITED","Prohibited",IF(C17="","Incomplete",IF(LEFT(C19,8)="Critical","Critical",IF(AND(LEFT(C19,9)="Min. High",C18&lt;&gt;"Critical"),"High",IF(AND(LEFT(C19,11)="Min. Medium",C18="Low"),"Medium",C18)))))</f>
-        <v/>
+        <v>High</v>
       </c>
       <c r="D21" s="15" t="n"/>
       <c r="E21" s="15" t="n"/>
@@ -2039,9 +2039,9 @@
           <t>Assessment requirements</t>
         </is>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="14" t="str">
         <f>IFERROR(VLOOKUP(C21,Scales!$A$36:$H$39,3,FALSE),IF(C21="Prohibited","Do not proceed. Refer to Legal and AI Committee.",""))</f>
-        <v/>
+        <v>Full risk &amp; impact assessment (ISO/IEC 42005 / FRIA where required); independent validation; AI Committee approval.</v>
       </c>
       <c r="D22" s="15" t="n"/>
       <c r="E22" s="15" t="n"/>
@@ -2053,9 +2053,9 @@
           <t>Approval authority</t>
         </is>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="14" t="str">
         <f>IFERROR(VLOOKUP(C21,Scales!$A$36:$H$39,6,FALSE),IF(C21="Prohibited","Legal + Executive Committee",""))</f>
-        <v/>
+        <v>AI Committee / CoE</v>
       </c>
       <c r="D23" s="15" t="n"/>
       <c r="E23" s="15" t="n"/>
@@ -2067,9 +2067,9 @@
           <t>Review frequency</t>
         </is>
       </c>
-      <c r="C24" s="14">
+      <c r="C24" s="14" t="str">
         <f>IFERROR(VLOOKUP(C21,Scales!$A$36:$H$39,8,FALSE),"")</f>
-        <v/>
+        <v>Every 6 months + continuous KRI monitoring</v>
       </c>
       <c r="D24" s="15" t="n"/>
       <c r="E24" s="15" t="n"/>
@@ -2338,11 +2338,11 @@
       </c>
       <c r="F5" s="17" t="n"/>
       <c r="G5" s="17" t="n"/>
-      <c r="H5" s="9">
+      <c r="H5" s="9" t="str">
         <f>IF(OR($A5&lt;&gt;"Yes",F5="",G5=""),"",MATCH(F5,Lists!$B$1:$B$5,0)*MATCH(G5,Lists!$C$1:$C$5,0))</f>
         <v/>
       </c>
-      <c r="I5" s="9">
+      <c r="I5" s="9" t="str">
         <f>IF(H5="","",IF(H5&gt;=17,"Critical",IF(H5&gt;=10,"High",IF(H5&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
@@ -2352,15 +2352,15 @@
         </is>
       </c>
       <c r="K5" s="17" t="n"/>
-      <c r="L5" s="9">
+      <c r="L5" s="9" t="str">
         <f>IF(OR(H5="",K5=""),"",ROUND(H5*VLOOKUP(K5,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
       </c>
-      <c r="M5" s="9">
+      <c r="M5" s="9" t="str">
         <f>IF(L5="","",IF(L5&gt;=17,"Critical",IF(L5&gt;=10,"High",IF(L5&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="N5" s="9">
+      <c r="N5" s="9" t="str">
         <f>IF(M5="","",IF(OR(M5="Low",M5="Medium"),"Yes","No"))</f>
         <v/>
       </c>
@@ -2374,7 +2374,7 @@
           <t>% AI systems in register without named owner</t>
         </is>
       </c>
-      <c r="V5">
+      <c r="V5" t="str">
         <f>IF(L5="","",L5+ROW()/100000)</f>
         <v/>
       </c>
@@ -2407,11 +2407,11 @@
       </c>
       <c r="F6" s="17" t="n"/>
       <c r="G6" s="17" t="n"/>
-      <c r="H6" s="9">
+      <c r="H6" s="9" t="str">
         <f>IF(OR($A6&lt;&gt;"Yes",F6="",G6=""),"",MATCH(F6,Lists!$B$1:$B$5,0)*MATCH(G6,Lists!$C$1:$C$5,0))</f>
         <v/>
       </c>
-      <c r="I6" s="9">
+      <c r="I6" s="9" t="str">
         <f>IF(H6="","",IF(H6&gt;=17,"Critical",IF(H6&gt;=10,"High",IF(H6&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
@@ -2421,15 +2421,15 @@
         </is>
       </c>
       <c r="K6" s="17" t="n"/>
-      <c r="L6" s="9">
+      <c r="L6" s="9" t="str">
         <f>IF(OR(H6="",K6=""),"",ROUND(H6*VLOOKUP(K6,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
       </c>
-      <c r="M6" s="9">
+      <c r="M6" s="9" t="str">
         <f>IF(L6="","",IF(L6&gt;=17,"Critical",IF(L6&gt;=10,"High",IF(L6&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="N6" s="9">
+      <c r="N6" s="9" t="str">
         <f>IF(M6="","",IF(OR(M6="Low",M6="Medium"),"Yes","No"))</f>
         <v/>
       </c>
@@ -2443,7 +2443,7 @@
           <t>Unsanctioned AI services detected per month</t>
         </is>
       </c>
-      <c r="V6">
+      <c r="V6" t="str">
         <f>IF(L6="","",L6+ROW()/100000)</f>
         <v/>
       </c>
@@ -2486,11 +2486,11 @@
       </c>
       <c r="H7" s="9">
         <f>IF(OR($A7&lt;&gt;"Yes",F7="",G7=""),"",MATCH(F7,Lists!$B$1:$B$5,0)*MATCH(G7,Lists!$C$1:$C$5,0))</f>
-        <v/>
-      </c>
-      <c r="I7" s="9">
+        <v>12</v>
+      </c>
+      <c r="I7" s="9" t="str">
         <f>IF(H7="","",IF(H7&gt;=17,"Critical",IF(H7&gt;=10,"High",IF(H7&gt;=5,"Medium","Low"))))</f>
-        <v/>
+        <v>High</v>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
@@ -2504,15 +2504,15 @@
       </c>
       <c r="L7" s="9">
         <f>IF(OR(H7="",K7=""),"",ROUND(H7*VLOOKUP(K7,Scales!$A$22:$B$25,2,FALSE),1))</f>
-        <v/>
-      </c>
-      <c r="M7" s="9">
+        <v>7.2</v>
+      </c>
+      <c r="M7" s="9" t="str">
         <f>IF(L7="","",IF(L7&gt;=17,"Critical",IF(L7&gt;=10,"High",IF(L7&gt;=5,"Medium","Low"))))</f>
-        <v/>
-      </c>
-      <c r="N7" s="9">
+        <v>Medium</v>
+      </c>
+      <c r="N7" s="9" t="str">
         <f>IF(M7="","",IF(OR(M7="Low",M7="Medium"),"Yes","No"))</f>
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="O7" s="17" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="V7">
         <f>IF(L7="","",L7+ROW()/100000)</f>
-        <v/>
+        <v>7.20007</v>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1">
@@ -2573,11 +2573,11 @@
       </c>
       <c r="F8" s="17" t="n"/>
       <c r="G8" s="17" t="n"/>
-      <c r="H8" s="9">
+      <c r="H8" s="9" t="str">
         <f>IF(OR($A8&lt;&gt;"Yes",F8="",G8=""),"",MATCH(F8,Lists!$B$1:$B$5,0)*MATCH(G8,Lists!$C$1:$C$5,0))</f>
         <v/>
       </c>
-      <c r="I8" s="9">
+      <c r="I8" s="9" t="str">
         <f>IF(H8="","",IF(H8&gt;=17,"Critical",IF(H8&gt;=10,"High",IF(H8&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
@@ -2587,15 +2587,15 @@
         </is>
       </c>
       <c r="K8" s="17" t="n"/>
-      <c r="L8" s="9">
+      <c r="L8" s="9" t="str">
         <f>IF(OR(H8="",K8=""),"",ROUND(H8*VLOOKUP(K8,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
       </c>
-      <c r="M8" s="9">
+      <c r="M8" s="9" t="str">
         <f>IF(L8="","",IF(L8&gt;=17,"Critical",IF(L8&gt;=10,"High",IF(L8&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="N8" s="9">
+      <c r="N8" s="9" t="str">
         <f>IF(M8="","",IF(OR(M8="Low",M8="Medium"),"Yes","No"))</f>
         <v/>
       </c>
@@ -2609,7 +2609,7 @@
           <t>% AI initiatives meeting benefit KPIs</t>
         </is>
       </c>
-      <c r="V8">
+      <c r="V8" t="str">
         <f>IF(L8="","",L8+ROW()/100000)</f>
         <v/>
       </c>
@@ -2642,11 +2642,11 @@
       </c>
       <c r="F9" s="17" t="n"/>
       <c r="G9" s="17" t="n"/>
-      <c r="H9" s="9">
+      <c r="H9" s="9" t="str">
         <f>IF(OR($A9&lt;&gt;"Yes",F9="",G9=""),"",MATCH(F9,Lists!$B$1:$B$5,0)*MATCH(G9,Lists!$C$1:$C$5,0))</f>
         <v/>
       </c>
-      <c r="I9" s="9">
+      <c r="I9" s="9" t="str">
         <f>IF(H9="","",IF(H9&gt;=17,"Critical",IF(H9&gt;=10,"High",IF(H9&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
@@ -2656,15 +2656,15 @@
         </is>
       </c>
       <c r="K9" s="17" t="n"/>
-      <c r="L9" s="9">
+      <c r="L9" s="9" t="str">
         <f>IF(OR(H9="",K9=""),"",ROUND(H9*VLOOKUP(K9,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
       </c>
-      <c r="M9" s="9">
+      <c r="M9" s="9" t="str">
         <f>IF(L9="","",IF(L9&gt;=17,"Critical",IF(L9&gt;=10,"High",IF(L9&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="N9" s="9">
+      <c r="N9" s="9" t="str">
         <f>IF(M9="","",IF(OR(M9="Low",M9="Medium"),"Yes","No"))</f>
         <v/>
       </c>
@@ -2678,7 +2678,7 @@
           <t>Number of use cases failing prohibited-practice screen</t>
         </is>
       </c>
-      <c r="V9">
+      <c r="V9" t="str">
         <f>IF(L9="","",L9+ROW()/100000)</f>
         <v/>
       </c>
@@ -2721,11 +2721,11 @@
       </c>
       <c r="H10" s="9">
         <f>IF(OR($A10&lt;&gt;"Yes",F10="",G10=""),"",MATCH(F10,Lists!$B$1:$B$5,0)*MATCH(G10,Lists!$C$1:$C$5,0))</f>
-        <v/>
-      </c>
-      <c r="I10" s="9">
+        <v>8</v>
+      </c>
+      <c r="I10" s="9" t="str">
         <f>IF(H10="","",IF(H10&gt;=17,"Critical",IF(H10&gt;=10,"High",IF(H10&gt;=5,"Medium","Low"))))</f>
-        <v/>
+        <v>Medium</v>
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
@@ -2739,15 +2739,15 @@
       </c>
       <c r="L10" s="9">
         <f>IF(OR(H10="",K10=""),"",ROUND(H10*VLOOKUP(K10,Scales!$A$22:$B$25,2,FALSE),1))</f>
-        <v/>
-      </c>
-      <c r="M10" s="9">
+        <v>4.8</v>
+      </c>
+      <c r="M10" s="9" t="str">
         <f>IF(L10="","",IF(L10&gt;=17,"Critical",IF(L10&gt;=10,"High",IF(L10&gt;=5,"Medium","Low"))))</f>
-        <v/>
-      </c>
-      <c r="N10" s="9">
+        <v>Low</v>
+      </c>
+      <c r="N10" s="9" t="str">
         <f>IF(M10="","",IF(OR(M10="Low",M10="Medium"),"Yes","No"))</f>
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="O10" s="17" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="V10">
         <f>IF(L10="","",L10+ROW()/100000)</f>
-        <v/>
+        <v>4.8001</v>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1">
@@ -2818,11 +2818,11 @@
       </c>
       <c r="H11" s="9">
         <f>IF(OR($A11&lt;&gt;"Yes",F11="",G11=""),"",MATCH(F11,Lists!$B$1:$B$5,0)*MATCH(G11,Lists!$C$1:$C$5,0))</f>
-        <v/>
-      </c>
-      <c r="I11" s="9">
+        <v>12</v>
+      </c>
+      <c r="I11" s="9" t="str">
         <f>IF(H11="","",IF(H11&gt;=17,"Critical",IF(H11&gt;=10,"High",IF(H11&gt;=5,"Medium","Low"))))</f>
-        <v/>
+        <v>High</v>
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
@@ -2836,15 +2836,15 @@
       </c>
       <c r="L11" s="9">
         <f>IF(OR(H11="",K11=""),"",ROUND(H11*VLOOKUP(K11,Scales!$A$22:$B$25,2,FALSE),1))</f>
-        <v/>
-      </c>
-      <c r="M11" s="9">
+        <v>9.6</v>
+      </c>
+      <c r="M11" s="9" t="str">
         <f>IF(L11="","",IF(L11&gt;=17,"Critical",IF(L11&gt;=10,"High",IF(L11&gt;=5,"Medium","Low"))))</f>
-        <v/>
-      </c>
-      <c r="N11" s="9">
+        <v>Medium</v>
+      </c>
+      <c r="N11" s="9" t="str">
         <f>IF(M11="","",IF(OR(M11="Low",M11="Medium"),"Yes","No"))</f>
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="O11" s="17" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="V11">
         <f>IF(L11="","",L11+ROW()/100000)</f>
-        <v/>
+        <v>9.60011</v>
       </c>
     </row>
     <row r="12" ht="44" customHeight="1">
@@ -2905,11 +2905,11 @@
       </c>
       <c r="F12" s="17" t="n"/>
       <c r="G12" s="17" t="n"/>
-      <c r="H12" s="9">
+      <c r="H12" s="9" t="str">
         <f>IF(OR($A12&lt;&gt;"Yes",F12="",G12=""),"",MATCH(F12,Lists!$B$1:$B$5,0)*MATCH(G12,Lists!$C$1:$C$5,0))</f>
         <v/>
       </c>
-      <c r="I12" s="9">
+      <c r="I12" s="9" t="str">
         <f>IF(H12="","",IF(H12&gt;=17,"Critical",IF(H12&gt;=10,"High",IF(H12&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
@@ -2919,15 +2919,15 @@
         </is>
       </c>
       <c r="K12" s="17" t="n"/>
-      <c r="L12" s="9">
+      <c r="L12" s="9" t="str">
         <f>IF(OR(H12="",K12=""),"",ROUND(H12*VLOOKUP(K12,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
       </c>
-      <c r="M12" s="9">
+      <c r="M12" s="9" t="str">
         <f>IF(L12="","",IF(L12&gt;=17,"Critical",IF(L12&gt;=10,"High",IF(L12&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="N12" s="9">
+      <c r="N12" s="9" t="str">
         <f>IF(M12="","",IF(OR(M12="Low",M12="Medium"),"Yes","No"))</f>
         <v/>
       </c>
@@ -2941,7 +2941,7 @@
           <t>IP complaints / takedown requests</t>
         </is>
       </c>
-      <c r="V12">
+      <c r="V12" t="str">
         <f>IF(L12="","",L12+ROW()/100000)</f>
         <v/>
       </c>
@@ -2974,11 +2974,11 @@
       </c>
       <c r="F13" s="17" t="n"/>
       <c r="G13" s="17" t="n"/>
-      <c r="H13" s="9">
+      <c r="H13" s="9" t="str">
         <f>IF(OR($A13&lt;&gt;"Yes",F13="",G13=""),"",MATCH(F13,Lists!$B$1:$B$5,0)*MATCH(G13,Lists!$C$1:$C$5,0))</f>
         <v/>
       </c>
-      <c r="I13" s="9">
+      <c r="I13" s="9" t="str">
         <f>IF(H13="","",IF(H13&gt;=17,"Critical",IF(H13&gt;=10,"High",IF(H13&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
@@ -2988,15 +2988,15 @@
         </is>
       </c>
       <c r="K13" s="17" t="n"/>
-      <c r="L13" s="9">
+      <c r="L13" s="9" t="str">
         <f>IF(OR(H13="",K13=""),"",ROUND(H13*VLOOKUP(K13,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
       </c>
-      <c r="M13" s="9">
+      <c r="M13" s="9" t="str">
         <f>IF(L13="","",IF(L13&gt;=17,"Critical",IF(L13&gt;=10,"High",IF(L13&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="N13" s="9">
+      <c r="N13" s="9" t="str">
         <f>IF(M13="","",IF(OR(M13="Low",M13="Medium"),"Yes","No"))</f>
         <v/>
       </c>
@@ -3010,7 +3010,7 @@
           <t>Claims / complaints attributed to AI</t>
         </is>
       </c>
-      <c r="V13">
+      <c r="V13" t="str">
         <f>IF(L13="","",L13+ROW()/100000)</f>
         <v/>
       </c>
@@ -3043,11 +3043,11 @@
       </c>
       <c r="F14" s="17" t="n"/>
       <c r="G14" s="17" t="n"/>
-      <c r="H14" s="9">
+      <c r="H14" s="9" t="str">
         <f>IF(OR($A14&lt;&gt;"Yes",F14="",G14=""),"",MATCH(F14,Lists!$B$1:$B$5,0)*MATCH(G14,Lists!$C$1:$C$5,0))</f>
         <v/>
       </c>
-      <c r="I14" s="9">
+      <c r="I14" s="9" t="str">
         <f>IF(H14="","",IF(H14&gt;=17,"Critical",IF(H14&gt;=10,"High",IF(H14&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
@@ -3057,15 +3057,15 @@
         </is>
       </c>
       <c r="K14" s="17" t="n"/>
-      <c r="L14" s="9">
+      <c r="L14" s="9" t="str">
         <f>IF(OR(H14="",K14=""),"",ROUND(H14*VLOOKUP(K14,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
       </c>
-      <c r="M14" s="9">
+      <c r="M14" s="9" t="str">
         <f>IF(L14="","",IF(L14&gt;=17,"Critical",IF(L14&gt;=10,"High",IF(L14&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="N14" s="9">
+      <c r="N14" s="9" t="str">
         <f>IF(M14="","",IF(OR(M14="Low",M14="Medium"),"Yes","No"))</f>
         <v/>
       </c>
@@ -3079,7 +3079,7 @@
           <t>Disparate impact ratio across cohorts</t>
         </is>
       </c>
-      <c r="V14">
+      <c r="V14" t="str">
         <f>IF(L14="","",L14+ROW()/100000)</f>
         <v/>
       </c>
@@ -3122,11 +3122,11 @@
       </c>
       <c r="H15" s="9">
         <f>IF(OR($A15&lt;&gt;"Yes",F15="",G15=""),"",MATCH(F15,Lists!$B$1:$B$5,0)*MATCH(G15,Lists!$C$1:$C$5,0))</f>
-        <v/>
-      </c>
-      <c r="I15" s="9">
+        <v>9</v>
+      </c>
+      <c r="I15" s="9" t="str">
         <f>IF(H15="","",IF(H15&gt;=17,"Critical",IF(H15&gt;=10,"High",IF(H15&gt;=5,"Medium","Low"))))</f>
-        <v/>
+        <v>Medium</v>
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
@@ -3140,15 +3140,15 @@
       </c>
       <c r="L15" s="9">
         <f>IF(OR(H15="",K15=""),"",ROUND(H15*VLOOKUP(K15,Scales!$A$22:$B$25,2,FALSE),1))</f>
-        <v/>
-      </c>
-      <c r="M15" s="9">
+        <v>7.2</v>
+      </c>
+      <c r="M15" s="9" t="str">
         <f>IF(L15="","",IF(L15&gt;=17,"Critical",IF(L15&gt;=10,"High",IF(L15&gt;=5,"Medium","Low"))))</f>
-        <v/>
-      </c>
-      <c r="N15" s="9">
+        <v>Medium</v>
+      </c>
+      <c r="N15" s="9" t="str">
         <f>IF(M15="","",IF(OR(M15="Low",M15="Medium"),"Yes","No"))</f>
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="O15" s="17" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
       </c>
       <c r="V15">
         <f>IF(L15="","",L15+ROW()/100000)</f>
-        <v/>
+        <v>7.20015</v>
       </c>
     </row>
     <row r="16" ht="44" customHeight="1">
@@ -3209,11 +3209,11 @@
       </c>
       <c r="F16" s="17" t="n"/>
       <c r="G16" s="17" t="n"/>
-      <c r="H16" s="9">
+      <c r="H16" s="9" t="str">
         <f>IF(OR($A16&lt;&gt;"Yes",F16="",G16=""),"",MATCH(F16,Lists!$B$1:$B$5,0)*MATCH(G16,Lists!$C$1:$C$5,0))</f>
         <v/>
       </c>
-      <c r="I16" s="9">
+      <c r="I16" s="9" t="str">
         <f>IF(H16="","",IF(H16&gt;=17,"Critical",IF(H16&gt;=10,"High",IF(H16&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
@@ -3223,15 +3223,15 @@
         </is>
       </c>
       <c r="K16" s="17" t="n"/>
-      <c r="L16" s="9">
+      <c r="L16" s="9" t="str">
         <f>IF(OR(H16="",K16=""),"",ROUND(H16*VLOOKUP(K16,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
       </c>
-      <c r="M16" s="9">
+      <c r="M16" s="9" t="str">
         <f>IF(L16="","",IF(L16&gt;=17,"Critical",IF(L16&gt;=10,"High",IF(L16&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="N16" s="9">
+      <c r="N16" s="9" t="str">
         <f>IF(M16="","",IF(OR(M16="Low",M16="Medium"),"Yes","No"))</f>
         <v/>
       </c>
@@ -3245,7 +3245,7 @@
           <t>FRIAs outstanding for in-scope systems</t>
         </is>
       </c>
-      <c r="V16">
+      <c r="V16" t="str">
         <f>IF(L16="","",L16+ROW()/100000)</f>
         <v/>
       </c>
@@ -3278,11 +3278,11 @@
       </c>
       <c r="F17" s="17" t="n"/>
       <c r="G17" s="17" t="n"/>
-      <c r="H17" s="9">
+      <c r="H17" s="9" t="str">
         <f>IF(OR($A17&lt;&gt;"Yes",F17="",G17=""),"",MATCH(F17,Lists!$B$1:$B$5,0)*MATCH(G17,Lists!$C$1:$C$5,0))</f>
         <v/>
       </c>
-      <c r="I17" s="9">
+      <c r="I17" s="9" t="str">
         <f>IF(H17="","",IF(H17&gt;=17,"Critical",IF(H17&gt;=10,"High",IF(H17&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
@@ -3292,15 +3292,15 @@
         </is>
       </c>
       <c r="K17" s="17" t="n"/>
-      <c r="L17" s="9">
+      <c r="L17" s="9" t="str">
         <f>IF(OR(H17="",K17=""),"",ROUND(H17*VLOOKUP(K17,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
       </c>
-      <c r="M17" s="9">
+      <c r="M17" s="9" t="str">
         <f>IF(L17="","",IF(L17&gt;=17,"Critical",IF(L17&gt;=10,"High",IF(L17&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="N17" s="9">
+      <c r="N17" s="9" t="str">
         <f>IF(M17="","",IF(OR(M17="Low",M17="Medium"),"Yes","No"))</f>
         <v/>
       </c>
@@ -3314,7 +3314,7 @@
           <t>Accessibility defects open</t>
         </is>
       </c>
-      <c r="V17">
+      <c r="V17" t="str">
         <f>IF(L17="","",L17+ROW()/100000)</f>
         <v/>
       </c>
@@ -3347,11 +3347,11 @@
       </c>
       <c r="F18" s="17" t="n"/>
       <c r="G18" s="17" t="n"/>
-      <c r="H18" s="9">
+      <c r="H18" s="9" t="str">
         <f>IF(OR($A18&lt;&gt;"Yes",F18="",G18=""),"",MATCH(F18,Lists!$B$1:$B$5,0)*MATCH(G18,Lists!$C$1:$C$5,0))</f>
         <v/>
       </c>
-      <c r="I18" s="9">
+      <c r="I18" s="9" t="str">
         <f>IF(H18="","",IF(H18&gt;=17,"Critical",IF(H18&gt;=10,"High",IF(H18&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
@@ -3361,15 +3361,15 @@
         </is>
       </c>
       <c r="K18" s="17" t="n"/>
-      <c r="L18" s="9">
+      <c r="L18" s="9" t="str">
         <f>IF(OR(H18="",K18=""),"",ROUND(H18*VLOOKUP(K18,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
       </c>
-      <c r="M18" s="9">
+      <c r="M18" s="9" t="str">
         <f>IF(L18="","",IF(L18&gt;=17,"Critical",IF(L18&gt;=10,"High",IF(L18&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="N18" s="9">
+      <c r="N18" s="9" t="str">
         <f>IF(M18="","",IF(OR(M18="Low",M18="Medium"),"Yes","No"))</f>
         <v/>
       </c>
@@ -3383,7 +3383,7 @@
           <t>AI systems processing personal data without DPIA</t>
         </is>
       </c>
-      <c r="V18">
+      <c r="V18" t="str">
         <f>IF(L18="","",L18+ROW()/100000)</f>
         <v/>
       </c>
@@ -3426,11 +3426,11 @@
       </c>
       <c r="H19" s="9">
         <f>IF(OR($A19&lt;&gt;"Yes",F19="",G19=""),"",MATCH(F19,Lists!$B$1:$B$5,0)*MATCH(G19,Lists!$C$1:$C$5,0))</f>
-        <v/>
-      </c>
-      <c r="I19" s="9">
+        <v>16</v>
+      </c>
+      <c r="I19" s="9" t="str">
         <f>IF(H19="","",IF(H19&gt;=17,"Critical",IF(H19&gt;=10,"High",IF(H19&gt;=5,"Medium","Low"))))</f>
-        <v/>
+        <v>High</v>
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
@@ -3444,15 +3444,15 @@
       </c>
       <c r="L19" s="9">
         <f>IF(OR(H19="",K19=""),"",ROUND(H19*VLOOKUP(K19,Scales!$A$22:$B$25,2,FALSE),1))</f>
-        <v/>
-      </c>
-      <c r="M19" s="9">
+        <v>12.8</v>
+      </c>
+      <c r="M19" s="9" t="str">
         <f>IF(L19="","",IF(L19&gt;=17,"Critical",IF(L19&gt;=10,"High",IF(L19&gt;=5,"Medium","Low"))))</f>
-        <v/>
-      </c>
-      <c r="N19" s="9">
+        <v>High</v>
+      </c>
+      <c r="N19" s="9" t="str">
         <f>IF(M19="","",IF(OR(M19="Low",M19="Medium"),"Yes","No"))</f>
-        <v/>
+        <v>No</v>
       </c>
       <c r="O19" s="17" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="V19">
         <f>IF(L19="","",L19+ROW()/100000)</f>
-        <v/>
+        <v>12.80019</v>
       </c>
     </row>
     <row r="20" ht="44" customHeight="1">
@@ -3523,11 +3523,11 @@
       </c>
       <c r="H20" s="9">
         <f>IF(OR($A20&lt;&gt;"Yes",F20="",G20=""),"",MATCH(F20,Lists!$B$1:$B$5,0)*MATCH(G20,Lists!$C$1:$C$5,0))</f>
-        <v/>
-      </c>
-      <c r="I20" s="9">
+        <v>6</v>
+      </c>
+      <c r="I20" s="9" t="str">
         <f>IF(H20="","",IF(H20&gt;=17,"Critical",IF(H20&gt;=10,"High",IF(H20&gt;=5,"Medium","Low"))))</f>
-        <v/>
+        <v>Medium</v>
       </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
@@ -3541,15 +3541,15 @@
       </c>
       <c r="L20" s="9">
         <f>IF(OR(H20="",K20=""),"",ROUND(H20*VLOOKUP(K20,Scales!$A$22:$B$25,2,FALSE),1))</f>
-        <v/>
-      </c>
-      <c r="M20" s="9">
+        <v>2.4</v>
+      </c>
+      <c r="M20" s="9" t="str">
         <f>IF(L20="","",IF(L20&gt;=17,"Critical",IF(L20&gt;=10,"High",IF(L20&gt;=5,"Medium","Low"))))</f>
-        <v/>
-      </c>
-      <c r="N20" s="9">
+        <v>Low</v>
+      </c>
+      <c r="N20" s="9" t="str">
         <f>IF(M20="","",IF(OR(M20="Low",M20="Medium"),"Yes","No"))</f>
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="O20" s="17" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="V20">
         <f>IF(L20="","",L20+ROW()/100000)</f>
-        <v/>
+        <v>2.4002</v>
       </c>
     </row>
     <row r="21" ht="44" customHeight="1">
@@ -3610,11 +3610,11 @@
       </c>
       <c r="F21" s="17" t="n"/>
       <c r="G21" s="17" t="n"/>
-      <c r="H21" s="9">
+      <c r="H21" s="9" t="str">
         <f>IF(OR($A21&lt;&gt;"Yes",F21="",G21=""),"",MATCH(F21,Lists!$B$1:$B$5,0)*MATCH(G21,Lists!$C$1:$C$5,0))</f>
         <v/>
       </c>
-      <c r="I21" s="9">
+      <c r="I21" s="9" t="str">
         <f>IF(H21="","",IF(H21&gt;=17,"Critical",IF(H21&gt;=10,"High",IF(H21&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
@@ -3624,15 +3624,15 @@
         </is>
       </c>
       <c r="K21" s="17" t="n"/>
-      <c r="L21" s="9">
+      <c r="L21" s="9" t="str">
         <f>IF(OR(H21="",K21=""),"",ROUND(H21*VLOOKUP(K21,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
       </c>
-      <c r="M21" s="9">
+      <c r="M21" s="9" t="str">
         <f>IF(L21="","",IF(L21&gt;=17,"Critical",IF(L21&gt;=10,"High",IF(L21&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="N21" s="9">
+      <c r="N21" s="9" t="str">
         <f>IF(M21="","",IF(OR(M21="Low",M21="Medium"),"Yes","No"))</f>
         <v/>
       </c>
@@ -3646,7 +3646,7 @@
           <t>DSRs involving AI exceeding SLA</t>
         </is>
       </c>
-      <c r="V21">
+      <c r="V21" t="str">
         <f>IF(L21="","",L21+ROW()/100000)</f>
         <v/>
       </c>
@@ -3679,11 +3679,11 @@
       </c>
       <c r="F22" s="17" t="n"/>
       <c r="G22" s="17" t="n"/>
-      <c r="H22" s="9">
+      <c r="H22" s="9" t="str">
         <f>IF(OR($A22&lt;&gt;"Yes",F22="",G22=""),"",MATCH(F22,Lists!$B$1:$B$5,0)*MATCH(G22,Lists!$C$1:$C$5,0))</f>
         <v/>
       </c>
-      <c r="I22" s="9">
+      <c r="I22" s="9" t="str">
         <f>IF(H22="","",IF(H22&gt;=17,"Critical",IF(H22&gt;=10,"High",IF(H22&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
@@ -3693,15 +3693,15 @@
         </is>
       </c>
       <c r="K22" s="17" t="n"/>
-      <c r="L22" s="9">
+      <c r="L22" s="9" t="str">
         <f>IF(OR(H22="",K22=""),"",ROUND(H22*VLOOKUP(K22,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
       </c>
-      <c r="M22" s="9">
+      <c r="M22" s="9" t="str">
         <f>IF(L22="","",IF(L22&gt;=17,"Critical",IF(L22&gt;=10,"High",IF(L22&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="N22" s="9">
+      <c r="N22" s="9" t="str">
         <f>IF(M22="","",IF(OR(M22="Low",M22="Medium"),"Yes","No"))</f>
         <v/>
       </c>
@@ -3715,7 +3715,7 @@
           <t>Re-identification test failures</t>
         </is>
       </c>
-      <c r="V22">
+      <c r="V22" t="str">
         <f>IF(L22="","",L22+ROW()/100000)</f>
         <v/>
       </c>
@@ -3748,11 +3748,11 @@
       </c>
       <c r="F23" s="17" t="n"/>
       <c r="G23" s="17" t="n"/>
-      <c r="H23" s="9">
+      <c r="H23" s="9" t="str">
         <f>IF(OR($A23&lt;&gt;"Yes",F23="",G23=""),"",MATCH(F23,Lists!$B$1:$B$5,0)*MATCH(G23,Lists!$C$1:$C$5,0))</f>
         <v/>
       </c>
-      <c r="I23" s="9">
+      <c r="I23" s="9" t="str">
         <f>IF(H23="","",IF(H23&gt;=17,"Critical",IF(H23&gt;=10,"High",IF(H23&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
@@ -3762,15 +3762,15 @@
         </is>
       </c>
       <c r="K23" s="17" t="n"/>
-      <c r="L23" s="9">
+      <c r="L23" s="9" t="str">
         <f>IF(OR(H23="",K23=""),"",ROUND(H23*VLOOKUP(K23,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
       </c>
-      <c r="M23" s="9">
+      <c r="M23" s="9" t="str">
         <f>IF(L23="","",IF(L23&gt;=17,"Critical",IF(L23&gt;=10,"High",IF(L23&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="N23" s="9">
+      <c r="N23" s="9" t="str">
         <f>IF(M23="","",IF(OR(M23="Low",M23="Medium"),"Yes","No"))</f>
         <v/>
       </c>
@@ -3784,7 +3784,7 @@
           <t>Data-quality rule failures</t>
         </is>
       </c>
-      <c r="V23">
+      <c r="V23" t="str">
         <f>IF(L23="","",L23+ROW()/100000)</f>
         <v/>
       </c>
@@ -3817,11 +3817,11 @@
       </c>
       <c r="F24" s="17" t="n"/>
       <c r="G24" s="17" t="n"/>
-      <c r="H24" s="9">
+      <c r="H24" s="9" t="str">
         <f>IF(OR($A24&lt;&gt;"Yes",F24="",G24=""),"",MATCH(F24,Lists!$B$1:$B$5,0)*MATCH(G24,Lists!$C$1:$C$5,0))</f>
         <v/>
       </c>
-      <c r="I24" s="9">
+      <c r="I24" s="9" t="str">
         <f>IF(H24="","",IF(H24&gt;=17,"Critical",IF(H24&gt;=10,"High",IF(H24&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
@@ -3831,15 +3831,15 @@
         </is>
       </c>
       <c r="K24" s="17" t="n"/>
-      <c r="L24" s="9">
+      <c r="L24" s="9" t="str">
         <f>IF(OR(H24="",K24=""),"",ROUND(H24*VLOOKUP(K24,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
       </c>
-      <c r="M24" s="9">
+      <c r="M24" s="9" t="str">
         <f>IF(L24="","",IF(L24&gt;=17,"Critical",IF(L24&gt;=10,"High",IF(L24&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="N24" s="9">
+      <c r="N24" s="9" t="str">
         <f>IF(M24="","",IF(OR(M24="Low",M24="Medium"),"Yes","No"))</f>
         <v/>
       </c>
@@ -3853,7 +3853,7 @@
           <t>% datasets with documented lineage</t>
         </is>
       </c>
-      <c r="V24">
+      <c r="V24" t="str">
         <f>IF(L24="","",L24+ROW()/100000)</f>
         <v/>
       </c>
@@ -3886,11 +3886,11 @@
       </c>
       <c r="F25" s="17" t="n"/>
       <c r="G25" s="17" t="n"/>
-      <c r="H25" s="9">
+      <c r="H25" s="9" t="str">
         <f>IF(OR($A25&lt;&gt;"Yes",F25="",G25=""),"",MATCH(F25,Lists!$B$1:$B$5,0)*MATCH(G25,Lists!$C$1:$C$5,0))</f>
         <v/>
       </c>
-      <c r="I25" s="9">
+      <c r="I25" s="9" t="str">
         <f>IF(H25="","",IF(H25&gt;=17,"Critical",IF(H25&gt;=10,"High",IF(H25&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
@@ -3900,15 +3900,15 @@
         </is>
       </c>
       <c r="K25" s="17" t="n"/>
-      <c r="L25" s="9">
+      <c r="L25" s="9" t="str">
         <f>IF(OR(H25="",K25=""),"",ROUND(H25*VLOOKUP(K25,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
       </c>
-      <c r="M25" s="9">
+      <c r="M25" s="9" t="str">
         <f>IF(L25="","",IF(L25&gt;=17,"Critical",IF(L25&gt;=10,"High",IF(L25&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="N25" s="9">
+      <c r="N25" s="9" t="str">
         <f>IF(M25="","",IF(OR(M25="Low",M25="Medium"),"Yes","No"))</f>
         <v/>
       </c>
@@ -3922,7 +3922,7 @@
           <t>Population stability index / drift score</t>
         </is>
       </c>
-      <c r="V25">
+      <c r="V25" t="str">
         <f>IF(L25="","",L25+ROW()/100000)</f>
         <v/>
       </c>
@@ -3955,11 +3955,11 @@
       </c>
       <c r="F26" s="17" t="n"/>
       <c r="G26" s="17" t="n"/>
-      <c r="H26" s="9">
+      <c r="H26" s="9" t="str">
         <f>IF(OR($A26&lt;&gt;"Yes",F26="",G26=""),"",MATCH(F26,Lists!$B$1:$B$5,0)*MATCH(G26,Lists!$C$1:$C$5,0))</f>
         <v/>
       </c>
-      <c r="I26" s="9">
+      <c r="I26" s="9" t="str">
         <f>IF(H26="","",IF(H26&gt;=17,"Critical",IF(H26&gt;=10,"High",IF(H26&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
@@ -3969,15 +3969,15 @@
         </is>
       </c>
       <c r="K26" s="17" t="n"/>
-      <c r="L26" s="9">
+      <c r="L26" s="9" t="str">
         <f>IF(OR(H26="",K26=""),"",ROUND(H26*VLOOKUP(K26,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
       </c>
-      <c r="M26" s="9">
+      <c r="M26" s="9" t="str">
         <f>IF(L26="","",IF(L26&gt;=17,"Critical",IF(L26&gt;=10,"High",IF(L26&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="N26" s="9">
+      <c r="N26" s="9" t="str">
         <f>IF(M26="","",IF(OR(M26="Low",M26="Medium"),"Yes","No"))</f>
         <v/>
       </c>
@@ -3991,7 +3991,7 @@
           <t>Error rate vs threshold</t>
         </is>
       </c>
-      <c r="V26">
+      <c r="V26" t="str">
         <f>IF(L26="","",L26+ROW()/100000)</f>
         <v/>
       </c>
@@ -4034,11 +4034,11 @@
       </c>
       <c r="H27" s="9">
         <f>IF(OR($A27&lt;&gt;"Yes",F27="",G27=""),"",MATCH(F27,Lists!$B$1:$B$5,0)*MATCH(G27,Lists!$C$1:$C$5,0))</f>
-        <v/>
-      </c>
-      <c r="I27" s="9">
+        <v>12</v>
+      </c>
+      <c r="I27" s="9" t="str">
         <f>IF(H27="","",IF(H27&gt;=17,"Critical",IF(H27&gt;=10,"High",IF(H27&gt;=5,"Medium","Low"))))</f>
-        <v/>
+        <v>High</v>
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
@@ -4052,15 +4052,15 @@
       </c>
       <c r="L27" s="9">
         <f>IF(OR(H27="",K27=""),"",ROUND(H27*VLOOKUP(K27,Scales!$A$22:$B$25,2,FALSE),1))</f>
-        <v/>
-      </c>
-      <c r="M27" s="9">
+        <v>9.6</v>
+      </c>
+      <c r="M27" s="9" t="str">
         <f>IF(L27="","",IF(L27&gt;=17,"Critical",IF(L27&gt;=10,"High",IF(L27&gt;=5,"Medium","Low"))))</f>
-        <v/>
-      </c>
-      <c r="N27" s="9">
+        <v>Medium</v>
+      </c>
+      <c r="N27" s="9" t="str">
         <f>IF(M27="","",IF(OR(M27="Low",M27="Medium"),"Yes","No"))</f>
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="O27" s="17" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
       </c>
       <c r="V27">
         <f>IF(L27="","",L27+ROW()/100000)</f>
-        <v/>
+        <v>9.60027</v>
       </c>
     </row>
     <row r="28" ht="44" customHeight="1">
@@ -4121,11 +4121,11 @@
       </c>
       <c r="F28" s="17" t="n"/>
       <c r="G28" s="17" t="n"/>
-      <c r="H28" s="9">
+      <c r="H28" s="9" t="str">
         <f>IF(OR($A28&lt;&gt;"Yes",F28="",G28=""),"",MATCH(F28,Lists!$B$1:$B$5,0)*MATCH(G28,Lists!$C$1:$C$5,0))</f>
         <v/>
       </c>
-      <c r="I28" s="9">
+      <c r="I28" s="9" t="str">
         <f>IF(H28="","",IF(H28&gt;=17,"Critical",IF(H28&gt;=10,"High",IF(H28&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
@@ -4135,15 +4135,15 @@
         </is>
       </c>
       <c r="K28" s="17" t="n"/>
-      <c r="L28" s="9">
+      <c r="L28" s="9" t="str">
         <f>IF(OR(H28="",K28=""),"",ROUND(H28*VLOOKUP(K28,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
       </c>
-      <c r="M28" s="9">
+      <c r="M28" s="9" t="str">
         <f>IF(L28="","",IF(L28&gt;=17,"Critical",IF(L28&gt;=10,"High",IF(L28&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="N28" s="9">
+      <c r="N28" s="9" t="str">
         <f>IF(M28="","",IF(OR(M28="Low",M28="Medium"),"Yes","No"))</f>
         <v/>
       </c>
@@ -4157,7 +4157,7 @@
           <t>Robustness test pass rate</t>
         </is>
       </c>
-      <c r="V28">
+      <c r="V28" t="str">
         <f>IF(L28="","",L28+ROW()/100000)</f>
         <v/>
       </c>
@@ -4190,11 +4190,11 @@
       </c>
       <c r="F29" s="17" t="n"/>
       <c r="G29" s="17" t="n"/>
-      <c r="H29" s="9">
+      <c r="H29" s="9" t="str">
         <f>IF(OR($A29&lt;&gt;"Yes",F29="",G29=""),"",MATCH(F29,Lists!$B$1:$B$5,0)*MATCH(G29,Lists!$C$1:$C$5,0))</f>
         <v/>
       </c>
-      <c r="I29" s="9">
+      <c r="I29" s="9" t="str">
         <f>IF(H29="","",IF(H29&gt;=17,"Critical",IF(H29&gt;=10,"High",IF(H29&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
@@ -4204,15 +4204,15 @@
         </is>
       </c>
       <c r="K29" s="17" t="n"/>
-      <c r="L29" s="9">
+      <c r="L29" s="9" t="str">
         <f>IF(OR(H29="",K29=""),"",ROUND(H29*VLOOKUP(K29,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
       </c>
-      <c r="M29" s="9">
+      <c r="M29" s="9" t="str">
         <f>IF(L29="","",IF(L29&gt;=17,"Critical",IF(L29&gt;=10,"High",IF(L29&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="N29" s="9">
+      <c r="N29" s="9" t="str">
         <f>IF(M29="","",IF(OR(M29="Low",M29="Medium"),"Yes","No"))</f>
         <v/>
       </c>
@@ -4226,7 +4226,7 @@
           <t>Unvalidated model version changes</t>
         </is>
       </c>
-      <c r="V29">
+      <c r="V29" t="str">
         <f>IF(L29="","",L29+ROW()/100000)</f>
         <v/>
       </c>
@@ -4259,11 +4259,11 @@
       </c>
       <c r="F30" s="17" t="n"/>
       <c r="G30" s="17" t="n"/>
-      <c r="H30" s="9">
+      <c r="H30" s="9" t="str">
         <f>IF(OR($A30&lt;&gt;"Yes",F30="",G30=""),"",MATCH(F30,Lists!$B$1:$B$5,0)*MATCH(G30,Lists!$C$1:$C$5,0))</f>
         <v/>
       </c>
-      <c r="I30" s="9">
+      <c r="I30" s="9" t="str">
         <f>IF(H30="","",IF(H30&gt;=17,"Critical",IF(H30&gt;=10,"High",IF(H30&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
@@ -4273,15 +4273,15 @@
         </is>
       </c>
       <c r="K30" s="17" t="n"/>
-      <c r="L30" s="9">
+      <c r="L30" s="9" t="str">
         <f>IF(OR(H30="",K30=""),"",ROUND(H30*VLOOKUP(K30,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
       </c>
-      <c r="M30" s="9">
+      <c r="M30" s="9" t="str">
         <f>IF(L30="","",IF(L30&gt;=17,"Critical",IF(L30&gt;=10,"High",IF(L30&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="N30" s="9">
+      <c r="N30" s="9" t="str">
         <f>IF(M30="","",IF(OR(M30="Low",M30="Medium"),"Yes","No"))</f>
         <v/>
       </c>
@@ -4295,7 +4295,7 @@
           <t>Releases without passing LLM regression suite</t>
         </is>
       </c>
-      <c r="V30">
+      <c r="V30" t="str">
         <f>IF(L30="","",L30+ROW()/100000)</f>
         <v/>
       </c>
@@ -4338,11 +4338,11 @@
       </c>
       <c r="H31" s="9">
         <f>IF(OR($A31&lt;&gt;"Yes",F31="",G31=""),"",MATCH(F31,Lists!$B$1:$B$5,0)*MATCH(G31,Lists!$C$1:$C$5,0))</f>
-        <v/>
-      </c>
-      <c r="I31" s="9">
+        <v>6</v>
+      </c>
+      <c r="I31" s="9" t="str">
         <f>IF(H31="","",IF(H31&gt;=17,"Critical",IF(H31&gt;=10,"High",IF(H31&gt;=5,"Medium","Low"))))</f>
-        <v/>
+        <v>Medium</v>
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
@@ -4356,15 +4356,15 @@
       </c>
       <c r="L31" s="9">
         <f>IF(OR(H31="",K31=""),"",ROUND(H31*VLOOKUP(K31,Scales!$A$22:$B$25,2,FALSE),1))</f>
-        <v/>
-      </c>
-      <c r="M31" s="9">
+        <v>3.6</v>
+      </c>
+      <c r="M31" s="9" t="str">
         <f>IF(L31="","",IF(L31&gt;=17,"Critical",IF(L31&gt;=10,"High",IF(L31&gt;=5,"Medium","Low"))))</f>
-        <v/>
-      </c>
-      <c r="N31" s="9">
+        <v>Low</v>
+      </c>
+      <c r="N31" s="9" t="str">
         <f>IF(M31="","",IF(OR(M31="Low",M31="Medium"),"Yes","No"))</f>
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="O31" s="17" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="V31">
         <f>IF(L31="","",L31+ROW()/100000)</f>
-        <v/>
+        <v>3.60031</v>
       </c>
     </row>
     <row r="32" ht="44" customHeight="1">
@@ -4425,11 +4425,11 @@
       </c>
       <c r="F32" s="17" t="n"/>
       <c r="G32" s="17" t="n"/>
-      <c r="H32" s="9">
+      <c r="H32" s="9" t="str">
         <f>IF(OR($A32&lt;&gt;"Yes",F32="",G32=""),"",MATCH(F32,Lists!$B$1:$B$5,0)*MATCH(G32,Lists!$C$1:$C$5,0))</f>
         <v/>
       </c>
-      <c r="I32" s="9">
+      <c r="I32" s="9" t="str">
         <f>IF(H32="","",IF(H32&gt;=17,"Critical",IF(H32&gt;=10,"High",IF(H32&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
@@ -4439,15 +4439,15 @@
         </is>
       </c>
       <c r="K32" s="17" t="n"/>
-      <c r="L32" s="9">
+      <c r="L32" s="9" t="str">
         <f>IF(OR(H32="",K32=""),"",ROUND(H32*VLOOKUP(K32,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
       </c>
-      <c r="M32" s="9">
+      <c r="M32" s="9" t="str">
         <f>IF(L32="","",IF(L32&gt;=17,"Critical",IF(L32&gt;=10,"High",IF(L32&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="N32" s="9">
+      <c r="N32" s="9" t="str">
         <f>IF(M32="","",IF(OR(M32="Low",M32="Medium"),"Yes","No"))</f>
         <v/>
       </c>
@@ -4461,7 +4461,7 @@
           <t>Explanation requests not satisfied</t>
         </is>
       </c>
-      <c r="V32">
+      <c r="V32" t="str">
         <f>IF(L32="","",L32+ROW()/100000)</f>
         <v/>
       </c>
@@ -4494,11 +4494,11 @@
       </c>
       <c r="F33" s="17" t="n"/>
       <c r="G33" s="17" t="n"/>
-      <c r="H33" s="9">
+      <c r="H33" s="9" t="str">
         <f>IF(OR($A33&lt;&gt;"Yes",F33="",G33=""),"",MATCH(F33,Lists!$B$1:$B$5,0)*MATCH(G33,Lists!$C$1:$C$5,0))</f>
         <v/>
       </c>
-      <c r="I33" s="9">
+      <c r="I33" s="9" t="str">
         <f>IF(H33="","",IF(H33&gt;=17,"Critical",IF(H33&gt;=10,"High",IF(H33&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
@@ -4508,15 +4508,15 @@
         </is>
       </c>
       <c r="K33" s="17" t="n"/>
-      <c r="L33" s="9">
+      <c r="L33" s="9" t="str">
         <f>IF(OR(H33="",K33=""),"",ROUND(H33*VLOOKUP(K33,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
       </c>
-      <c r="M33" s="9">
+      <c r="M33" s="9" t="str">
         <f>IF(L33="","",IF(L33&gt;=17,"Critical",IF(L33&gt;=10,"High",IF(L33&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="N33" s="9">
+      <c r="N33" s="9" t="str">
         <f>IF(M33="","",IF(OR(M33="Low",M33="Medium"),"Yes","No"))</f>
         <v/>
       </c>
@@ -4530,7 +4530,7 @@
           <t>Appeals exceeding SLA</t>
         </is>
       </c>
-      <c r="V33">
+      <c r="V33" t="str">
         <f>IF(L33="","",L33+ROW()/100000)</f>
         <v/>
       </c>
@@ -4563,11 +4563,11 @@
       </c>
       <c r="F34" s="17" t="n"/>
       <c r="G34" s="17" t="n"/>
-      <c r="H34" s="9">
+      <c r="H34" s="9" t="str">
         <f>IF(OR($A34&lt;&gt;"Yes",F34="",G34=""),"",MATCH(F34,Lists!$B$1:$B$5,0)*MATCH(G34,Lists!$C$1:$C$5,0))</f>
         <v/>
       </c>
-      <c r="I34" s="9">
+      <c r="I34" s="9" t="str">
         <f>IF(H34="","",IF(H34&gt;=17,"Critical",IF(H34&gt;=10,"High",IF(H34&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
@@ -4577,15 +4577,15 @@
         </is>
       </c>
       <c r="K34" s="17" t="n"/>
-      <c r="L34" s="9">
+      <c r="L34" s="9" t="str">
         <f>IF(OR(H34="",K34=""),"",ROUND(H34*VLOOKUP(K34,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
       </c>
-      <c r="M34" s="9">
+      <c r="M34" s="9" t="str">
         <f>IF(L34="","",IF(L34&gt;=17,"Critical",IF(L34&gt;=10,"High",IF(L34&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="N34" s="9">
+      <c r="N34" s="9" t="str">
         <f>IF(M34="","",IF(OR(M34="Low",M34="Medium"),"Yes","No"))</f>
         <v/>
       </c>
@@ -4599,7 +4599,7 @@
           <t>Systems with incomplete documentation pack</t>
         </is>
       </c>
-      <c r="V34">
+      <c r="V34" t="str">
         <f>IF(L34="","",L34+ROW()/100000)</f>
         <v/>
       </c>
@@ -4642,11 +4642,11 @@
       </c>
       <c r="H35" s="9">
         <f>IF(OR($A35&lt;&gt;"Yes",F35="",G35=""),"",MATCH(F35,Lists!$B$1:$B$5,0)*MATCH(G35,Lists!$C$1:$C$5,0))</f>
-        <v/>
-      </c>
-      <c r="I35" s="9">
+        <v>16</v>
+      </c>
+      <c r="I35" s="9" t="str">
         <f>IF(H35="","",IF(H35&gt;=17,"Critical",IF(H35&gt;=10,"High",IF(H35&gt;=5,"Medium","Low"))))</f>
-        <v/>
+        <v>High</v>
       </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
@@ -4660,15 +4660,15 @@
       </c>
       <c r="L35" s="9">
         <f>IF(OR(H35="",K35=""),"",ROUND(H35*VLOOKUP(K35,Scales!$A$22:$B$25,2,FALSE),1))</f>
-        <v/>
-      </c>
-      <c r="M35" s="9">
+        <v>12.8</v>
+      </c>
+      <c r="M35" s="9" t="str">
         <f>IF(L35="","",IF(L35&gt;=17,"Critical",IF(L35&gt;=10,"High",IF(L35&gt;=5,"Medium","Low"))))</f>
-        <v/>
-      </c>
-      <c r="N35" s="9">
+        <v>High</v>
+      </c>
+      <c r="N35" s="9" t="str">
         <f>IF(M35="","",IF(OR(M35="Low",M35="Medium"),"Yes","No"))</f>
-        <v/>
+        <v>No</v>
       </c>
       <c r="O35" s="17" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="V35">
         <f>IF(L35="","",L35+ROW()/100000)</f>
-        <v/>
+        <v>12.80035</v>
       </c>
     </row>
     <row r="36" ht="44" customHeight="1">
@@ -4729,11 +4729,11 @@
       </c>
       <c r="F36" s="17" t="n"/>
       <c r="G36" s="17" t="n"/>
-      <c r="H36" s="9">
+      <c r="H36" s="9" t="str">
         <f>IF(OR($A36&lt;&gt;"Yes",F36="",G36=""),"",MATCH(F36,Lists!$B$1:$B$5,0)*MATCH(G36,Lists!$C$1:$C$5,0))</f>
         <v/>
       </c>
-      <c r="I36" s="9">
+      <c r="I36" s="9" t="str">
         <f>IF(H36="","",IF(H36&gt;=17,"Critical",IF(H36&gt;=10,"High",IF(H36&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
@@ -4743,15 +4743,15 @@
         </is>
       </c>
       <c r="K36" s="17" t="n"/>
-      <c r="L36" s="9">
+      <c r="L36" s="9" t="str">
         <f>IF(OR(H36="",K36=""),"",ROUND(H36*VLOOKUP(K36,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
       </c>
-      <c r="M36" s="9">
+      <c r="M36" s="9" t="str">
         <f>IF(L36="","",IF(L36&gt;=17,"Critical",IF(L36&gt;=10,"High",IF(L36&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="N36" s="9">
+      <c r="N36" s="9" t="str">
         <f>IF(M36="","",IF(OR(M36="Low",M36="Medium"),"Yes","No"))</f>
         <v/>
       </c>
@@ -4765,7 +4765,7 @@
           <t>Integrity check failures</t>
         </is>
       </c>
-      <c r="V36">
+      <c r="V36" t="str">
         <f>IF(L36="","",L36+ROW()/100000)</f>
         <v/>
       </c>
@@ -4798,11 +4798,11 @@
       </c>
       <c r="F37" s="17" t="n"/>
       <c r="G37" s="17" t="n"/>
-      <c r="H37" s="9">
+      <c r="H37" s="9" t="str">
         <f>IF(OR($A37&lt;&gt;"Yes",F37="",G37=""),"",MATCH(F37,Lists!$B$1:$B$5,0)*MATCH(G37,Lists!$C$1:$C$5,0))</f>
         <v/>
       </c>
-      <c r="I37" s="9">
+      <c r="I37" s="9" t="str">
         <f>IF(H37="","",IF(H37&gt;=17,"Critical",IF(H37&gt;=10,"High",IF(H37&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
@@ -4812,15 +4812,15 @@
         </is>
       </c>
       <c r="K37" s="17" t="n"/>
-      <c r="L37" s="9">
+      <c r="L37" s="9" t="str">
         <f>IF(OR(H37="",K37=""),"",ROUND(H37*VLOOKUP(K37,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
       </c>
-      <c r="M37" s="9">
+      <c r="M37" s="9" t="str">
         <f>IF(L37="","",IF(L37&gt;=17,"Critical",IF(L37&gt;=10,"High",IF(L37&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="N37" s="9">
+      <c r="N37" s="9" t="str">
         <f>IF(M37="","",IF(OR(M37="Low",M37="Medium"),"Yes","No"))</f>
         <v/>
       </c>
@@ -4834,7 +4834,7 @@
           <t>Anomalous query volumes</t>
         </is>
       </c>
-      <c r="V37">
+      <c r="V37" t="str">
         <f>IF(L37="","",L37+ROW()/100000)</f>
         <v/>
       </c>
@@ -4877,11 +4877,11 @@
       </c>
       <c r="H38" s="9">
         <f>IF(OR($A38&lt;&gt;"Yes",F38="",G38=""),"",MATCH(F38,Lists!$B$1:$B$5,0)*MATCH(G38,Lists!$C$1:$C$5,0))</f>
-        <v/>
-      </c>
-      <c r="I38" s="9">
+        <v>15</v>
+      </c>
+      <c r="I38" s="9" t="str">
         <f>IF(H38="","",IF(H38&gt;=17,"Critical",IF(H38&gt;=10,"High",IF(H38&gt;=5,"Medium","Low"))))</f>
-        <v/>
+        <v>High</v>
       </c>
       <c r="J38" s="7" t="inlineStr">
         <is>
@@ -4895,15 +4895,15 @@
       </c>
       <c r="L38" s="9">
         <f>IF(OR(H38="",K38=""),"",ROUND(H38*VLOOKUP(K38,Scales!$A$22:$B$25,2,FALSE),1))</f>
-        <v/>
-      </c>
-      <c r="M38" s="9">
+        <v>12</v>
+      </c>
+      <c r="M38" s="9" t="str">
         <f>IF(L38="","",IF(L38&gt;=17,"Critical",IF(L38&gt;=10,"High",IF(L38&gt;=5,"Medium","Low"))))</f>
-        <v/>
-      </c>
-      <c r="N38" s="9">
+        <v>High</v>
+      </c>
+      <c r="N38" s="9" t="str">
         <f>IF(M38="","",IF(OR(M38="Low",M38="Medium"),"Yes","No"))</f>
-        <v/>
+        <v>No</v>
       </c>
       <c r="O38" s="17" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="V38">
         <f>IF(L38="","",L38+ROW()/100000)</f>
-        <v/>
+        <v>12.00038</v>
       </c>
     </row>
     <row r="39" ht="44" customHeight="1">
@@ -4974,11 +4974,11 @@
       </c>
       <c r="H39" s="9">
         <f>IF(OR($A39&lt;&gt;"Yes",F39="",G39=""),"",MATCH(F39,Lists!$B$1:$B$5,0)*MATCH(G39,Lists!$C$1:$C$5,0))</f>
-        <v/>
-      </c>
-      <c r="I39" s="9">
+        <v>12</v>
+      </c>
+      <c r="I39" s="9" t="str">
         <f>IF(H39="","",IF(H39&gt;=17,"Critical",IF(H39&gt;=10,"High",IF(H39&gt;=5,"Medium","Low"))))</f>
-        <v/>
+        <v>High</v>
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
@@ -4992,15 +4992,15 @@
       </c>
       <c r="L39" s="9">
         <f>IF(OR(H39="",K39=""),"",ROUND(H39*VLOOKUP(K39,Scales!$A$22:$B$25,2,FALSE),1))</f>
-        <v/>
-      </c>
-      <c r="M39" s="9">
+        <v>9.6</v>
+      </c>
+      <c r="M39" s="9" t="str">
         <f>IF(L39="","",IF(L39&gt;=17,"Critical",IF(L39&gt;=10,"High",IF(L39&gt;=5,"Medium","Low"))))</f>
-        <v/>
-      </c>
-      <c r="N39" s="9">
+        <v>Medium</v>
+      </c>
+      <c r="N39" s="9" t="str">
         <f>IF(M39="","",IF(OR(M39="Low",M39="Medium"),"Yes","No"))</f>
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="O39" s="17" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="V39">
         <f>IF(L39="","",L39+ROW()/100000)</f>
-        <v/>
+        <v>9.60039</v>
       </c>
     </row>
     <row r="40" ht="44" customHeight="1">
@@ -5061,11 +5061,11 @@
       </c>
       <c r="F40" s="17" t="n"/>
       <c r="G40" s="17" t="n"/>
-      <c r="H40" s="9">
+      <c r="H40" s="9" t="str">
         <f>IF(OR($A40&lt;&gt;"Yes",F40="",G40=""),"",MATCH(F40,Lists!$B$1:$B$5,0)*MATCH(G40,Lists!$C$1:$C$5,0))</f>
         <v/>
       </c>
-      <c r="I40" s="9">
+      <c r="I40" s="9" t="str">
         <f>IF(H40="","",IF(H40&gt;=17,"Critical",IF(H40&gt;=10,"High",IF(H40&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
@@ -5075,15 +5075,15 @@
         </is>
       </c>
       <c r="K40" s="17" t="n"/>
-      <c r="L40" s="9">
+      <c r="L40" s="9" t="str">
         <f>IF(OR(H40="",K40=""),"",ROUND(H40*VLOOKUP(K40,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
       </c>
-      <c r="M40" s="9">
+      <c r="M40" s="9" t="str">
         <f>IF(L40="","",IF(L40&gt;=17,"Critical",IF(L40&gt;=10,"High",IF(L40&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="N40" s="9">
+      <c r="N40" s="9" t="str">
         <f>IF(M40="","",IF(OR(M40="Low",M40="Medium"),"Yes","No"))</f>
         <v/>
       </c>
@@ -5097,7 +5097,7 @@
           <t>Blocked egress / SSRF attempts</t>
         </is>
       </c>
-      <c r="V40">
+      <c r="V40" t="str">
         <f>IF(L40="","",L40+ROW()/100000)</f>
         <v/>
       </c>
@@ -5130,11 +5130,11 @@
       </c>
       <c r="F41" s="17" t="n"/>
       <c r="G41" s="17" t="n"/>
-      <c r="H41" s="9">
+      <c r="H41" s="9" t="str">
         <f>IF(OR($A41&lt;&gt;"Yes",F41="",G41=""),"",MATCH(F41,Lists!$B$1:$B$5,0)*MATCH(G41,Lists!$C$1:$C$5,0))</f>
         <v/>
       </c>
-      <c r="I41" s="9">
+      <c r="I41" s="9" t="str">
         <f>IF(H41="","",IF(H41&gt;=17,"Critical",IF(H41&gt;=10,"High",IF(H41&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
@@ -5144,15 +5144,15 @@
         </is>
       </c>
       <c r="K41" s="17" t="n"/>
-      <c r="L41" s="9">
+      <c r="L41" s="9" t="str">
         <f>IF(OR(H41="",K41=""),"",ROUND(H41*VLOOKUP(K41,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
       </c>
-      <c r="M41" s="9">
+      <c r="M41" s="9" t="str">
         <f>IF(L41="","",IF(L41&gt;=17,"Critical",IF(L41&gt;=10,"High",IF(L41&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="N41" s="9">
+      <c r="N41" s="9" t="str">
         <f>IF(M41="","",IF(OR(M41="Low",M41="Medium"),"Yes","No"))</f>
         <v/>
       </c>
@@ -5166,7 +5166,7 @@
           <t>Unscanned model artefacts</t>
         </is>
       </c>
-      <c r="V41">
+      <c r="V41" t="str">
         <f>IF(L41="","",L41+ROW()/100000)</f>
         <v/>
       </c>
@@ -5209,11 +5209,11 @@
       </c>
       <c r="H42" s="9">
         <f>IF(OR($A42&lt;&gt;"Yes",F42="",G42=""),"",MATCH(F42,Lists!$B$1:$B$5,0)*MATCH(G42,Lists!$C$1:$C$5,0))</f>
-        <v/>
-      </c>
-      <c r="I42" s="9">
+        <v>9</v>
+      </c>
+      <c r="I42" s="9" t="str">
         <f>IF(H42="","",IF(H42&gt;=17,"Critical",IF(H42&gt;=10,"High",IF(H42&gt;=5,"Medium","Low"))))</f>
-        <v/>
+        <v>Medium</v>
       </c>
       <c r="J42" s="7" t="inlineStr">
         <is>
@@ -5227,15 +5227,15 @@
       </c>
       <c r="L42" s="9">
         <f>IF(OR(H42="",K42=""),"",ROUND(H42*VLOOKUP(K42,Scales!$A$22:$B$25,2,FALSE),1))</f>
-        <v/>
-      </c>
-      <c r="M42" s="9">
+        <v>5.4</v>
+      </c>
+      <c r="M42" s="9" t="str">
         <f>IF(L42="","",IF(L42&gt;=17,"Critical",IF(L42&gt;=10,"High",IF(L42&gt;=5,"Medium","Low"))))</f>
-        <v/>
-      </c>
-      <c r="N42" s="9">
+        <v>Medium</v>
+      </c>
+      <c r="N42" s="9" t="str">
         <f>IF(M42="","",IF(OR(M42="Low",M42="Medium"),"Yes","No"))</f>
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="O42" s="17" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
       </c>
       <c r="V42">
         <f>IF(L42="","",L42+ROW()/100000)</f>
-        <v/>
+        <v>5.40042</v>
       </c>
     </row>
     <row r="43" ht="44" customHeight="1">
@@ -5296,11 +5296,11 @@
       </c>
       <c r="F43" s="17" t="n"/>
       <c r="G43" s="17" t="n"/>
-      <c r="H43" s="9">
+      <c r="H43" s="9" t="str">
         <f>IF(OR($A43&lt;&gt;"Yes",F43="",G43=""),"",MATCH(F43,Lists!$B$1:$B$5,0)*MATCH(G43,Lists!$C$1:$C$5,0))</f>
         <v/>
       </c>
-      <c r="I43" s="9">
+      <c r="I43" s="9" t="str">
         <f>IF(H43="","",IF(H43&gt;=17,"Critical",IF(H43&gt;=10,"High",IF(H43&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
@@ -5310,15 +5310,15 @@
         </is>
       </c>
       <c r="K43" s="17" t="n"/>
-      <c r="L43" s="9">
+      <c r="L43" s="9" t="str">
         <f>IF(OR(H43="",K43=""),"",ROUND(H43*VLOOKUP(K43,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
       </c>
-      <c r="M43" s="9">
+      <c r="M43" s="9" t="str">
         <f>IF(L43="","",IF(L43&gt;=17,"Critical",IF(L43&gt;=10,"High",IF(L43&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="N43" s="9">
+      <c r="N43" s="9" t="str">
         <f>IF(M43="","",IF(OR(M43="Low",M43="Medium"),"Yes","No"))</f>
         <v/>
       </c>
@@ -5332,7 +5332,7 @@
           <t>Oversight roles without training</t>
         </is>
       </c>
-      <c r="V43">
+      <c r="V43" t="str">
         <f>IF(L43="","",L43+ROW()/100000)</f>
         <v/>
       </c>
@@ -5375,11 +5375,11 @@
       </c>
       <c r="H44" s="9">
         <f>IF(OR($A44&lt;&gt;"Yes",F44="",G44=""),"",MATCH(F44,Lists!$B$1:$B$5,0)*MATCH(G44,Lists!$C$1:$C$5,0))</f>
-        <v/>
-      </c>
-      <c r="I44" s="9">
+        <v>15</v>
+      </c>
+      <c r="I44" s="9" t="str">
         <f>IF(H44="","",IF(H44&gt;=17,"Critical",IF(H44&gt;=10,"High",IF(H44&gt;=5,"Medium","Low"))))</f>
-        <v/>
+        <v>High</v>
       </c>
       <c r="J44" s="7" t="inlineStr">
         <is>
@@ -5393,15 +5393,15 @@
       </c>
       <c r="L44" s="9">
         <f>IF(OR(H44="",K44=""),"",ROUND(H44*VLOOKUP(K44,Scales!$A$22:$B$25,2,FALSE),1))</f>
-        <v/>
-      </c>
-      <c r="M44" s="9">
+        <v>12</v>
+      </c>
+      <c r="M44" s="9" t="str">
         <f>IF(L44="","",IF(L44&gt;=17,"Critical",IF(L44&gt;=10,"High",IF(L44&gt;=5,"Medium","Low"))))</f>
-        <v/>
-      </c>
-      <c r="N44" s="9">
+        <v>High</v>
+      </c>
+      <c r="N44" s="9" t="str">
         <f>IF(M44="","",IF(OR(M44="Low",M44="Medium"),"Yes","No"))</f>
-        <v/>
+        <v>No</v>
       </c>
       <c r="O44" s="17" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
       </c>
       <c r="V44">
         <f>IF(L44="","",L44+ROW()/100000)</f>
-        <v/>
+        <v>12.00044</v>
       </c>
     </row>
     <row r="45" ht="44" customHeight="1">
@@ -5462,11 +5462,11 @@
       </c>
       <c r="F45" s="17" t="n"/>
       <c r="G45" s="17" t="n"/>
-      <c r="H45" s="9">
+      <c r="H45" s="9" t="str">
         <f>IF(OR($A45&lt;&gt;"Yes",F45="",G45=""),"",MATCH(F45,Lists!$B$1:$B$5,0)*MATCH(G45,Lists!$C$1:$C$5,0))</f>
         <v/>
       </c>
-      <c r="I45" s="9">
+      <c r="I45" s="9" t="str">
         <f>IF(H45="","",IF(H45&gt;=17,"Critical",IF(H45&gt;=10,"High",IF(H45&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
@@ -5476,15 +5476,15 @@
         </is>
       </c>
       <c r="K45" s="17" t="n"/>
-      <c r="L45" s="9">
+      <c r="L45" s="9" t="str">
         <f>IF(OR(H45="",K45=""),"",ROUND(H45*VLOOKUP(K45,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
       </c>
-      <c r="M45" s="9">
+      <c r="M45" s="9" t="str">
         <f>IF(L45="","",IF(L45&gt;=17,"Critical",IF(L45&gt;=10,"High",IF(L45&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="N45" s="9">
+      <c r="N45" s="9" t="str">
         <f>IF(M45="","",IF(OR(M45="Low",M45="Medium"),"Yes","No"))</f>
         <v/>
       </c>
@@ -5498,7 +5498,7 @@
           <t>Staff sentiment / attrition in affected roles</t>
         </is>
       </c>
-      <c r="V45">
+      <c r="V45" t="str">
         <f>IF(L45="","",L45+ROW()/100000)</f>
         <v/>
       </c>
@@ -5531,11 +5531,11 @@
       </c>
       <c r="F46" s="17" t="n"/>
       <c r="G46" s="17" t="n"/>
-      <c r="H46" s="9">
+      <c r="H46" s="9" t="str">
         <f>IF(OR($A46&lt;&gt;"Yes",F46="",G46=""),"",MATCH(F46,Lists!$B$1:$B$5,0)*MATCH(G46,Lists!$C$1:$C$5,0))</f>
         <v/>
       </c>
-      <c r="I46" s="9">
+      <c r="I46" s="9" t="str">
         <f>IF(H46="","",IF(H46&gt;=17,"Critical",IF(H46&gt;=10,"High",IF(H46&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
@@ -5545,15 +5545,15 @@
         </is>
       </c>
       <c r="K46" s="17" t="n"/>
-      <c r="L46" s="9">
+      <c r="L46" s="9" t="str">
         <f>IF(OR(H46="",K46=""),"",ROUND(H46*VLOOKUP(K46,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
       </c>
-      <c r="M46" s="9">
+      <c r="M46" s="9" t="str">
         <f>IF(L46="","",IF(L46&gt;=17,"Critical",IF(L46&gt;=10,"High",IF(L46&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="N46" s="9">
+      <c r="N46" s="9" t="str">
         <f>IF(M46="","",IF(OR(M46="Low",M46="Medium"),"Yes","No"))</f>
         <v/>
       </c>
@@ -5567,7 +5567,7 @@
           <t>% critical AI workloads on single provider</t>
         </is>
       </c>
-      <c r="V46">
+      <c r="V46" t="str">
         <f>IF(L46="","",L46+ROW()/100000)</f>
         <v/>
       </c>
@@ -5610,11 +5610,11 @@
       </c>
       <c r="H47" s="9">
         <f>IF(OR($A47&lt;&gt;"Yes",F47="",G47=""),"",MATCH(F47,Lists!$B$1:$B$5,0)*MATCH(G47,Lists!$C$1:$C$5,0))</f>
-        <v/>
-      </c>
-      <c r="I47" s="9">
+        <v>9</v>
+      </c>
+      <c r="I47" s="9" t="str">
         <f>IF(H47="","",IF(H47&gt;=17,"Critical",IF(H47&gt;=10,"High",IF(H47&gt;=5,"Medium","Low"))))</f>
-        <v/>
+        <v>Medium</v>
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
@@ -5628,15 +5628,15 @@
       </c>
       <c r="L47" s="9">
         <f>IF(OR(H47="",K47=""),"",ROUND(H47*VLOOKUP(K47,Scales!$A$22:$B$25,2,FALSE),1))</f>
-        <v/>
-      </c>
-      <c r="M47" s="9">
+        <v>5.4</v>
+      </c>
+      <c r="M47" s="9" t="str">
         <f>IF(L47="","",IF(L47&gt;=17,"Critical",IF(L47&gt;=10,"High",IF(L47&gt;=5,"Medium","Low"))))</f>
-        <v/>
-      </c>
-      <c r="N47" s="9">
+        <v>Medium</v>
+      </c>
+      <c r="N47" s="9" t="str">
         <f>IF(M47="","",IF(OR(M47="Low",M47="Medium"),"Yes","No"))</f>
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="O47" s="17" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="V47">
         <f>IF(L47="","",L47+ROW()/100000)</f>
-        <v/>
+        <v>5.40047</v>
       </c>
     </row>
     <row r="48" ht="44" customHeight="1">
@@ -5697,11 +5697,11 @@
       </c>
       <c r="F48" s="17" t="n"/>
       <c r="G48" s="17" t="n"/>
-      <c r="H48" s="9">
+      <c r="H48" s="9" t="str">
         <f>IF(OR($A48&lt;&gt;"Yes",F48="",G48=""),"",MATCH(F48,Lists!$B$1:$B$5,0)*MATCH(G48,Lists!$C$1:$C$5,0))</f>
         <v/>
       </c>
-      <c r="I48" s="9">
+      <c r="I48" s="9" t="str">
         <f>IF(H48="","",IF(H48&gt;=17,"Critical",IF(H48&gt;=10,"High",IF(H48&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
@@ -5711,15 +5711,15 @@
         </is>
       </c>
       <c r="K48" s="17" t="n"/>
-      <c r="L48" s="9">
+      <c r="L48" s="9" t="str">
         <f>IF(OR(H48="",K48=""),"",ROUND(H48*VLOOKUP(K48,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
       </c>
-      <c r="M48" s="9">
+      <c r="M48" s="9" t="str">
         <f>IF(L48="","",IF(L48&gt;=17,"Critical",IF(L48&gt;=10,"High",IF(L48&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="N48" s="9">
+      <c r="N48" s="9" t="str">
         <f>IF(M48="","",IF(OR(M48="Low",M48="Medium"),"Yes","No"))</f>
         <v/>
       </c>
@@ -5733,7 +5733,7 @@
           <t>Contracts lacking no-training clause</t>
         </is>
       </c>
-      <c r="V48">
+      <c r="V48" t="str">
         <f>IF(L48="","",L48+ROW()/100000)</f>
         <v/>
       </c>
@@ -5776,11 +5776,11 @@
       </c>
       <c r="H49" s="9">
         <f>IF(OR($A49&lt;&gt;"Yes",F49="",G49=""),"",MATCH(F49,Lists!$B$1:$B$5,0)*MATCH(G49,Lists!$C$1:$C$5,0))</f>
-        <v/>
-      </c>
-      <c r="I49" s="9">
+        <v>6</v>
+      </c>
+      <c r="I49" s="9" t="str">
         <f>IF(H49="","",IF(H49&gt;=17,"Critical",IF(H49&gt;=10,"High",IF(H49&gt;=5,"Medium","Low"))))</f>
-        <v/>
+        <v>Medium</v>
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
@@ -5794,15 +5794,15 @@
       </c>
       <c r="L49" s="9">
         <f>IF(OR(H49="",K49=""),"",ROUND(H49*VLOOKUP(K49,Scales!$A$22:$B$25,2,FALSE),1))</f>
-        <v/>
-      </c>
-      <c r="M49" s="9">
+        <v>3.6</v>
+      </c>
+      <c r="M49" s="9" t="str">
         <f>IF(L49="","",IF(L49&gt;=17,"Critical",IF(L49&gt;=10,"High",IF(L49&gt;=5,"Medium","Low"))))</f>
-        <v/>
-      </c>
-      <c r="N49" s="9">
+        <v>Low</v>
+      </c>
+      <c r="N49" s="9" t="str">
         <f>IF(M49="","",IF(OR(M49="Low",M49="Medium"),"Yes","No"))</f>
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="O49" s="17" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
       </c>
       <c r="V49">
         <f>IF(L49="","",L49+ROW()/100000)</f>
-        <v/>
+        <v>3.60049</v>
       </c>
     </row>
     <row r="50" ht="44" customHeight="1">
@@ -5863,11 +5863,11 @@
       </c>
       <c r="F50" s="17" t="n"/>
       <c r="G50" s="17" t="n"/>
-      <c r="H50" s="9">
+      <c r="H50" s="9" t="str">
         <f>IF(OR($A50&lt;&gt;"Yes",F50="",G50=""),"",MATCH(F50,Lists!$B$1:$B$5,0)*MATCH(G50,Lists!$C$1:$C$5,0))</f>
         <v/>
       </c>
-      <c r="I50" s="9">
+      <c r="I50" s="9" t="str">
         <f>IF(H50="","",IF(H50&gt;=17,"Critical",IF(H50&gt;=10,"High",IF(H50&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
@@ -5877,15 +5877,15 @@
         </is>
       </c>
       <c r="K50" s="17" t="n"/>
-      <c r="L50" s="9">
+      <c r="L50" s="9" t="str">
         <f>IF(OR(H50="",K50=""),"",ROUND(H50*VLOOKUP(K50,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
       </c>
-      <c r="M50" s="9">
+      <c r="M50" s="9" t="str">
         <f>IF(L50="","",IF(L50&gt;=17,"Critical",IF(L50&gt;=10,"High",IF(L50&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="N50" s="9">
+      <c r="N50" s="9" t="str">
         <f>IF(M50="","",IF(OR(M50="Low",M50="Medium"),"Yes","No"))</f>
         <v/>
       </c>
@@ -5899,7 +5899,7 @@
           <t>AI spend vs budget</t>
         </is>
       </c>
-      <c r="V50">
+      <c r="V50" t="str">
         <f>IF(L50="","",L50+ROW()/100000)</f>
         <v/>
       </c>
@@ -5942,11 +5942,11 @@
       </c>
       <c r="H51" s="9">
         <f>IF(OR($A51&lt;&gt;"Yes",F51="",G51=""),"",MATCH(F51,Lists!$B$1:$B$5,0)*MATCH(G51,Lists!$C$1:$C$5,0))</f>
-        <v/>
-      </c>
-      <c r="I51" s="9">
+        <v>8</v>
+      </c>
+      <c r="I51" s="9" t="str">
         <f>IF(H51="","",IF(H51&gt;=17,"Critical",IF(H51&gt;=10,"High",IF(H51&gt;=5,"Medium","Low"))))</f>
-        <v/>
+        <v>Medium</v>
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
@@ -5960,15 +5960,15 @@
       </c>
       <c r="L51" s="9">
         <f>IF(OR(H51="",K51=""),"",ROUND(H51*VLOOKUP(K51,Scales!$A$22:$B$25,2,FALSE),1))</f>
-        <v/>
-      </c>
-      <c r="M51" s="9">
+        <v>4.8</v>
+      </c>
+      <c r="M51" s="9" t="str">
         <f>IF(L51="","",IF(L51&gt;=17,"Critical",IF(L51&gt;=10,"High",IF(L51&gt;=5,"Medium","Low"))))</f>
-        <v/>
-      </c>
-      <c r="N51" s="9">
+        <v>Low</v>
+      </c>
+      <c r="N51" s="9" t="str">
         <f>IF(M51="","",IF(OR(M51="Low",M51="Medium"),"Yes","No"))</f>
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="O51" s="17" t="inlineStr">
         <is>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="V51">
         <f>IF(L51="","",L51+ROW()/100000)</f>
-        <v/>
+        <v>4.80051</v>
       </c>
     </row>
     <row r="52" ht="44" customHeight="1">
@@ -6029,11 +6029,11 @@
       </c>
       <c r="F52" s="17" t="n"/>
       <c r="G52" s="17" t="n"/>
-      <c r="H52" s="9">
+      <c r="H52" s="9" t="str">
         <f>IF(OR($A52&lt;&gt;"Yes",F52="",G52=""),"",MATCH(F52,Lists!$B$1:$B$5,0)*MATCH(G52,Lists!$C$1:$C$5,0))</f>
         <v/>
       </c>
-      <c r="I52" s="9">
+      <c r="I52" s="9" t="str">
         <f>IF(H52="","",IF(H52&gt;=17,"Critical",IF(H52&gt;=10,"High",IF(H52&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
@@ -6043,15 +6043,15 @@
         </is>
       </c>
       <c r="K52" s="17" t="n"/>
-      <c r="L52" s="9">
+      <c r="L52" s="9" t="str">
         <f>IF(OR(H52="",K52=""),"",ROUND(H52*VLOOKUP(K52,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
       </c>
-      <c r="M52" s="9">
+      <c r="M52" s="9" t="str">
         <f>IF(L52="","",IF(L52&gt;=17,"Critical",IF(L52&gt;=10,"High",IF(L52&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="N52" s="9">
+      <c r="N52" s="9" t="str">
         <f>IF(M52="","",IF(OR(M52="Low",M52="Medium"),"Yes","No"))</f>
         <v/>
       </c>
@@ -6065,7 +6065,7 @@
           <t>kgCO2e per 1,000 inferences</t>
         </is>
       </c>
-      <c r="V52">
+      <c r="V52" t="str">
         <f>IF(L52="","",L52+ROW()/100000)</f>
         <v/>
       </c>
@@ -6098,11 +6098,11 @@
       </c>
       <c r="F53" s="17" t="n"/>
       <c r="G53" s="17" t="n"/>
-      <c r="H53" s="9">
+      <c r="H53" s="9" t="str">
         <f>IF(OR($A53&lt;&gt;"Yes",F53="",G53=""),"",MATCH(F53,Lists!$B$1:$B$5,0)*MATCH(G53,Lists!$C$1:$C$5,0))</f>
         <v/>
       </c>
-      <c r="I53" s="9">
+      <c r="I53" s="9" t="str">
         <f>IF(H53="","",IF(H53&gt;=17,"Critical",IF(H53&gt;=10,"High",IF(H53&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
@@ -6112,15 +6112,15 @@
         </is>
       </c>
       <c r="K53" s="17" t="n"/>
-      <c r="L53" s="9">
+      <c r="L53" s="9" t="str">
         <f>IF(OR(H53="",K53=""),"",ROUND(H53*VLOOKUP(K53,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
       </c>
-      <c r="M53" s="9">
+      <c r="M53" s="9" t="str">
         <f>IF(L53="","",IF(L53&gt;=17,"Critical",IF(L53&gt;=10,"High",IF(L53&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="N53" s="9">
+      <c r="N53" s="9" t="str">
         <f>IF(M53="","",IF(OR(M53="Low",M53="Medium"),"Yes","No"))</f>
         <v/>
       </c>
@@ -6134,7 +6134,7 @@
           <t>Content-policy violations per 1,000 outputs</t>
         </is>
       </c>
-      <c r="V53">
+      <c r="V53" t="str">
         <f>IF(L53="","",L53+ROW()/100000)</f>
         <v/>
       </c>
@@ -6177,11 +6177,11 @@
       </c>
       <c r="H54" s="9">
         <f>IF(OR($A54&lt;&gt;"Yes",F54="",G54=""),"",MATCH(F54,Lists!$B$1:$B$5,0)*MATCH(G54,Lists!$C$1:$C$5,0))</f>
-        <v/>
-      </c>
-      <c r="I54" s="9">
+        <v>12</v>
+      </c>
+      <c r="I54" s="9" t="str">
         <f>IF(H54="","",IF(H54&gt;=17,"Critical",IF(H54&gt;=10,"High",IF(H54&gt;=5,"Medium","Low"))))</f>
-        <v/>
+        <v>High</v>
       </c>
       <c r="J54" s="7" t="inlineStr">
         <is>
@@ -6195,15 +6195,15 @@
       </c>
       <c r="L54" s="9">
         <f>IF(OR(H54="",K54=""),"",ROUND(H54*VLOOKUP(K54,Scales!$A$22:$B$25,2,FALSE),1))</f>
-        <v/>
-      </c>
-      <c r="M54" s="9">
+        <v>7.2</v>
+      </c>
+      <c r="M54" s="9" t="str">
         <f>IF(L54="","",IF(L54&gt;=17,"Critical",IF(L54&gt;=10,"High",IF(L54&gt;=5,"Medium","Low"))))</f>
-        <v/>
-      </c>
-      <c r="N54" s="9">
+        <v>Medium</v>
+      </c>
+      <c r="N54" s="9" t="str">
         <f>IF(M54="","",IF(OR(M54="Low",M54="Medium"),"Yes","No"))</f>
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="O54" s="17" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
       </c>
       <c r="V54">
         <f>IF(L54="","",L54+ROW()/100000)</f>
-        <v/>
+        <v>7.20054</v>
       </c>
     </row>
     <row r="55" ht="44" customHeight="1">
@@ -6274,11 +6274,11 @@
       </c>
       <c r="H55" s="9">
         <f>IF(OR($A55&lt;&gt;"Yes",F55="",G55=""),"",MATCH(F55,Lists!$B$1:$B$5,0)*MATCH(G55,Lists!$C$1:$C$5,0))</f>
-        <v/>
-      </c>
-      <c r="I55" s="9">
+        <v>12</v>
+      </c>
+      <c r="I55" s="9" t="str">
         <f>IF(H55="","",IF(H55&gt;=17,"Critical",IF(H55&gt;=10,"High",IF(H55&gt;=5,"Medium","Low"))))</f>
-        <v/>
+        <v>High</v>
       </c>
       <c r="J55" s="7" t="inlineStr">
         <is>
@@ -6292,15 +6292,15 @@
       </c>
       <c r="L55" s="9">
         <f>IF(OR(H55="",K55=""),"",ROUND(H55*VLOOKUP(K55,Scales!$A$22:$B$25,2,FALSE),1))</f>
-        <v/>
-      </c>
-      <c r="M55" s="9">
+        <v>7.2</v>
+      </c>
+      <c r="M55" s="9" t="str">
         <f>IF(L55="","",IF(L55&gt;=17,"Critical",IF(L55&gt;=10,"High",IF(L55&gt;=5,"Medium","Low"))))</f>
-        <v/>
-      </c>
-      <c r="N55" s="9">
+        <v>Medium</v>
+      </c>
+      <c r="N55" s="9" t="str">
         <f>IF(M55="","",IF(OR(M55="Low",M55="Medium"),"Yes","No"))</f>
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="O55" s="17" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
       </c>
       <c r="V55">
         <f>IF(L55="","",L55+ROW()/100000)</f>
-        <v/>
+        <v>7.20055</v>
       </c>
     </row>
     <row r="56" ht="44" customHeight="1">
@@ -6361,11 +6361,11 @@
       </c>
       <c r="F56" s="17" t="n"/>
       <c r="G56" s="17" t="n"/>
-      <c r="H56" s="9">
+      <c r="H56" s="9" t="str">
         <f>IF(OR($A56&lt;&gt;"Yes",F56="",G56=""),"",MATCH(F56,Lists!$B$1:$B$5,0)*MATCH(G56,Lists!$C$1:$C$5,0))</f>
         <v/>
       </c>
-      <c r="I56" s="9">
+      <c r="I56" s="9" t="str">
         <f>IF(H56="","",IF(H56&gt;=17,"Critical",IF(H56&gt;=10,"High",IF(H56&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
@@ -6375,15 +6375,15 @@
         </is>
       </c>
       <c r="K56" s="17" t="n"/>
-      <c r="L56" s="9">
+      <c r="L56" s="9" t="str">
         <f>IF(OR(H56="",K56=""),"",ROUND(H56*VLOOKUP(K56,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
       </c>
-      <c r="M56" s="9">
+      <c r="M56" s="9" t="str">
         <f>IF(L56="","",IF(L56&gt;=17,"Critical",IF(L56&gt;=10,"High",IF(L56&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="N56" s="9">
+      <c r="N56" s="9" t="str">
         <f>IF(M56="","",IF(OR(M56="Low",M56="Medium"),"Yes","No"))</f>
         <v/>
       </c>
@@ -6397,7 +6397,7 @@
           <t>Mean time to remediate critical vulnerabilities</t>
         </is>
       </c>
-      <c r="V56">
+      <c r="V56" t="str">
         <f>IF(L56="","",L56+ROW()/100000)</f>
         <v/>
       </c>
@@ -6414,25 +6414,25 @@
       <c r="E57" s="7" t="n"/>
       <c r="F57" s="17" t="n"/>
       <c r="G57" s="17" t="n"/>
-      <c r="H57" s="9">
+      <c r="H57" s="9" t="str">
         <f>IF(OR($A57&lt;&gt;"Yes",F57="",G57=""),"",MATCH(F57,Lists!$B$1:$B$5,0)*MATCH(G57,Lists!$C$1:$C$5,0))</f>
         <v/>
       </c>
-      <c r="I57" s="9">
+      <c r="I57" s="9" t="str">
         <f>IF(H57="","",IF(H57&gt;=17,"Critical",IF(H57&gt;=10,"High",IF(H57&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
       <c r="J57" s="7" t="n"/>
       <c r="K57" s="17" t="n"/>
-      <c r="L57" s="9">
+      <c r="L57" s="9" t="str">
         <f>IF(OR(H57="",K57=""),"",ROUND(H57*VLOOKUP(K57,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
       </c>
-      <c r="M57" s="9">
+      <c r="M57" s="9" t="str">
         <f>IF(L57="","",IF(L57&gt;=17,"Critical",IF(L57&gt;=10,"High",IF(L57&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="N57" s="9">
+      <c r="N57" s="9" t="str">
         <f>IF(M57="","",IF(OR(M57="Low",M57="Medium"),"Yes","No"))</f>
         <v/>
       </c>
@@ -6442,7 +6442,7 @@
       <c r="R57" s="17" t="n"/>
       <c r="S57" s="17" t="n"/>
       <c r="T57" s="7" t="n"/>
-      <c r="V57">
+      <c r="V57" t="str">
         <f>IF(L57="","",L57+ROW()/100000)</f>
         <v/>
       </c>
@@ -6459,25 +6459,25 @@
       <c r="E58" s="7" t="n"/>
       <c r="F58" s="17" t="n"/>
       <c r="G58" s="17" t="n"/>
-      <c r="H58" s="9">
+      <c r="H58" s="9" t="str">
         <f>IF(OR($A58&lt;&gt;"Yes",F58="",G58=""),"",MATCH(F58,Lists!$B$1:$B$5,0)*MATCH(G58,Lists!$C$1:$C$5,0))</f>
         <v/>
       </c>
-      <c r="I58" s="9">
+      <c r="I58" s="9" t="str">
         <f>IF(H58="","",IF(H58&gt;=17,"Critical",IF(H58&gt;=10,"High",IF(H58&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
       <c r="J58" s="7" t="n"/>
       <c r="K58" s="17" t="n"/>
-      <c r="L58" s="9">
+      <c r="L58" s="9" t="str">
         <f>IF(OR(H58="",K58=""),"",ROUND(H58*VLOOKUP(K58,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
       </c>
-      <c r="M58" s="9">
+      <c r="M58" s="9" t="str">
         <f>IF(L58="","",IF(L58&gt;=17,"Critical",IF(L58&gt;=10,"High",IF(L58&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="N58" s="9">
+      <c r="N58" s="9" t="str">
         <f>IF(M58="","",IF(OR(M58="Low",M58="Medium"),"Yes","No"))</f>
         <v/>
       </c>
@@ -6487,7 +6487,7 @@
       <c r="R58" s="17" t="n"/>
       <c r="S58" s="17" t="n"/>
       <c r="T58" s="7" t="n"/>
-      <c r="V58">
+      <c r="V58" t="str">
         <f>IF(L58="","",L58+ROW()/100000)</f>
         <v/>
       </c>
@@ -6504,25 +6504,25 @@
       <c r="E59" s="7" t="n"/>
       <c r="F59" s="17" t="n"/>
       <c r="G59" s="17" t="n"/>
-      <c r="H59" s="9">
+      <c r="H59" s="9" t="str">
         <f>IF(OR($A59&lt;&gt;"Yes",F59="",G59=""),"",MATCH(F59,Lists!$B$1:$B$5,0)*MATCH(G59,Lists!$C$1:$C$5,0))</f>
         <v/>
       </c>
-      <c r="I59" s="9">
+      <c r="I59" s="9" t="str">
         <f>IF(H59="","",IF(H59&gt;=17,"Critical",IF(H59&gt;=10,"High",IF(H59&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
       <c r="J59" s="7" t="n"/>
       <c r="K59" s="17" t="n"/>
-      <c r="L59" s="9">
+      <c r="L59" s="9" t="str">
         <f>IF(OR(H59="",K59=""),"",ROUND(H59*VLOOKUP(K59,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
       </c>
-      <c r="M59" s="9">
+      <c r="M59" s="9" t="str">
         <f>IF(L59="","",IF(L59&gt;=17,"Critical",IF(L59&gt;=10,"High",IF(L59&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="N59" s="9">
+      <c r="N59" s="9" t="str">
         <f>IF(M59="","",IF(OR(M59="Low",M59="Medium"),"Yes","No"))</f>
         <v/>
       </c>
@@ -6532,7 +6532,7 @@
       <c r="R59" s="17" t="n"/>
       <c r="S59" s="17" t="n"/>
       <c r="T59" s="7" t="n"/>
-      <c r="V59">
+      <c r="V59" t="str">
         <f>IF(L59="","",L59+ROW()/100000)</f>
         <v/>
       </c>
@@ -6549,25 +6549,25 @@
       <c r="E60" s="7" t="n"/>
       <c r="F60" s="17" t="n"/>
       <c r="G60" s="17" t="n"/>
-      <c r="H60" s="9">
+      <c r="H60" s="9" t="str">
         <f>IF(OR($A60&lt;&gt;"Yes",F60="",G60=""),"",MATCH(F60,Lists!$B$1:$B$5,0)*MATCH(G60,Lists!$C$1:$C$5,0))</f>
         <v/>
       </c>
-      <c r="I60" s="9">
+      <c r="I60" s="9" t="str">
         <f>IF(H60="","",IF(H60&gt;=17,"Critical",IF(H60&gt;=10,"High",IF(H60&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
       <c r="J60" s="7" t="n"/>
       <c r="K60" s="17" t="n"/>
-      <c r="L60" s="9">
+      <c r="L60" s="9" t="str">
         <f>IF(OR(H60="",K60=""),"",ROUND(H60*VLOOKUP(K60,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
       </c>
-      <c r="M60" s="9">
+      <c r="M60" s="9" t="str">
         <f>IF(L60="","",IF(L60&gt;=17,"Critical",IF(L60&gt;=10,"High",IF(L60&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="N60" s="9">
+      <c r="N60" s="9" t="str">
         <f>IF(M60="","",IF(OR(M60="Low",M60="Medium"),"Yes","No"))</f>
         <v/>
       </c>
@@ -6577,7 +6577,7 @@
       <c r="R60" s="17" t="n"/>
       <c r="S60" s="17" t="n"/>
       <c r="T60" s="7" t="n"/>
-      <c r="V60">
+      <c r="V60" t="str">
         <f>IF(L60="","",L60+ROW()/100000)</f>
         <v/>
       </c>
@@ -6594,25 +6594,25 @@
       <c r="E61" s="7" t="n"/>
       <c r="F61" s="17" t="n"/>
       <c r="G61" s="17" t="n"/>
-      <c r="H61" s="9">
+      <c r="H61" s="9" t="str">
         <f>IF(OR($A61&lt;&gt;"Yes",F61="",G61=""),"",MATCH(F61,Lists!$B$1:$B$5,0)*MATCH(G61,Lists!$C$1:$C$5,0))</f>
         <v/>
       </c>
-      <c r="I61" s="9">
+      <c r="I61" s="9" t="str">
         <f>IF(H61="","",IF(H61&gt;=17,"Critical",IF(H61&gt;=10,"High",IF(H61&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
       <c r="J61" s="7" t="n"/>
       <c r="K61" s="17" t="n"/>
-      <c r="L61" s="9">
+      <c r="L61" s="9" t="str">
         <f>IF(OR(H61="",K61=""),"",ROUND(H61*VLOOKUP(K61,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
       </c>
-      <c r="M61" s="9">
+      <c r="M61" s="9" t="str">
         <f>IF(L61="","",IF(L61&gt;=17,"Critical",IF(L61&gt;=10,"High",IF(L61&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="N61" s="9">
+      <c r="N61" s="9" t="str">
         <f>IF(M61="","",IF(OR(M61="Low",M61="Medium"),"Yes","No"))</f>
         <v/>
       </c>
@@ -6622,7 +6622,7 @@
       <c r="R61" s="17" t="n"/>
       <c r="S61" s="17" t="n"/>
       <c r="T61" s="7" t="n"/>
-      <c r="V61">
+      <c r="V61" t="str">
         <f>IF(L61="","",L61+ROW()/100000)</f>
         <v/>
       </c>
@@ -6639,25 +6639,25 @@
       <c r="E62" s="7" t="n"/>
       <c r="F62" s="17" t="n"/>
       <c r="G62" s="17" t="n"/>
-      <c r="H62" s="9">
+      <c r="H62" s="9" t="str">
         <f>IF(OR($A62&lt;&gt;"Yes",F62="",G62=""),"",MATCH(F62,Lists!$B$1:$B$5,0)*MATCH(G62,Lists!$C$1:$C$5,0))</f>
         <v/>
       </c>
-      <c r="I62" s="9">
+      <c r="I62" s="9" t="str">
         <f>IF(H62="","",IF(H62&gt;=17,"Critical",IF(H62&gt;=10,"High",IF(H62&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
       <c r="J62" s="7" t="n"/>
       <c r="K62" s="17" t="n"/>
-      <c r="L62" s="9">
+      <c r="L62" s="9" t="str">
         <f>IF(OR(H62="",K62=""),"",ROUND(H62*VLOOKUP(K62,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
       </c>
-      <c r="M62" s="9">
+      <c r="M62" s="9" t="str">
         <f>IF(L62="","",IF(L62&gt;=17,"Critical",IF(L62&gt;=10,"High",IF(L62&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="N62" s="9">
+      <c r="N62" s="9" t="str">
         <f>IF(M62="","",IF(OR(M62="Low",M62="Medium"),"Yes","No"))</f>
         <v/>
       </c>
@@ -6667,7 +6667,7 @@
       <c r="R62" s="17" t="n"/>
       <c r="S62" s="17" t="n"/>
       <c r="T62" s="7" t="n"/>
-      <c r="V62">
+      <c r="V62" t="str">
         <f>IF(L62="","",L62+ROW()/100000)</f>
         <v/>
       </c>
@@ -6684,25 +6684,25 @@
       <c r="E63" s="7" t="n"/>
       <c r="F63" s="17" t="n"/>
       <c r="G63" s="17" t="n"/>
-      <c r="H63" s="9">
+      <c r="H63" s="9" t="str">
         <f>IF(OR($A63&lt;&gt;"Yes",F63="",G63=""),"",MATCH(F63,Lists!$B$1:$B$5,0)*MATCH(G63,Lists!$C$1:$C$5,0))</f>
         <v/>
       </c>
-      <c r="I63" s="9">
+      <c r="I63" s="9" t="str">
         <f>IF(H63="","",IF(H63&gt;=17,"Critical",IF(H63&gt;=10,"High",IF(H63&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
       <c r="J63" s="7" t="n"/>
       <c r="K63" s="17" t="n"/>
-      <c r="L63" s="9">
+      <c r="L63" s="9" t="str">
         <f>IF(OR(H63="",K63=""),"",ROUND(H63*VLOOKUP(K63,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
       </c>
-      <c r="M63" s="9">
+      <c r="M63" s="9" t="str">
         <f>IF(L63="","",IF(L63&gt;=17,"Critical",IF(L63&gt;=10,"High",IF(L63&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="N63" s="9">
+      <c r="N63" s="9" t="str">
         <f>IF(M63="","",IF(OR(M63="Low",M63="Medium"),"Yes","No"))</f>
         <v/>
       </c>
@@ -6712,7 +6712,7 @@
       <c r="R63" s="17" t="n"/>
       <c r="S63" s="17" t="n"/>
       <c r="T63" s="7" t="n"/>
-      <c r="V63">
+      <c r="V63" t="str">
         <f>IF(L63="","",L63+ROW()/100000)</f>
         <v/>
       </c>
@@ -6729,25 +6729,25 @@
       <c r="E64" s="7" t="n"/>
       <c r="F64" s="17" t="n"/>
       <c r="G64" s="17" t="n"/>
-      <c r="H64" s="9">
+      <c r="H64" s="9" t="str">
         <f>IF(OR($A64&lt;&gt;"Yes",F64="",G64=""),"",MATCH(F64,Lists!$B$1:$B$5,0)*MATCH(G64,Lists!$C$1:$C$5,0))</f>
         <v/>
       </c>
-      <c r="I64" s="9">
+      <c r="I64" s="9" t="str">
         <f>IF(H64="","",IF(H64&gt;=17,"Critical",IF(H64&gt;=10,"High",IF(H64&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
       <c r="J64" s="7" t="n"/>
       <c r="K64" s="17" t="n"/>
-      <c r="L64" s="9">
+      <c r="L64" s="9" t="str">
         <f>IF(OR(H64="",K64=""),"",ROUND(H64*VLOOKUP(K64,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
       </c>
-      <c r="M64" s="9">
+      <c r="M64" s="9" t="str">
         <f>IF(L64="","",IF(L64&gt;=17,"Critical",IF(L64&gt;=10,"High",IF(L64&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="N64" s="9">
+      <c r="N64" s="9" t="str">
         <f>IF(M64="","",IF(OR(M64="Low",M64="Medium"),"Yes","No"))</f>
         <v/>
       </c>
@@ -6757,7 +6757,7 @@
       <c r="R64" s="17" t="n"/>
       <c r="S64" s="17" t="n"/>
       <c r="T64" s="7" t="n"/>
-      <c r="V64">
+      <c r="V64" t="str">
         <f>IF(L64="","",L64+ROW()/100000)</f>
         <v/>
       </c>
@@ -6774,25 +6774,25 @@
       <c r="E65" s="7" t="n"/>
       <c r="F65" s="17" t="n"/>
       <c r="G65" s="17" t="n"/>
-      <c r="H65" s="9">
+      <c r="H65" s="9" t="str">
         <f>IF(OR($A65&lt;&gt;"Yes",F65="",G65=""),"",MATCH(F65,Lists!$B$1:$B$5,0)*MATCH(G65,Lists!$C$1:$C$5,0))</f>
         <v/>
       </c>
-      <c r="I65" s="9">
+      <c r="I65" s="9" t="str">
         <f>IF(H65="","",IF(H65&gt;=17,"Critical",IF(H65&gt;=10,"High",IF(H65&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
       <c r="J65" s="7" t="n"/>
       <c r="K65" s="17" t="n"/>
-      <c r="L65" s="9">
+      <c r="L65" s="9" t="str">
         <f>IF(OR(H65="",K65=""),"",ROUND(H65*VLOOKUP(K65,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
       </c>
-      <c r="M65" s="9">
+      <c r="M65" s="9" t="str">
         <f>IF(L65="","",IF(L65&gt;=17,"Critical",IF(L65&gt;=10,"High",IF(L65&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="N65" s="9">
+      <c r="N65" s="9" t="str">
         <f>IF(M65="","",IF(OR(M65="Low",M65="Medium"),"Yes","No"))</f>
         <v/>
       </c>
@@ -6802,7 +6802,7 @@
       <c r="R65" s="17" t="n"/>
       <c r="S65" s="17" t="n"/>
       <c r="T65" s="7" t="n"/>
-      <c r="V65">
+      <c r="V65" t="str">
         <f>IF(L65="","",L65+ROW()/100000)</f>
         <v/>
       </c>
@@ -6819,25 +6819,25 @@
       <c r="E66" s="7" t="n"/>
       <c r="F66" s="17" t="n"/>
       <c r="G66" s="17" t="n"/>
-      <c r="H66" s="9">
+      <c r="H66" s="9" t="str">
         <f>IF(OR($A66&lt;&gt;"Yes",F66="",G66=""),"",MATCH(F66,Lists!$B$1:$B$5,0)*MATCH(G66,Lists!$C$1:$C$5,0))</f>
         <v/>
       </c>
-      <c r="I66" s="9">
+      <c r="I66" s="9" t="str">
         <f>IF(H66="","",IF(H66&gt;=17,"Critical",IF(H66&gt;=10,"High",IF(H66&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
       <c r="J66" s="7" t="n"/>
       <c r="K66" s="17" t="n"/>
-      <c r="L66" s="9">
+      <c r="L66" s="9" t="str">
         <f>IF(OR(H66="",K66=""),"",ROUND(H66*VLOOKUP(K66,Scales!$A$22:$B$25,2,FALSE),1))</f>
         <v/>
       </c>
-      <c r="M66" s="9">
+      <c r="M66" s="9" t="str">
         <f>IF(L66="","",IF(L66&gt;=17,"Critical",IF(L66&gt;=10,"High",IF(L66&gt;=5,"Medium","Low"))))</f>
         <v/>
       </c>
-      <c r="N66" s="9">
+      <c r="N66" s="9" t="str">
         <f>IF(M66="","",IF(OR(M66="Low",M66="Medium"),"Yes","No"))</f>
         <v/>
       </c>
@@ -6847,7 +6847,7 @@
       <c r="R66" s="17" t="n"/>
       <c r="S66" s="17" t="n"/>
       <c r="T66" s="7" t="n"/>
-      <c r="V66">
+      <c r="V66" t="str">
         <f>IF(L66="","",L66+ROW()/100000)</f>
         <v/>
       </c>
@@ -6962,9 +6962,9 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18">
+      <c r="A2" s="18" t="str">
         <f>"Use case: "&amp;IF('1. Use Case Profile'!$C$5="","(not specified)",'1. Use Case Profile'!$C$5)&amp;"   |   Inherent tier: "&amp;'3. Risk Tiering'!$C$21&amp;"   |   Tiering score: "&amp;'3. Risk Tiering'!$C$17</f>
-        <v/>
+        <v>Use case: Example: 'Ask Aya' - GenAI customer-service assistant with account-servicing actions   |   Inherent tier: High   |   Tiering score: 74</v>
       </c>
     </row>
     <row r="4">
@@ -7029,23 +7029,23 @@
       </c>
       <c r="B6" s="20">
         <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Almost certain",'4. Risk Register'!$G$5:$G$66,"Insignificant")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C6" s="21">
         <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Almost certain",'4. Risk Register'!$G$5:$G$66,"Minor")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D6" s="21">
         <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Almost certain",'4. Risk Register'!$G$5:$G$66,"Moderate")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E6" s="22">
         <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Almost certain",'4. Risk Register'!$G$5:$G$66,"Major")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F6" s="22">
         <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Almost certain",'4. Risk Register'!$G$5:$G$66,"Severe")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H6" s="23" t="inlineStr">
         <is>
@@ -7054,11 +7054,11 @@
       </c>
       <c r="I6" s="9">
         <f>COUNTIF('4. Risk Register'!$I$5:$I$66,"Critical")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J6" s="9">
         <f>COUNTIF('4. Risk Register'!$M$5:$M$66,"Critical")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
@@ -7069,23 +7069,23 @@
       </c>
       <c r="B7" s="24">
         <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Likely",'4. Risk Register'!$G$5:$G$66,"Insignificant")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C7" s="20">
         <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Likely",'4. Risk Register'!$G$5:$G$66,"Minor")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D7" s="21">
         <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Likely",'4. Risk Register'!$G$5:$G$66,"Moderate")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="E7" s="21">
         <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Likely",'4. Risk Register'!$G$5:$G$66,"Major")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F7" s="22">
         <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Likely",'4. Risk Register'!$G$5:$G$66,"Severe")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H7" s="25" t="inlineStr">
         <is>
@@ -7094,11 +7094,11 @@
       </c>
       <c r="I7" s="9">
         <f>COUNTIF('4. Risk Register'!$I$5:$I$66,"High")</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="J7" s="9">
         <f>COUNTIF('4. Risk Register'!$M$5:$M$66,"High")</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
@@ -7109,23 +7109,23 @@
       </c>
       <c r="B8" s="24">
         <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Possible",'4. Risk Register'!$G$5:$G$66,"Insignificant")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C8" s="20">
         <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Possible",'4. Risk Register'!$G$5:$G$66,"Minor")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D8" s="20">
         <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Possible",'4. Risk Register'!$G$5:$G$66,"Moderate")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="E8" s="21">
         <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Possible",'4. Risk Register'!$G$5:$G$66,"Major")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="F8" s="21">
         <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Possible",'4. Risk Register'!$G$5:$G$66,"Severe")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="H8" s="26" t="inlineStr">
         <is>
@@ -7134,11 +7134,11 @@
       </c>
       <c r="I8" s="9">
         <f>COUNTIF('4. Risk Register'!$I$5:$I$66,"Medium")</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="J8" s="9">
         <f>COUNTIF('4. Risk Register'!$M$5:$M$66,"Medium")</f>
-        <v/>
+        <v>9</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
@@ -7149,23 +7149,23 @@
       </c>
       <c r="B9" s="24">
         <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Unlikely",'4. Risk Register'!$G$5:$G$66,"Insignificant")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C9" s="24">
         <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Unlikely",'4. Risk Register'!$G$5:$G$66,"Minor")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D9" s="20">
         <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Unlikely",'4. Risk Register'!$G$5:$G$66,"Moderate")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="E9" s="20">
         <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Unlikely",'4. Risk Register'!$G$5:$G$66,"Major")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F9" s="21">
         <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Unlikely",'4. Risk Register'!$G$5:$G$66,"Severe")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H9" s="27" t="inlineStr">
         <is>
@@ -7174,11 +7174,11 @@
       </c>
       <c r="I9" s="9">
         <f>COUNTIF('4. Risk Register'!$I$5:$I$66,"Low")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J9" s="9">
         <f>COUNTIF('4. Risk Register'!$M$5:$M$66,"Low")</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1">
@@ -7189,23 +7189,23 @@
       </c>
       <c r="B10" s="24">
         <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Rare",'4. Risk Register'!$G$5:$G$66,"Insignificant")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C10" s="24">
         <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Rare",'4. Risk Register'!$G$5:$G$66,"Minor")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D10" s="24">
         <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Rare",'4. Risk Register'!$G$5:$G$66,"Moderate")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E10" s="24">
         <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Rare",'4. Risk Register'!$G$5:$G$66,"Major")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F10" s="20">
         <f>COUNTIFS('4. Risk Register'!$A$5:$A$66,"Yes",'4. Risk Register'!$F$5:$F$66,"Rare",'4. Risk Register'!$G$5:$G$66,"Severe")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H10" s="13" t="inlineStr">
         <is>
@@ -7214,11 +7214,11 @@
       </c>
       <c r="I10" s="11">
         <f>SUM(I6:I9)</f>
-        <v/>
+        <v>18</v>
       </c>
       <c r="J10" s="11">
         <f>SUM(J6:J9)</f>
-        <v/>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
@@ -7235,7 +7235,7 @@
       <c r="I11" s="12" t="n"/>
       <c r="J11" s="11">
         <f>J6+J7</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -7292,27 +7292,27 @@
       </c>
       <c r="D16" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Governance &amp; Accountability",'4. Risk Register'!$A$5:$A$66,"Yes")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="E16" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Governance &amp; Accountability",'4. Risk Register'!$M$5:$M$66,"Critical")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F16" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Governance &amp; Accountability",'4. Risk Register'!$M$5:$M$66,"High")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G16" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Governance &amp; Accountability",'4. Risk Register'!$M$5:$M$66,"Medium")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H16" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Governance &amp; Accountability",'4. Risk Register'!$M$5:$M$66,"Low")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I16" s="9">
         <f>IFERROR(ROUND(AVERAGEIFS('4. Risk Register'!$L$5:$L$66,'4. Risk Register'!$C$5:$C$66,"Governance &amp; Accountability",'4. Risk Register'!$A$5:$A$66,"Yes"),1),"-")</f>
-        <v/>
+        <v>7.2</v>
       </c>
     </row>
     <row r="17">
@@ -7323,27 +7323,27 @@
       </c>
       <c r="D17" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Legal, Regulatory &amp; Compliance",'4. Risk Register'!$A$5:$A$66,"Yes")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="E17" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Legal, Regulatory &amp; Compliance",'4. Risk Register'!$M$5:$M$66,"Critical")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F17" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Legal, Regulatory &amp; Compliance",'4. Risk Register'!$M$5:$M$66,"High")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G17" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Legal, Regulatory &amp; Compliance",'4. Risk Register'!$M$5:$M$66,"Medium")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H17" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Legal, Regulatory &amp; Compliance",'4. Risk Register'!$M$5:$M$66,"Low")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I17" s="9">
         <f>IFERROR(ROUND(AVERAGEIFS('4. Risk Register'!$L$5:$L$66,'4. Risk Register'!$C$5:$C$66,"Legal, Regulatory &amp; Compliance",'4. Risk Register'!$A$5:$A$66,"Yes"),1),"-")</f>
-        <v/>
+        <v>7.2</v>
       </c>
     </row>
     <row r="18">
@@ -7354,27 +7354,27 @@
       </c>
       <c r="D18" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Fairness, Bias &amp; Human Rights",'4. Risk Register'!$A$5:$A$66,"Yes")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="E18" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Fairness, Bias &amp; Human Rights",'4. Risk Register'!$M$5:$M$66,"Critical")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F18" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Fairness, Bias &amp; Human Rights",'4. Risk Register'!$M$5:$M$66,"High")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G18" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Fairness, Bias &amp; Human Rights",'4. Risk Register'!$M$5:$M$66,"Medium")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H18" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Fairness, Bias &amp; Human Rights",'4. Risk Register'!$M$5:$M$66,"Low")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I18" s="9">
         <f>IFERROR(ROUND(AVERAGEIFS('4. Risk Register'!$L$5:$L$66,'4. Risk Register'!$C$5:$C$66,"Fairness, Bias &amp; Human Rights",'4. Risk Register'!$A$5:$A$66,"Yes"),1),"-")</f>
-        <v/>
+        <v>7.2</v>
       </c>
     </row>
     <row r="19">
@@ -7385,27 +7385,27 @@
       </c>
       <c r="D19" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Privacy &amp; Data Protection",'4. Risk Register'!$A$5:$A$66,"Yes")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="E19" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Privacy &amp; Data Protection",'4. Risk Register'!$M$5:$M$66,"Critical")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F19" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Privacy &amp; Data Protection",'4. Risk Register'!$M$5:$M$66,"High")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G19" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Privacy &amp; Data Protection",'4. Risk Register'!$M$5:$M$66,"Medium")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H19" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Privacy &amp; Data Protection",'4. Risk Register'!$M$5:$M$66,"Low")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I19" s="9">
         <f>IFERROR(ROUND(AVERAGEIFS('4. Risk Register'!$L$5:$L$66,'4. Risk Register'!$C$5:$C$66,"Privacy &amp; Data Protection",'4. Risk Register'!$A$5:$A$66,"Yes"),1),"-")</f>
-        <v/>
+        <v>7.6</v>
       </c>
     </row>
     <row r="20">
@@ -7416,27 +7416,27 @@
       </c>
       <c r="D20" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Data Quality &amp; Integrity",'4. Risk Register'!$A$5:$A$66,"Yes")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E20" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Data Quality &amp; Integrity",'4. Risk Register'!$M$5:$M$66,"Critical")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F20" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Data Quality &amp; Integrity",'4. Risk Register'!$M$5:$M$66,"High")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G20" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Data Quality &amp; Integrity",'4. Risk Register'!$M$5:$M$66,"Medium")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H20" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Data Quality &amp; Integrity",'4. Risk Register'!$M$5:$M$66,"Low")</f>
-        <v/>
-      </c>
-      <c r="I20" s="9">
+        <v>0</v>
+      </c>
+      <c r="I20" s="9" t="str">
         <f>IFERROR(ROUND(AVERAGEIFS('4. Risk Register'!$L$5:$L$66,'4. Risk Register'!$C$5:$C$66,"Data Quality &amp; Integrity",'4. Risk Register'!$A$5:$A$66,"Yes"),1),"-")</f>
-        <v/>
+        <v>-</v>
       </c>
     </row>
     <row r="21">
@@ -7447,27 +7447,27 @@
       </c>
       <c r="D21" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Model Performance, Reliability &amp; Robustness",'4. Risk Register'!$A$5:$A$66,"Yes")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="E21" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Model Performance, Reliability &amp; Robustness",'4. Risk Register'!$M$5:$M$66,"Critical")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F21" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Model Performance, Reliability &amp; Robustness",'4. Risk Register'!$M$5:$M$66,"High")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G21" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Model Performance, Reliability &amp; Robustness",'4. Risk Register'!$M$5:$M$66,"Medium")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H21" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Model Performance, Reliability &amp; Robustness",'4. Risk Register'!$M$5:$M$66,"Low")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I21" s="9">
         <f>IFERROR(ROUND(AVERAGEIFS('4. Risk Register'!$L$5:$L$66,'4. Risk Register'!$C$5:$C$66,"Model Performance, Reliability &amp; Robustness",'4. Risk Register'!$A$5:$A$66,"Yes"),1),"-")</f>
-        <v/>
+        <v>9.6</v>
       </c>
     </row>
     <row r="22">
@@ -7478,27 +7478,27 @@
       </c>
       <c r="D22" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Transparency, Explainability &amp; Contestability",'4. Risk Register'!$A$5:$A$66,"Yes")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="E22" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Transparency, Explainability &amp; Contestability",'4. Risk Register'!$M$5:$M$66,"Critical")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F22" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Transparency, Explainability &amp; Contestability",'4. Risk Register'!$M$5:$M$66,"High")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G22" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Transparency, Explainability &amp; Contestability",'4. Risk Register'!$M$5:$M$66,"Medium")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H22" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Transparency, Explainability &amp; Contestability",'4. Risk Register'!$M$5:$M$66,"Low")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I22" s="9">
         <f>IFERROR(ROUND(AVERAGEIFS('4. Risk Register'!$L$5:$L$66,'4. Risk Register'!$C$5:$C$66,"Transparency, Explainability &amp; Contestability",'4. Risk Register'!$A$5:$A$66,"Yes"),1),"-")</f>
-        <v/>
+        <v>3.6</v>
       </c>
     </row>
     <row r="23">
@@ -7509,27 +7509,27 @@
       </c>
       <c r="D23" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Security of AI Systems",'4. Risk Register'!$A$5:$A$66,"Yes")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="E23" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Security of AI Systems",'4. Risk Register'!$M$5:$M$66,"Critical")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F23" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Security of AI Systems",'4. Risk Register'!$M$5:$M$66,"High")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G23" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Security of AI Systems",'4. Risk Register'!$M$5:$M$66,"Medium")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H23" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Security of AI Systems",'4. Risk Register'!$M$5:$M$66,"Low")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I23" s="9">
         <f>IFERROR(ROUND(AVERAGEIFS('4. Risk Register'!$L$5:$L$66,'4. Risk Register'!$C$5:$C$66,"Security of AI Systems",'4. Risk Register'!$A$5:$A$66,"Yes"),1),"-")</f>
-        <v/>
+        <v>11.5</v>
       </c>
     </row>
     <row r="24">
@@ -7540,27 +7540,27 @@
       </c>
       <c r="D24" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Human Oversight &amp; Autonomy",'4. Risk Register'!$A$5:$A$66,"Yes")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="E24" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Human Oversight &amp; Autonomy",'4. Risk Register'!$M$5:$M$66,"Critical")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F24" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Human Oversight &amp; Autonomy",'4. Risk Register'!$M$5:$M$66,"High")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G24" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Human Oversight &amp; Autonomy",'4. Risk Register'!$M$5:$M$66,"Medium")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H24" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Human Oversight &amp; Autonomy",'4. Risk Register'!$M$5:$M$66,"Low")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I24" s="9">
         <f>IFERROR(ROUND(AVERAGEIFS('4. Risk Register'!$L$5:$L$66,'4. Risk Register'!$C$5:$C$66,"Human Oversight &amp; Autonomy",'4. Risk Register'!$A$5:$A$66,"Yes"),1),"-")</f>
-        <v/>
+        <v>8.7</v>
       </c>
     </row>
     <row r="25">
@@ -7571,27 +7571,27 @@
       </c>
       <c r="D25" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Third-Party &amp; Supply Chain",'4. Risk Register'!$A$5:$A$66,"Yes")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="E25" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Third-Party &amp; Supply Chain",'4. Risk Register'!$M$5:$M$66,"Critical")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F25" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Third-Party &amp; Supply Chain",'4. Risk Register'!$M$5:$M$66,"High")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G25" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Third-Party &amp; Supply Chain",'4. Risk Register'!$M$5:$M$66,"Medium")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H25" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Third-Party &amp; Supply Chain",'4. Risk Register'!$M$5:$M$66,"Low")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I25" s="9">
         <f>IFERROR(ROUND(AVERAGEIFS('4. Risk Register'!$L$5:$L$66,'4. Risk Register'!$C$5:$C$66,"Third-Party &amp; Supply Chain",'4. Risk Register'!$A$5:$A$66,"Yes"),1),"-")</f>
-        <v/>
+        <v>5.4</v>
       </c>
     </row>
     <row r="26">
@@ -7602,27 +7602,27 @@
       </c>
       <c r="D26" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Operational, Financial &amp; Sustainability",'4. Risk Register'!$A$5:$A$66,"Yes")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="E26" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Operational, Financial &amp; Sustainability",'4. Risk Register'!$M$5:$M$66,"Critical")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F26" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Operational, Financial &amp; Sustainability",'4. Risk Register'!$M$5:$M$66,"High")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G26" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Operational, Financial &amp; Sustainability",'4. Risk Register'!$M$5:$M$66,"Medium")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H26" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Operational, Financial &amp; Sustainability",'4. Risk Register'!$M$5:$M$66,"Low")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="I26" s="9">
         <f>IFERROR(ROUND(AVERAGEIFS('4. Risk Register'!$L$5:$L$66,'4. Risk Register'!$C$5:$C$66,"Operational, Financial &amp; Sustainability",'4. Risk Register'!$A$5:$A$66,"Yes"),1),"-")</f>
-        <v/>
+        <v>4.2</v>
       </c>
     </row>
     <row r="27">
@@ -7633,27 +7633,27 @@
       </c>
       <c r="D27" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Societal, Reputational &amp; AI-Enabled Threats",'4. Risk Register'!$A$5:$A$66,"Yes")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="E27" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Societal, Reputational &amp; AI-Enabled Threats",'4. Risk Register'!$M$5:$M$66,"Critical")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F27" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Societal, Reputational &amp; AI-Enabled Threats",'4. Risk Register'!$M$5:$M$66,"High")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G27" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Societal, Reputational &amp; AI-Enabled Threats",'4. Risk Register'!$M$5:$M$66,"Medium")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="H27" s="9">
         <f>COUNTIFS('4. Risk Register'!$C$5:$C$66,"Societal, Reputational &amp; AI-Enabled Threats",'4. Risk Register'!$M$5:$M$66,"Low")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I27" s="9">
         <f>IFERROR(ROUND(AVERAGEIFS('4. Risk Register'!$L$5:$L$66,'4. Risk Register'!$C$5:$C$66,"Societal, Reputational &amp; AI-Enabled Threats",'4. Risk Register'!$A$5:$A$66,"Yes"),1),"-")</f>
-        <v/>
+        <v>7.2</v>
       </c>
     </row>
     <row r="30">
@@ -7712,360 +7712,360 @@
       <c r="A32" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B32" s="9">
+      <c r="B32" s="9" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$B$5:$B$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,1),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C32" s="14">
+        <v>SEC-01</v>
+      </c>
+      <c r="C32" s="14" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$D$5:$D$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,1),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
+        <v>Prompt injection and jailbreak</v>
       </c>
       <c r="D32" s="14" t="n"/>
       <c r="E32" s="14" t="n"/>
       <c r="F32" s="14" t="n"/>
       <c r="G32" s="9">
         <f>IFERROR(INDEX('4. Risk Register'!$L$5:$L$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,1),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H32" s="9">
+        <v>12.8</v>
+      </c>
+      <c r="H32" s="9" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$M$5:$M$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,1),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I32" s="9">
+        <v>High</v>
+      </c>
+      <c r="I32" s="9" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$O$5:$O$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,1),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="J32" s="14">
+        <v>Mitigate</v>
+      </c>
+      <c r="J32" s="14" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$Q$5:$Q$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,1),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="K32" s="9">
+        <v>CISO</v>
+      </c>
+      <c r="K32" s="9" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$S$5:$S$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,1),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
+        <v>In progress</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B33" s="9">
+      <c r="B33" s="9" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$B$5:$B$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,2),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C33" s="14">
+        <v>PRI-02</v>
+      </c>
+      <c r="C33" s="14" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$D$5:$D$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,2),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
+        <v>Leakage of confidential / personal data via AI</v>
       </c>
       <c r="D33" s="14" t="n"/>
       <c r="E33" s="14" t="n"/>
       <c r="F33" s="14" t="n"/>
       <c r="G33" s="9">
         <f>IFERROR(INDEX('4. Risk Register'!$L$5:$L$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,2),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H33" s="9">
+        <v>12.8</v>
+      </c>
+      <c r="H33" s="9" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$M$5:$M$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,2),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I33" s="9">
+        <v>High</v>
+      </c>
+      <c r="I33" s="9" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$O$5:$O$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,2),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="J33" s="14">
+        <v>Mitigate</v>
+      </c>
+      <c r="J33" s="14" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$Q$5:$Q$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,2),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="K33" s="9">
+        <v>DPO</v>
+      </c>
+      <c r="K33" s="9" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$S$5:$S$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,2),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
+        <v>In progress</v>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B34" s="9">
+      <c r="B34" s="9" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$B$5:$B$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,3),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C34" s="14">
+        <v>HUM-03</v>
+      </c>
+      <c r="C34" s="14" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$D$5:$D$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,3),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
+        <v>Unbounded autonomous agent actions</v>
       </c>
       <c r="D34" s="14" t="n"/>
       <c r="E34" s="14" t="n"/>
       <c r="F34" s="14" t="n"/>
       <c r="G34" s="9">
         <f>IFERROR(INDEX('4. Risk Register'!$L$5:$L$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,3),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H34" s="9">
+        <v>12</v>
+      </c>
+      <c r="H34" s="9" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$M$5:$M$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,3),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I34" s="9">
+        <v>High</v>
+      </c>
+      <c r="I34" s="9" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$O$5:$O$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,3),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="J34" s="14">
+        <v>Mitigate</v>
+      </c>
+      <c r="J34" s="14" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$Q$5:$Q$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,3),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="K34" s="9">
+        <v>Head of Digital Engineering</v>
+      </c>
+      <c r="K34" s="9" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$S$5:$S$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,3),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
+        <v>In progress</v>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B35" s="9">
+      <c r="B35" s="9" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$B$5:$B$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,4),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C35" s="14">
+        <v>SEC-04</v>
+      </c>
+      <c r="C35" s="14" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$D$5:$D$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,4),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
+        <v>Insecure integration and excessive privilege</v>
       </c>
       <c r="D35" s="14" t="n"/>
       <c r="E35" s="14" t="n"/>
       <c r="F35" s="14" t="n"/>
       <c r="G35" s="9">
         <f>IFERROR(INDEX('4. Risk Register'!$L$5:$L$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,4),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H35" s="9">
+        <v>12</v>
+      </c>
+      <c r="H35" s="9" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$M$5:$M$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,4),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I35" s="9">
+        <v>High</v>
+      </c>
+      <c r="I35" s="9" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$O$5:$O$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,4),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="J35" s="14">
+        <v>Mitigate</v>
+      </c>
+      <c r="J35" s="14" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$Q$5:$Q$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,4),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="K35" s="9">
+        <v>CISO</v>
+      </c>
+      <c r="K35" s="9" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$S$5:$S$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,4),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
+        <v>In progress</v>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B36" s="9">
+      <c r="B36" s="9" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$B$5:$B$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,5),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C36" s="14">
+        <v>SEC-06</v>
+      </c>
+      <c r="C36" s="14" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$D$5:$D$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,5),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
+        <v>Agent memory poisoning &amp; cross-session leakage</v>
       </c>
       <c r="D36" s="14" t="n"/>
       <c r="E36" s="14" t="n"/>
       <c r="F36" s="14" t="n"/>
       <c r="G36" s="9">
         <f>IFERROR(INDEX('4. Risk Register'!$L$5:$L$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,5),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H36" s="9">
+        <v>9.6</v>
+      </c>
+      <c r="H36" s="9" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$M$5:$M$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,5),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I36" s="9">
+        <v>Medium</v>
+      </c>
+      <c r="I36" s="9" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$O$5:$O$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,5),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="J36" s="14">
+        <v>Mitigate</v>
+      </c>
+      <c r="J36" s="14" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$Q$5:$Q$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,5),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="K36" s="9">
+        <v>Head of Digital Engineering</v>
+      </c>
+      <c r="K36" s="9" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$S$5:$S$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,5),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
+        <v>In progress</v>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B37" s="9">
+      <c r="B37" s="9" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$B$5:$B$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,6),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C37" s="14">
+        <v>PER-02</v>
+      </c>
+      <c r="C37" s="14" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$D$5:$D$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,6),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
+        <v>Hallucination / confabulation</v>
       </c>
       <c r="D37" s="14" t="n"/>
       <c r="E37" s="14" t="n"/>
       <c r="F37" s="14" t="n"/>
       <c r="G37" s="9">
         <f>IFERROR(INDEX('4. Risk Register'!$L$5:$L$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,6),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H37" s="9">
+        <v>9.6</v>
+      </c>
+      <c r="H37" s="9" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$M$5:$M$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,6),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I37" s="9">
+        <v>Medium</v>
+      </c>
+      <c r="I37" s="9" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$O$5:$O$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,6),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="J37" s="14">
+        <v>Mitigate</v>
+      </c>
+      <c r="J37" s="14" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$Q$5:$Q$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,6),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="K37" s="9">
+        <v>Product Owner</v>
+      </c>
+      <c r="K37" s="9" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$S$5:$S$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,6),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
+        <v>In progress</v>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="B38" s="9">
+      <c r="B38" s="9" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$B$5:$B$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,7),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C38" s="14">
+        <v>LEG-03</v>
+      </c>
+      <c r="C38" s="14" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$D$5:$D$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,7),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
+        <v>Breach of sector or local regulation</v>
       </c>
       <c r="D38" s="14" t="n"/>
       <c r="E38" s="14" t="n"/>
       <c r="F38" s="14" t="n"/>
       <c r="G38" s="9">
         <f>IFERROR(INDEX('4. Risk Register'!$L$5:$L$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,7),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H38" s="9">
+        <v>9.6</v>
+      </c>
+      <c r="H38" s="9" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$M$5:$M$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,7),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I38" s="9">
+        <v>Medium</v>
+      </c>
+      <c r="I38" s="9" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$O$5:$O$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,7),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="J38" s="14">
+        <v>Mitigate</v>
+      </c>
+      <c r="J38" s="14" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$Q$5:$Q$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,7),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="K38" s="9">
+        <v>Compliance</v>
+      </c>
+      <c r="K38" s="9" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$S$5:$S$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,7),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
+        <v>In progress</v>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="B39" s="9">
+      <c r="B39" s="9" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$B$5:$B$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,8),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C39" s="14">
+        <v>SOC-03</v>
+      </c>
+      <c r="C39" s="14" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$D$5:$D$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,8),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
+        <v>Deepfake and AI-enabled fraud against the organisation</v>
       </c>
       <c r="D39" s="14" t="n"/>
       <c r="E39" s="14" t="n"/>
       <c r="F39" s="14" t="n"/>
       <c r="G39" s="9">
         <f>IFERROR(INDEX('4. Risk Register'!$L$5:$L$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,8),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H39" s="9">
+        <v>7.2</v>
+      </c>
+      <c r="H39" s="9" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$M$5:$M$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,8),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I39" s="9">
+        <v>Medium</v>
+      </c>
+      <c r="I39" s="9" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$O$5:$O$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,8),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="J39" s="14">
+        <v>Mitigate</v>
+      </c>
+      <c r="J39" s="14" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$Q$5:$Q$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,8),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="K39" s="9">
+        <v>Fraud Risk</v>
+      </c>
+      <c r="K39" s="9" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$S$5:$S$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,8),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
+        <v>In progress</v>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="B40" s="9">
+      <c r="B40" s="9" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$B$5:$B$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,9),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C40" s="14">
+        <v>SOC-02</v>
+      </c>
+      <c r="C40" s="14" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$D$5:$D$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,9),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
+        <v>Misinformation and loss of stakeholder trust</v>
       </c>
       <c r="D40" s="14" t="n"/>
       <c r="E40" s="14" t="n"/>
       <c r="F40" s="14" t="n"/>
       <c r="G40" s="9">
         <f>IFERROR(INDEX('4. Risk Register'!$L$5:$L$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,9),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H40" s="9">
+        <v>7.2</v>
+      </c>
+      <c r="H40" s="9" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$M$5:$M$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,9),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I40" s="9">
+        <v>Medium</v>
+      </c>
+      <c r="I40" s="9" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$O$5:$O$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,9),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="J40" s="14">
+        <v>Mitigate</v>
+      </c>
+      <c r="J40" s="14" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$Q$5:$Q$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,9),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="K40" s="9">
+        <v>Conduct Risk</v>
+      </c>
+      <c r="K40" s="9" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$S$5:$S$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,9),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
+        <v>Treatment planned</v>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="B41" s="9">
+      <c r="B41" s="9" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$B$5:$B$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,10),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C41" s="14">
+        <v>FAI-02</v>
+      </c>
+      <c r="C41" s="14" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$D$5:$D$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,10),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
+        <v>Unrepresentative training or evaluation data</v>
       </c>
       <c r="D41" s="14" t="n"/>
       <c r="E41" s="14" t="n"/>
       <c r="F41" s="14" t="n"/>
       <c r="G41" s="9">
         <f>IFERROR(INDEX('4. Risk Register'!$L$5:$L$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,10),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H41" s="9">
+        <v>7.2</v>
+      </c>
+      <c r="H41" s="9" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$M$5:$M$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,10),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I41" s="9">
+        <v>Medium</v>
+      </c>
+      <c r="I41" s="9" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$O$5:$O$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,10),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="J41" s="14">
+        <v>Mitigate</v>
+      </c>
+      <c r="J41" s="14" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$Q$5:$Q$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,10),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
-      </c>
-      <c r="K41" s="9">
+        <v>Data Science Lead</v>
+      </c>
+      <c r="K41" s="9" t="str">
         <f>IFERROR(INDEX('4. Risk Register'!$S$5:$S$66,MATCH(LARGE('4. Risk Register'!$V$5:$V$66,10),'4. Risk Register'!$V$5:$V$66,0)),"")</f>
-        <v/>
+        <v>Treatment planned</v>
       </c>
     </row>
     <row r="43">
@@ -8081,9 +8081,9 @@
           <t>Required approval authority:</t>
         </is>
       </c>
-      <c r="D44">
+      <c r="D44" t="str">
         <f>'3. Risk Tiering'!C23</f>
-        <v/>
+        <v>AI Committee / CoE</v>
       </c>
     </row>
     <row r="45">
